--- a/data/historico/historico_documentos.xlsx
+++ b/data/historico/historico_documentos.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E186"/>
+  <dimension ref="A1:E216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2185,1743 +2185,1981 @@
       <c r="A104" t="n">
         <v>4034123</v>
       </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>2400002805</t>
-        </is>
+      <c r="B104" t="n">
+        <v>2400002805</v>
       </c>
       <c r="C104" t="n">
         <v>400</v>
       </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>600012400</t>
-        </is>
+      <c r="D104" t="n">
+        <v>600012400</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46219.72766950409</v>
+        <v>46219.72766950232</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
         <v>4000194</v>
       </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>2500045827</t>
-        </is>
+      <c r="B105" t="n">
+        <v>2500045827</v>
       </c>
       <c r="C105" t="n">
         <v>400</v>
       </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>600012400</t>
-        </is>
+      <c r="D105" t="n">
+        <v>600012400</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46219.72766950409</v>
+        <v>46219.72766950232</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
         <v>4021439</v>
       </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>2500035963</t>
-        </is>
+      <c r="B106" t="n">
+        <v>2500035963</v>
       </c>
       <c r="C106" t="n">
         <v>400</v>
       </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>600012400</t>
-        </is>
+      <c r="D106" t="n">
+        <v>600012400</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46219.72766950409</v>
+        <v>46219.72766950232</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
         <v>4000688</v>
       </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>2500045655</t>
-        </is>
+      <c r="B107" t="n">
+        <v>2500045655</v>
       </c>
       <c r="C107" t="n">
         <v>400</v>
       </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>600012400</t>
-        </is>
+      <c r="D107" t="n">
+        <v>600012400</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46219.72766950409</v>
+        <v>46219.72766950232</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
         <v>4036635</v>
       </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>2500043146</t>
-        </is>
+      <c r="B108" t="n">
+        <v>2500043146</v>
       </c>
       <c r="C108" t="n">
         <v>400</v>
       </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>600012400</t>
-        </is>
+      <c r="D108" t="n">
+        <v>600012400</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46219.72766950409</v>
+        <v>46219.72766950232</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
         <v>4000194</v>
       </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>2500044511</t>
-        </is>
+      <c r="B109" t="n">
+        <v>2500044511</v>
       </c>
       <c r="C109" t="n">
         <v>400</v>
       </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>600012400</t>
-        </is>
+      <c r="D109" t="n">
+        <v>600012400</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46219.72766950409</v>
+        <v>46219.72766950232</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
         <v>4042278</v>
       </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>2600016475</t>
-        </is>
+      <c r="B110" t="n">
+        <v>2600016475</v>
       </c>
       <c r="C110" t="n">
         <v>400</v>
       </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>600012400</t>
-        </is>
+      <c r="D110" t="n">
+        <v>600012400</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46219.72766950409</v>
+        <v>46219.72766950232</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
         <v>4033776</v>
       </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>2600001895</t>
-        </is>
+      <c r="B111" t="n">
+        <v>2600001895</v>
       </c>
       <c r="C111" t="n">
         <v>400</v>
       </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>600012400</t>
-        </is>
+      <c r="D111" t="n">
+        <v>600012400</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46219.72766950409</v>
+        <v>46219.72766950232</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
         <v>4038921</v>
       </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>2500029182</t>
-        </is>
+      <c r="B112" t="n">
+        <v>2500029182</v>
       </c>
       <c r="C112" t="n">
         <v>400</v>
       </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>600012400</t>
-        </is>
+      <c r="D112" t="n">
+        <v>600012400</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46219.72766950409</v>
+        <v>46219.72766950232</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
         <v>4038921</v>
       </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>2500041942</t>
-        </is>
+      <c r="B113" t="n">
+        <v>2500041942</v>
       </c>
       <c r="C113" t="n">
         <v>400</v>
       </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>600012400</t>
-        </is>
+      <c r="D113" t="n">
+        <v>600012400</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46219.72766950409</v>
+        <v>46219.72766950232</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
         <v>4038915</v>
       </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>2500041125</t>
-        </is>
+      <c r="B114" t="n">
+        <v>2500041125</v>
       </c>
       <c r="C114" t="n">
         <v>400</v>
       </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>600012400</t>
-        </is>
+      <c r="D114" t="n">
+        <v>600012400</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46219.72766950409</v>
+        <v>46219.72766950232</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
         <v>4009062</v>
       </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>2500039537</t>
-        </is>
+      <c r="B115" t="n">
+        <v>2500039537</v>
       </c>
       <c r="C115" t="n">
         <v>400</v>
       </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>600012400</t>
-        </is>
+      <c r="D115" t="n">
+        <v>600012400</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46219.72766950409</v>
+        <v>46219.72766950232</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
         <v>4038915</v>
       </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>2500020147</t>
-        </is>
+      <c r="B116" t="n">
+        <v>2500020147</v>
       </c>
       <c r="C116" t="n">
         <v>400</v>
       </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>600012400</t>
-        </is>
+      <c r="D116" t="n">
+        <v>600012400</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46219.72766950409</v>
+        <v>46219.72766950232</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
         <v>4036765</v>
       </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>2600007337</t>
-        </is>
+      <c r="B117" t="n">
+        <v>2600007337</v>
       </c>
       <c r="C117" t="n">
         <v>400</v>
       </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>600012400</t>
-        </is>
+      <c r="D117" t="n">
+        <v>600012400</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46219.72766950409</v>
+        <v>46219.72766950232</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
         <v>3002286</v>
       </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>2600013791</t>
-        </is>
+      <c r="B118" t="n">
+        <v>2600013791</v>
       </c>
       <c r="C118" t="n">
         <v>400</v>
       </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>600012400</t>
-        </is>
+      <c r="D118" t="n">
+        <v>600012400</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46219.72766950409</v>
+        <v>46219.72766950232</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
         <v>3000283</v>
       </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>2500043884</t>
-        </is>
+      <c r="B119" t="n">
+        <v>2500043884</v>
       </c>
       <c r="C119" t="n">
         <v>400</v>
       </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>600012400</t>
-        </is>
+      <c r="D119" t="n">
+        <v>600012400</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46219.72766950409</v>
+        <v>46219.72766950232</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
         <v>3000226</v>
       </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>2400039501</t>
-        </is>
+      <c r="B120" t="n">
+        <v>2400039501</v>
       </c>
       <c r="C120" t="n">
         <v>400</v>
       </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>600012400</t>
-        </is>
+      <c r="D120" t="n">
+        <v>600012400</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46219.72766950409</v>
+        <v>46219.72766950232</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
         <v>3000308</v>
       </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>2300036125</t>
-        </is>
+      <c r="B121" t="n">
+        <v>2300036125</v>
       </c>
       <c r="C121" t="n">
         <v>400</v>
       </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>600012400</t>
-        </is>
+      <c r="D121" t="n">
+        <v>600012400</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46219.72766950409</v>
+        <v>46219.72766950232</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
         <v>3000037</v>
       </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>2500036985</t>
-        </is>
+      <c r="B122" t="n">
+        <v>2500036985</v>
       </c>
       <c r="C122" t="n">
         <v>400</v>
       </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>600012400</t>
-        </is>
+      <c r="D122" t="n">
+        <v>600012400</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46219.72766950409</v>
+        <v>46219.72766950232</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
         <v>3003905</v>
       </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>2200006176</t>
-        </is>
+      <c r="B123" t="n">
+        <v>2200006176</v>
       </c>
       <c r="C123" t="n">
         <v>400</v>
       </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>600012400</t>
-        </is>
+      <c r="D123" t="n">
+        <v>600012400</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46219.72766950409</v>
+        <v>46219.72766950232</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
         <v>3005374</v>
       </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>2600018808</t>
-        </is>
+      <c r="B124" t="n">
+        <v>2600018808</v>
       </c>
       <c r="C124" t="n">
         <v>400</v>
       </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>600012400</t>
-        </is>
+      <c r="D124" t="n">
+        <v>600012400</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46219.72766950409</v>
+        <v>46219.72766950232</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
         <v>3000514</v>
       </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>2300029770</t>
-        </is>
+      <c r="B125" t="n">
+        <v>2300029770</v>
       </c>
       <c r="C125" t="n">
         <v>400</v>
       </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>600012400</t>
-        </is>
+      <c r="D125" t="n">
+        <v>600012400</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46219.72766950409</v>
+        <v>46219.72766950232</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
         <v>3000530</v>
       </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>2400027417</t>
-        </is>
+      <c r="B126" t="n">
+        <v>2400027417</v>
       </c>
       <c r="C126" t="n">
         <v>400</v>
       </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>600012400</t>
-        </is>
+      <c r="D126" t="n">
+        <v>600012400</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46219.72766950409</v>
+        <v>46219.72766950232</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
         <v>3001654</v>
       </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>2500015753</t>
-        </is>
+      <c r="B127" t="n">
+        <v>2500015753</v>
       </c>
       <c r="C127" t="n">
         <v>400</v>
       </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>600012400</t>
-        </is>
+      <c r="D127" t="n">
+        <v>600012400</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46219.72766950409</v>
+        <v>46219.72766950232</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
         <v>3005183</v>
       </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>2500036212</t>
-        </is>
+      <c r="B128" t="n">
+        <v>2500036212</v>
       </c>
       <c r="C128" t="n">
         <v>400</v>
       </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>600012400</t>
-        </is>
+      <c r="D128" t="n">
+        <v>600012400</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46219.72766950409</v>
+        <v>46219.72766950232</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
         <v>3000045</v>
       </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>2400022273</t>
-        </is>
+      <c r="B129" t="n">
+        <v>2400022273</v>
       </c>
       <c r="C129" t="n">
         <v>400</v>
       </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>600012400</t>
-        </is>
+      <c r="D129" t="n">
+        <v>600012400</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46219.72766950409</v>
+        <v>46219.72766950232</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
         <v>3000159</v>
       </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>2600006048</t>
-        </is>
+      <c r="B130" t="n">
+        <v>2600006048</v>
       </c>
       <c r="C130" t="n">
         <v>400</v>
       </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>600012400</t>
-        </is>
+      <c r="D130" t="n">
+        <v>600012400</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46219.72766950409</v>
+        <v>46219.72766950232</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
         <v>3000552</v>
       </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>2600004772</t>
-        </is>
+      <c r="B131" t="n">
+        <v>2600004772</v>
       </c>
       <c r="C131" t="n">
         <v>400</v>
       </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>600012400</t>
-        </is>
+      <c r="D131" t="n">
+        <v>600012400</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46219.72766950409</v>
+        <v>46219.72766950232</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
         <v>4001566</v>
       </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>2600007843</t>
-        </is>
+      <c r="B132" t="n">
+        <v>2600007843</v>
       </c>
       <c r="C132" t="n">
         <v>400</v>
       </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>600012400</t>
-        </is>
+      <c r="D132" t="n">
+        <v>600012400</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46219.72766950409</v>
+        <v>46219.72766950232</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
         <v>3000223</v>
       </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>2400022595</t>
-        </is>
+      <c r="B133" t="n">
+        <v>2400022595</v>
       </c>
       <c r="C133" t="n">
         <v>400</v>
       </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>600012400</t>
-        </is>
+      <c r="D133" t="n">
+        <v>600012400</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46219.72766950409</v>
+        <v>46219.72766950232</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
         <v>3000401</v>
       </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>2500046008</t>
-        </is>
+      <c r="B134" t="n">
+        <v>2500046008</v>
       </c>
       <c r="C134" t="n">
         <v>400</v>
       </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>600012400</t>
-        </is>
+      <c r="D134" t="n">
+        <v>600012400</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46219.72766950409</v>
+        <v>46219.72766950232</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
         <v>3000541</v>
       </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>2500021517</t>
-        </is>
+      <c r="B135" t="n">
+        <v>2500021517</v>
       </c>
       <c r="C135" t="n">
         <v>400</v>
       </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>600012400</t>
-        </is>
+      <c r="D135" t="n">
+        <v>600012400</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46219.72766950409</v>
+        <v>46219.72766950232</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
         <v>3003818</v>
       </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>2300010087</t>
-        </is>
+      <c r="B136" t="n">
+        <v>2300010087</v>
       </c>
       <c r="C136" t="n">
         <v>400</v>
       </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>600012400</t>
-        </is>
+      <c r="D136" t="n">
+        <v>600012400</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46219.72766950409</v>
+        <v>46219.72766950232</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
         <v>3004347</v>
       </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>2400016921</t>
-        </is>
+      <c r="B137" t="n">
+        <v>2400016921</v>
       </c>
       <c r="C137" t="n">
         <v>400</v>
       </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>600012400</t>
-        </is>
+      <c r="D137" t="n">
+        <v>600012400</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46219.72766950409</v>
+        <v>46219.72766950232</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
         <v>3000504</v>
       </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>2500039786</t>
-        </is>
+      <c r="B138" t="n">
+        <v>2500039786</v>
       </c>
       <c r="C138" t="n">
         <v>400</v>
       </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>600012400</t>
-        </is>
+      <c r="D138" t="n">
+        <v>600012400</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46219.72766950409</v>
+        <v>46219.72766950232</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
         <v>3003697</v>
       </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>2500024474</t>
-        </is>
+      <c r="B139" t="n">
+        <v>2500024474</v>
       </c>
       <c r="C139" t="n">
         <v>400</v>
       </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>600012400</t>
-        </is>
+      <c r="D139" t="n">
+        <v>600012400</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46219.72766950409</v>
+        <v>46219.72766950232</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
         <v>3000248</v>
       </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>2400021064</t>
-        </is>
+      <c r="B140" t="n">
+        <v>2400021064</v>
       </c>
       <c r="C140" t="n">
         <v>400</v>
       </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>600012400</t>
-        </is>
+      <c r="D140" t="n">
+        <v>600012400</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46219.72766950409</v>
+        <v>46219.72766950232</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
         <v>3000283</v>
       </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>2200021343</t>
-        </is>
+      <c r="B141" t="n">
+        <v>2200021343</v>
       </c>
       <c r="C141" t="n">
         <v>400</v>
       </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>600012400</t>
-        </is>
+      <c r="D141" t="n">
+        <v>600012400</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46219.72766950409</v>
+        <v>46219.72766950232</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
         <v>3000464</v>
       </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>2600004513</t>
-        </is>
+      <c r="B142" t="n">
+        <v>2600004513</v>
       </c>
       <c r="C142" t="n">
         <v>400</v>
       </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>600012400</t>
-        </is>
+      <c r="D142" t="n">
+        <v>600012400</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46219.72766950409</v>
+        <v>46219.72766950232</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
         <v>3000286</v>
       </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>2100044072</t>
-        </is>
+      <c r="B143" t="n">
+        <v>2100044072</v>
       </c>
       <c r="C143" t="n">
         <v>400</v>
       </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>600012400</t>
-        </is>
+      <c r="D143" t="n">
+        <v>600012400</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46219.72766950409</v>
+        <v>46219.72766950232</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
         <v>3000068</v>
       </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>2500007417</t>
-        </is>
+      <c r="B144" t="n">
+        <v>2500007417</v>
       </c>
       <c r="C144" t="n">
         <v>400</v>
       </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>600012400</t>
-        </is>
+      <c r="D144" t="n">
+        <v>600012400</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46219.72766950409</v>
+        <v>46219.72766950232</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
         <v>3000429</v>
       </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>2500016590</t>
-        </is>
+      <c r="B145" t="n">
+        <v>2500016590</v>
       </c>
       <c r="C145" t="n">
         <v>400</v>
       </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>600012400</t>
-        </is>
+      <c r="D145" t="n">
+        <v>600012400</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46219.72766950409</v>
+        <v>46219.72766950232</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
         <v>3004763</v>
       </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>2600006599</t>
-        </is>
+      <c r="B146" t="n">
+        <v>2600006599</v>
       </c>
       <c r="C146" t="n">
         <v>400</v>
       </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>600012400</t>
-        </is>
+      <c r="D146" t="n">
+        <v>600012400</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46219.72766950409</v>
+        <v>46219.72766950232</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
         <v>3000436</v>
       </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>2500021933</t>
-        </is>
+      <c r="B147" t="n">
+        <v>2500021933</v>
       </c>
       <c r="C147" t="n">
         <v>400</v>
       </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>600012400</t>
-        </is>
+      <c r="D147" t="n">
+        <v>600012400</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46219.72766950409</v>
+        <v>46219.72766950232</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
         <v>3000560</v>
       </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>2600008270</t>
-        </is>
+      <c r="B148" t="n">
+        <v>2600008270</v>
       </c>
       <c r="C148" t="n">
         <v>400</v>
       </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>600012400</t>
-        </is>
+      <c r="D148" t="n">
+        <v>600012400</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46219.72766950409</v>
+        <v>46219.72766950232</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
         <v>3001656</v>
       </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>2500009811</t>
-        </is>
+      <c r="B149" t="n">
+        <v>2500009811</v>
       </c>
       <c r="C149" t="n">
         <v>400</v>
       </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>600012400</t>
-        </is>
+      <c r="D149" t="n">
+        <v>600012400</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46219.72766950409</v>
+        <v>46219.72766950232</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
         <v>3005182</v>
       </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>2500036211</t>
-        </is>
+      <c r="B150" t="n">
+        <v>2500036211</v>
       </c>
       <c r="C150" t="n">
         <v>400</v>
       </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>600012400</t>
-        </is>
+      <c r="D150" t="n">
+        <v>600012400</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46219.72766950409</v>
+        <v>46219.72766950232</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
         <v>3003695</v>
       </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>2500024475</t>
-        </is>
+      <c r="B151" t="n">
+        <v>2500024475</v>
       </c>
       <c r="C151" t="n">
         <v>400</v>
       </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>600012400</t>
-        </is>
+      <c r="D151" t="n">
+        <v>600012400</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46219.72766950409</v>
+        <v>46219.72766950232</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
         <v>3004469</v>
       </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>2300029145</t>
-        </is>
+      <c r="B152" t="n">
+        <v>2300029145</v>
       </c>
       <c r="C152" t="n">
         <v>400</v>
       </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>600012400</t>
-        </is>
+      <c r="D152" t="n">
+        <v>600012400</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46219.72766950409</v>
+        <v>46219.72766950232</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
         <v>3000157</v>
       </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>2300009303</t>
-        </is>
+      <c r="B153" t="n">
+        <v>2300009303</v>
       </c>
       <c r="C153" t="n">
         <v>400</v>
       </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>600012400</t>
-        </is>
+      <c r="D153" t="n">
+        <v>600012400</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46219.72766950409</v>
+        <v>46219.72766950232</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
         <v>3000490</v>
       </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>2500039413</t>
-        </is>
+      <c r="B154" t="n">
+        <v>2500039413</v>
       </c>
       <c r="C154" t="n">
         <v>400</v>
       </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>600012400</t>
-        </is>
+      <c r="D154" t="n">
+        <v>600012400</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46219.72766950409</v>
+        <v>46219.72766950232</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
         <v>3004367</v>
       </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>2400031808</t>
-        </is>
+      <c r="B155" t="n">
+        <v>2400031808</v>
       </c>
       <c r="C155" t="n">
         <v>400</v>
       </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>600012400</t>
-        </is>
+      <c r="D155" t="n">
+        <v>600012400</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46219.72766950409</v>
+        <v>46219.72766950232</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
         <v>3000546</v>
       </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>2400014170</t>
-        </is>
+      <c r="B156" t="n">
+        <v>2400014170</v>
       </c>
       <c r="C156" t="n">
         <v>400</v>
       </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>600012400</t>
-        </is>
+      <c r="D156" t="n">
+        <v>600012400</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46219.72766950409</v>
+        <v>46219.72766950232</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
         <v>3001646</v>
       </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>2500011316</t>
-        </is>
+      <c r="B157" t="n">
+        <v>2500011316</v>
       </c>
       <c r="C157" t="n">
         <v>400</v>
       </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>600012400</t>
-        </is>
+      <c r="D157" t="n">
+        <v>600012400</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46219.72766950409</v>
+        <v>46219.72766950232</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
         <v>3004911</v>
       </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>2400026379</t>
-        </is>
+      <c r="B158" t="n">
+        <v>2400026379</v>
       </c>
       <c r="C158" t="n">
         <v>400</v>
       </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>600012400</t>
-        </is>
+      <c r="D158" t="n">
+        <v>600012400</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46219.72766950409</v>
+        <v>46219.72766950232</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
         <v>3000066</v>
       </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>2300039452</t>
-        </is>
+      <c r="B159" t="n">
+        <v>2300039452</v>
       </c>
       <c r="C159" t="n">
         <v>400</v>
       </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>600012400</t>
-        </is>
+      <c r="D159" t="n">
+        <v>600012400</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46219.72766950409</v>
+        <v>46219.72766950232</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
         <v>3004367</v>
       </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>2400031809</t>
-        </is>
+      <c r="B160" t="n">
+        <v>2400031809</v>
       </c>
       <c r="C160" t="n">
         <v>400</v>
       </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>600012400</t>
-        </is>
+      <c r="D160" t="n">
+        <v>600012400</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46219.72766950409</v>
+        <v>46219.72766950232</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
         <v>3005198</v>
       </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>2500007037</t>
-        </is>
+      <c r="B161" t="n">
+        <v>2500007037</v>
       </c>
       <c r="C161" t="n">
         <v>400</v>
       </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>600012400</t>
-        </is>
+      <c r="D161" t="n">
+        <v>600012400</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46219.72766950409</v>
+        <v>46219.72766950232</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
         <v>3000473</v>
       </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>2600007959</t>
-        </is>
+      <c r="B162" t="n">
+        <v>2600007959</v>
       </c>
       <c r="C162" t="n">
         <v>400</v>
       </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>600012400</t>
-        </is>
+      <c r="D162" t="n">
+        <v>600012400</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46219.72766950409</v>
+        <v>46219.72766950232</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
         <v>3000078</v>
       </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>2600013788</t>
-        </is>
+      <c r="B163" t="n">
+        <v>2600013788</v>
       </c>
       <c r="C163" t="n">
         <v>400</v>
       </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>600012400</t>
-        </is>
+      <c r="D163" t="n">
+        <v>600012400</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46219.72766950409</v>
+        <v>46219.72766950232</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
         <v>3000226</v>
       </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>2500013395</t>
-        </is>
+      <c r="B164" t="n">
+        <v>2500013395</v>
       </c>
       <c r="C164" t="n">
         <v>400</v>
       </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>600012400</t>
-        </is>
+      <c r="D164" t="n">
+        <v>600012400</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46219.72766950409</v>
+        <v>46219.72766950232</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
         <v>3000253</v>
       </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>2600009307</t>
-        </is>
+      <c r="B165" t="n">
+        <v>2600009307</v>
       </c>
       <c r="C165" t="n">
         <v>400</v>
       </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>600012400</t>
-        </is>
+      <c r="D165" t="n">
+        <v>600012400</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46219.72766950409</v>
+        <v>46219.72766950232</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
         <v>3000401</v>
       </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>2600010724</t>
-        </is>
+      <c r="B166" t="n">
+        <v>2600010724</v>
       </c>
       <c r="C166" t="n">
         <v>400</v>
       </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>600012400</t>
-        </is>
+      <c r="D166" t="n">
+        <v>600012400</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46219.72766950409</v>
+        <v>46219.72766950232</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
         <v>3002742</v>
       </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>2600009136</t>
-        </is>
+      <c r="B167" t="n">
+        <v>2600009136</v>
       </c>
       <c r="C167" t="n">
         <v>400</v>
       </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>600012400</t>
-        </is>
+      <c r="D167" t="n">
+        <v>600012400</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46219.72766950409</v>
+        <v>46219.72766950232</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
         <v>3001656</v>
       </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>2600008925</t>
-        </is>
+      <c r="B168" t="n">
+        <v>2600008925</v>
       </c>
       <c r="C168" t="n">
         <v>400</v>
       </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>600012400</t>
-        </is>
+      <c r="D168" t="n">
+        <v>600012400</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46219.72766950409</v>
+        <v>46219.72766950232</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
         <v>3003209</v>
       </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>2600012407</t>
-        </is>
+      <c r="B169" t="n">
+        <v>2600012407</v>
       </c>
       <c r="C169" t="n">
         <v>400</v>
       </c>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t>600012400</t>
-        </is>
+      <c r="D169" t="n">
+        <v>600012400</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46219.72766950409</v>
+        <v>46219.72766950232</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
         <v>3004304</v>
       </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>2300021855</t>
-        </is>
+      <c r="B170" t="n">
+        <v>2300021855</v>
       </c>
       <c r="C170" t="n">
         <v>400</v>
       </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>600012400</t>
-        </is>
+      <c r="D170" t="n">
+        <v>600012400</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46219.72766950409</v>
+        <v>46219.72766950232</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
         <v>3000523</v>
       </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>2400022609</t>
-        </is>
+      <c r="B171" t="n">
+        <v>2400022609</v>
       </c>
       <c r="C171" t="n">
         <v>400</v>
       </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>600012400</t>
-        </is>
+      <c r="D171" t="n">
+        <v>600012400</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46219.72766950409</v>
+        <v>46219.72766950232</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
         <v>3000363</v>
       </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>2500025622</t>
-        </is>
+      <c r="B172" t="n">
+        <v>2500025622</v>
       </c>
       <c r="C172" t="n">
         <v>400</v>
       </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>600012400</t>
-        </is>
+      <c r="D172" t="n">
+        <v>600012400</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46219.72766950409</v>
+        <v>46219.72766950232</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
         <v>3000473</v>
       </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>2500002724</t>
-        </is>
+      <c r="B173" t="n">
+        <v>2500002724</v>
       </c>
       <c r="C173" t="n">
         <v>400</v>
       </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>600012400</t>
-        </is>
+      <c r="D173" t="n">
+        <v>600012400</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46219.72766950409</v>
+        <v>46219.72766950232</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
         <v>3000473</v>
       </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>2500013397</t>
-        </is>
+      <c r="B174" t="n">
+        <v>2500013397</v>
       </c>
       <c r="C174" t="n">
         <v>400</v>
       </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>600012400</t>
-        </is>
+      <c r="D174" t="n">
+        <v>600012400</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46219.72766950409</v>
+        <v>46219.72766950232</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
         <v>3000567</v>
       </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>2600010566</t>
-        </is>
+      <c r="B175" t="n">
+        <v>2600010566</v>
       </c>
       <c r="C175" t="n">
         <v>400</v>
       </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>600012400</t>
-        </is>
+      <c r="D175" t="n">
+        <v>600012400</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46219.72766950409</v>
+        <v>46219.72766950232</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
         <v>3000068</v>
       </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>2500043544</t>
-        </is>
+      <c r="B176" t="n">
+        <v>2500043544</v>
       </c>
       <c r="C176" t="n">
         <v>400</v>
       </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>600012400</t>
-        </is>
+      <c r="D176" t="n">
+        <v>600012400</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46219.72766950409</v>
+        <v>46219.72766950232</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
         <v>3000286</v>
       </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>2400038367</t>
-        </is>
+      <c r="B177" t="n">
+        <v>2400038367</v>
       </c>
       <c r="C177" t="n">
         <v>400</v>
       </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>600012400</t>
-        </is>
+      <c r="D177" t="n">
+        <v>600012400</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46219.72766950409</v>
+        <v>46219.72766950232</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
         <v>3000401</v>
       </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>2500012622</t>
-        </is>
+      <c r="B178" t="n">
+        <v>2500012622</v>
       </c>
       <c r="C178" t="n">
         <v>400</v>
       </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>600012400</t>
-        </is>
+      <c r="D178" t="n">
+        <v>600012400</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46219.72766950409</v>
+        <v>46219.72766950232</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
         <v>3000514</v>
       </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>2500013650</t>
-        </is>
+      <c r="B179" t="n">
+        <v>2500013650</v>
       </c>
       <c r="C179" t="n">
         <v>400</v>
       </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>600012400</t>
-        </is>
+      <c r="D179" t="n">
+        <v>600012400</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46219.72766950409</v>
+        <v>46219.72766950232</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
         <v>3003818</v>
       </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>2300022939</t>
-        </is>
+      <c r="B180" t="n">
+        <v>2300022939</v>
       </c>
       <c r="C180" t="n">
         <v>400</v>
       </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>600012400</t>
-        </is>
+      <c r="D180" t="n">
+        <v>600012400</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46219.72766950409</v>
+        <v>46219.72766950232</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
         <v>3004356</v>
       </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>2300005754</t>
-        </is>
+      <c r="B181" t="n">
+        <v>2300005754</v>
       </c>
       <c r="C181" t="n">
         <v>400</v>
       </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>600012400</t>
-        </is>
+      <c r="D181" t="n">
+        <v>600012400</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46219.72766950409</v>
+        <v>46219.72766950232</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
         <v>3001649</v>
       </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>2400036656</t>
-        </is>
+      <c r="B182" t="n">
+        <v>2400036656</v>
       </c>
       <c r="C182" t="n">
         <v>400</v>
       </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>600012400</t>
-        </is>
+      <c r="D182" t="n">
+        <v>600012400</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46219.72766950409</v>
+        <v>46219.72766950232</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
         <v>3002882</v>
       </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>2500012584</t>
-        </is>
+      <c r="B183" t="n">
+        <v>2500012584</v>
       </c>
       <c r="C183" t="n">
         <v>400</v>
       </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>600012400</t>
-        </is>
+      <c r="D183" t="n">
+        <v>600012400</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46219.72766950409</v>
+        <v>46219.72766950232</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
         <v>3000226</v>
       </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>2400037346</t>
-        </is>
+      <c r="B184" t="n">
+        <v>2400037346</v>
       </c>
       <c r="C184" t="n">
         <v>400</v>
       </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>600012400</t>
-        </is>
+      <c r="D184" t="n">
+        <v>600012400</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46219.72766950409</v>
+        <v>46219.72766950232</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
         <v>3005396</v>
       </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>2600019201</t>
-        </is>
+      <c r="B185" t="n">
+        <v>2600019201</v>
       </c>
       <c r="C185" t="n">
         <v>400</v>
       </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>600012400</t>
-        </is>
+      <c r="D185" t="n">
+        <v>600012400</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46219.72766950409</v>
+        <v>46219.72766950232</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
         <v>3005413</v>
       </c>
-      <c r="B186" t="inlineStr">
+      <c r="B186" t="n">
+        <v>2600019803</v>
+      </c>
+      <c r="C186" t="n">
+        <v>400</v>
+      </c>
+      <c r="D186" t="n">
+        <v>600012400</v>
+      </c>
+      <c r="E186" s="1" t="n">
+        <v>46219.72766950232</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>3000366</v>
+      </c>
+      <c r="B187" t="n">
+        <v>2600018162</v>
+      </c>
+      <c r="C187" t="n">
+        <v>300</v>
+      </c>
+      <c r="D187" t="n">
+        <v>600002123</v>
+      </c>
+      <c r="E187" s="1" t="n">
+        <v>46219.77955907407</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>3000366</v>
+      </c>
+      <c r="B188" t="n">
+        <v>2600015715</v>
+      </c>
+      <c r="C188" t="n">
+        <v>300</v>
+      </c>
+      <c r="D188" t="n">
+        <v>600002123</v>
+      </c>
+      <c r="E188" s="1" t="n">
+        <v>46219.77955907407</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>3000550</v>
+      </c>
+      <c r="B189" t="n">
+        <v>2600012494</v>
+      </c>
+      <c r="C189" t="n">
+        <v>300</v>
+      </c>
+      <c r="D189" t="n">
+        <v>600002123</v>
+      </c>
+      <c r="E189" s="1" t="n">
+        <v>46219.77955907407</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>3000550</v>
+      </c>
+      <c r="B190" t="n">
+        <v>2600004986</v>
+      </c>
+      <c r="C190" t="n">
+        <v>300</v>
+      </c>
+      <c r="D190" t="n">
+        <v>600002123</v>
+      </c>
+      <c r="E190" s="1" t="n">
+        <v>46219.77955907407</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>3000550</v>
+      </c>
+      <c r="B191" t="n">
+        <v>2600012581</v>
+      </c>
+      <c r="C191" t="n">
+        <v>300</v>
+      </c>
+      <c r="D191" t="n">
+        <v>600002123</v>
+      </c>
+      <c r="E191" s="1" t="n">
+        <v>46219.77955907407</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>3000550</v>
+      </c>
+      <c r="B192" t="n">
+        <v>2600004989</v>
+      </c>
+      <c r="C192" t="n">
+        <v>300</v>
+      </c>
+      <c r="D192" t="n">
+        <v>600002123</v>
+      </c>
+      <c r="E192" s="1" t="n">
+        <v>46219.77955907407</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>3000550</v>
+      </c>
+      <c r="B193" t="n">
+        <v>2600012492</v>
+      </c>
+      <c r="C193" t="n">
+        <v>300</v>
+      </c>
+      <c r="D193" t="n">
+        <v>600002123</v>
+      </c>
+      <c r="E193" s="1" t="n">
+        <v>46219.77955907407</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>3000550</v>
+      </c>
+      <c r="B194" t="n">
+        <v>2600004995</v>
+      </c>
+      <c r="C194" t="n">
+        <v>300</v>
+      </c>
+      <c r="D194" t="n">
+        <v>600002123</v>
+      </c>
+      <c r="E194" s="1" t="n">
+        <v>46219.77955907407</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>3000093</v>
+      </c>
+      <c r="B195" t="n">
+        <v>2600019667</v>
+      </c>
+      <c r="C195" t="n">
+        <v>300</v>
+      </c>
+      <c r="D195" t="n">
+        <v>600002123</v>
+      </c>
+      <c r="E195" s="1" t="n">
+        <v>46219.77955907407</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>3000486</v>
+      </c>
+      <c r="B196" t="n">
+        <v>2600020244</v>
+      </c>
+      <c r="C196" t="n">
+        <v>300</v>
+      </c>
+      <c r="D196" t="n">
+        <v>600002123</v>
+      </c>
+      <c r="E196" s="1" t="n">
+        <v>46219.77955907407</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>3000093</v>
+      </c>
+      <c r="B197" t="n">
+        <v>2600008079</v>
+      </c>
+      <c r="C197" t="n">
+        <v>300</v>
+      </c>
+      <c r="D197" t="n">
+        <v>600002123</v>
+      </c>
+      <c r="E197" s="1" t="n">
+        <v>46219.77955907407</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>3000537</v>
+      </c>
+      <c r="B198" t="n">
+        <v>2600014583</v>
+      </c>
+      <c r="C198" t="n">
+        <v>300</v>
+      </c>
+      <c r="D198" t="n">
+        <v>600002123</v>
+      </c>
+      <c r="E198" s="1" t="n">
+        <v>46219.77955907407</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>3000292</v>
+      </c>
+      <c r="B199" t="n">
+        <v>2600012774</v>
+      </c>
+      <c r="C199" t="n">
+        <v>300</v>
+      </c>
+      <c r="D199" t="n">
+        <v>600002123</v>
+      </c>
+      <c r="E199" s="1" t="n">
+        <v>46219.77955907407</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>3000537</v>
+      </c>
+      <c r="B200" t="n">
+        <v>2600012348</v>
+      </c>
+      <c r="C200" t="n">
+        <v>300</v>
+      </c>
+      <c r="D200" t="n">
+        <v>600002123</v>
+      </c>
+      <c r="E200" s="1" t="n">
+        <v>46219.77955907407</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>3000733</v>
+      </c>
+      <c r="B201" t="n">
+        <v>2600017894</v>
+      </c>
+      <c r="C201" t="n">
+        <v>300</v>
+      </c>
+      <c r="D201" t="n">
+        <v>600002123</v>
+      </c>
+      <c r="E201" s="1" t="n">
+        <v>46219.77955907407</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>4038837</v>
+      </c>
+      <c r="B202" t="inlineStr">
         <is>
-          <t>2600019803</t>
+          <t>2500043845</t>
         </is>
       </c>
-      <c r="C186" t="n">
-        <v>400</v>
-      </c>
-      <c r="D186" t="inlineStr">
+      <c r="C202" t="n">
+        <v>310</v>
+      </c>
+      <c r="D202" t="inlineStr">
         <is>
-          <t>600012400</t>
+          <t>600031067</t>
         </is>
       </c>
-      <c r="E186" s="1" t="n">
-        <v>46219.72766950409</v>
+      <c r="E202" s="1" t="n">
+        <v>46220.13574616074</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>4000689</v>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>2600020819</t>
+        </is>
+      </c>
+      <c r="C203" t="n">
+        <v>310</v>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>600031067</t>
+        </is>
+      </c>
+      <c r="E203" s="1" t="n">
+        <v>46220.13574616074</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>4009121</v>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>2600009846</t>
+        </is>
+      </c>
+      <c r="C204" t="n">
+        <v>310</v>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>600031067</t>
+        </is>
+      </c>
+      <c r="E204" s="1" t="n">
+        <v>46220.13574616074</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>4000194</v>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>2600017631</t>
+        </is>
+      </c>
+      <c r="C205" t="n">
+        <v>310</v>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>600031067</t>
+        </is>
+      </c>
+      <c r="E205" s="1" t="n">
+        <v>46220.13574616074</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>4000689</v>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>2600018163</t>
+        </is>
+      </c>
+      <c r="C206" t="n">
+        <v>310</v>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>600031067</t>
+        </is>
+      </c>
+      <c r="E206" s="1" t="n">
+        <v>46220.13574616074</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>4009121</v>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>2600016130</t>
+        </is>
+      </c>
+      <c r="C207" t="n">
+        <v>310</v>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>600031067</t>
+        </is>
+      </c>
+      <c r="E207" s="1" t="n">
+        <v>46220.13574616074</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>4000194</v>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>2600016030</t>
+        </is>
+      </c>
+      <c r="C208" t="n">
+        <v>310</v>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>600031067</t>
+        </is>
+      </c>
+      <c r="E208" s="1" t="n">
+        <v>46220.13574616074</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>4000194</v>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>2600010300</t>
+        </is>
+      </c>
+      <c r="C209" t="n">
+        <v>310</v>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>600031067</t>
+        </is>
+      </c>
+      <c r="E209" s="1" t="n">
+        <v>46220.13574616074</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>4000688</v>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>2600020945</t>
+        </is>
+      </c>
+      <c r="C210" t="n">
+        <v>310</v>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>600031067</t>
+        </is>
+      </c>
+      <c r="E210" s="1" t="n">
+        <v>46220.13574616074</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>4009121</v>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>2600005939</t>
+        </is>
+      </c>
+      <c r="C211" t="n">
+        <v>310</v>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>600031067</t>
+        </is>
+      </c>
+      <c r="E211" s="1" t="n">
+        <v>46220.13574616074</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>4000688</v>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>2600018239</t>
+        </is>
+      </c>
+      <c r="C212" t="n">
+        <v>310</v>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>600031067</t>
+        </is>
+      </c>
+      <c r="E212" s="1" t="n">
+        <v>46220.13574616074</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>4009062</v>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>2600013776</t>
+        </is>
+      </c>
+      <c r="C213" t="n">
+        <v>310</v>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>600031067</t>
+        </is>
+      </c>
+      <c r="E213" s="1" t="n">
+        <v>46220.13574616074</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>4000688</v>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>2600020621</t>
+        </is>
+      </c>
+      <c r="C214" t="n">
+        <v>310</v>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>600031067</t>
+        </is>
+      </c>
+      <c r="E214" s="1" t="n">
+        <v>46220.13574616074</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>4000194</v>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>2600016029</t>
+        </is>
+      </c>
+      <c r="C215" t="n">
+        <v>310</v>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>600031067</t>
+        </is>
+      </c>
+      <c r="E215" s="1" t="n">
+        <v>46220.13574616074</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>4021439</v>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>2600017475</t>
+        </is>
+      </c>
+      <c r="C216" t="n">
+        <v>310</v>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>600031067</t>
+        </is>
+      </c>
+      <c r="E216" s="1" t="n">
+        <v>46220.13574616074</v>
       </c>
     </row>
   </sheetData>

--- a/data/historico/historico_documentos.xlsx
+++ b/data/historico/historico_documentos.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E216"/>
+  <dimension ref="A1:E398"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3851,315 +3851,3523 @@
       <c r="A202" t="n">
         <v>4038837</v>
       </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>2500043845</t>
-        </is>
+      <c r="B202" t="n">
+        <v>2500043845</v>
       </c>
       <c r="C202" t="n">
         <v>310</v>
       </c>
-      <c r="D202" t="inlineStr">
-        <is>
-          <t>600031067</t>
-        </is>
+      <c r="D202" t="n">
+        <v>600031067</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46220.13574616074</v>
+        <v>46220.13574615741</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
         <v>4000689</v>
       </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>2600020819</t>
-        </is>
+      <c r="B203" t="n">
+        <v>2600020819</v>
       </c>
       <c r="C203" t="n">
         <v>310</v>
       </c>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>600031067</t>
-        </is>
+      <c r="D203" t="n">
+        <v>600031067</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46220.13574616074</v>
+        <v>46220.13574615741</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
         <v>4009121</v>
       </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>2600009846</t>
-        </is>
+      <c r="B204" t="n">
+        <v>2600009846</v>
       </c>
       <c r="C204" t="n">
         <v>310</v>
       </c>
-      <c r="D204" t="inlineStr">
-        <is>
-          <t>600031067</t>
-        </is>
+      <c r="D204" t="n">
+        <v>600031067</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46220.13574616074</v>
+        <v>46220.13574615741</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
         <v>4000194</v>
       </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>2600017631</t>
-        </is>
+      <c r="B205" t="n">
+        <v>2600017631</v>
       </c>
       <c r="C205" t="n">
         <v>310</v>
       </c>
-      <c r="D205" t="inlineStr">
-        <is>
-          <t>600031067</t>
-        </is>
+      <c r="D205" t="n">
+        <v>600031067</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46220.13574616074</v>
+        <v>46220.13574615741</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
         <v>4000689</v>
       </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>2600018163</t>
-        </is>
+      <c r="B206" t="n">
+        <v>2600018163</v>
       </c>
       <c r="C206" t="n">
         <v>310</v>
       </c>
-      <c r="D206" t="inlineStr">
-        <is>
-          <t>600031067</t>
-        </is>
+      <c r="D206" t="n">
+        <v>600031067</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46220.13574616074</v>
+        <v>46220.13574615741</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
         <v>4009121</v>
       </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>2600016130</t>
-        </is>
+      <c r="B207" t="n">
+        <v>2600016130</v>
       </c>
       <c r="C207" t="n">
         <v>310</v>
       </c>
-      <c r="D207" t="inlineStr">
-        <is>
-          <t>600031067</t>
-        </is>
+      <c r="D207" t="n">
+        <v>600031067</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46220.13574616074</v>
+        <v>46220.13574615741</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
         <v>4000194</v>
       </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>2600016030</t>
-        </is>
+      <c r="B208" t="n">
+        <v>2600016030</v>
       </c>
       <c r="C208" t="n">
         <v>310</v>
       </c>
-      <c r="D208" t="inlineStr">
-        <is>
-          <t>600031067</t>
-        </is>
+      <c r="D208" t="n">
+        <v>600031067</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46220.13574616074</v>
+        <v>46220.13574615741</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
         <v>4000194</v>
       </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>2600010300</t>
-        </is>
+      <c r="B209" t="n">
+        <v>2600010300</v>
       </c>
       <c r="C209" t="n">
         <v>310</v>
       </c>
-      <c r="D209" t="inlineStr">
-        <is>
-          <t>600031067</t>
-        </is>
+      <c r="D209" t="n">
+        <v>600031067</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46220.13574616074</v>
+        <v>46220.13574615741</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
         <v>4000688</v>
       </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>2600020945</t>
-        </is>
+      <c r="B210" t="n">
+        <v>2600020945</v>
       </c>
       <c r="C210" t="n">
         <v>310</v>
       </c>
-      <c r="D210" t="inlineStr">
-        <is>
-          <t>600031067</t>
-        </is>
+      <c r="D210" t="n">
+        <v>600031067</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46220.13574616074</v>
+        <v>46220.13574615741</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
         <v>4009121</v>
       </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>2600005939</t>
-        </is>
+      <c r="B211" t="n">
+        <v>2600005939</v>
       </c>
       <c r="C211" t="n">
         <v>310</v>
       </c>
-      <c r="D211" t="inlineStr">
-        <is>
-          <t>600031067</t>
-        </is>
+      <c r="D211" t="n">
+        <v>600031067</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46220.13574616074</v>
+        <v>46220.13574615741</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
         <v>4000688</v>
       </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>2600018239</t>
-        </is>
+      <c r="B212" t="n">
+        <v>2600018239</v>
       </c>
       <c r="C212" t="n">
         <v>310</v>
       </c>
-      <c r="D212" t="inlineStr">
-        <is>
-          <t>600031067</t>
-        </is>
+      <c r="D212" t="n">
+        <v>600031067</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46220.13574616074</v>
+        <v>46220.13574615741</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
         <v>4009062</v>
       </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>2600013776</t>
-        </is>
+      <c r="B213" t="n">
+        <v>2600013776</v>
       </c>
       <c r="C213" t="n">
         <v>310</v>
       </c>
-      <c r="D213" t="inlineStr">
-        <is>
-          <t>600031067</t>
-        </is>
+      <c r="D213" t="n">
+        <v>600031067</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46220.13574616074</v>
+        <v>46220.13574615741</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
         <v>4000688</v>
       </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>2600020621</t>
-        </is>
+      <c r="B214" t="n">
+        <v>2600020621</v>
       </c>
       <c r="C214" t="n">
         <v>310</v>
       </c>
-      <c r="D214" t="inlineStr">
-        <is>
-          <t>600031067</t>
-        </is>
+      <c r="D214" t="n">
+        <v>600031067</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46220.13574616074</v>
+        <v>46220.13574615741</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
         <v>4000194</v>
       </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>2600016029</t>
-        </is>
+      <c r="B215" t="n">
+        <v>2600016029</v>
       </c>
       <c r="C215" t="n">
         <v>310</v>
       </c>
-      <c r="D215" t="inlineStr">
-        <is>
-          <t>600031067</t>
-        </is>
+      <c r="D215" t="n">
+        <v>600031067</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46220.13574616074</v>
+        <v>46220.13574615741</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
         <v>4021439</v>
       </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>2600017475</t>
-        </is>
+      <c r="B216" t="n">
+        <v>2600017475</v>
       </c>
       <c r="C216" t="n">
         <v>310</v>
       </c>
-      <c r="D216" t="inlineStr">
-        <is>
-          <t>600031067</t>
-        </is>
+      <c r="D216" t="n">
+        <v>600031067</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46220.13574616074</v>
+        <v>46220.13574615741</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>4022441</v>
+      </c>
+      <c r="B217" t="n">
+        <v>2600016997</v>
+      </c>
+      <c r="C217" t="n">
+        <v>310</v>
+      </c>
+      <c r="D217" t="n">
+        <v>35346</v>
+      </c>
+      <c r="E217" s="1" t="n">
+        <v>46223.63135921297</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>4020495</v>
+      </c>
+      <c r="B218" t="n">
+        <v>2600019215</v>
+      </c>
+      <c r="C218" t="n">
+        <v>310</v>
+      </c>
+      <c r="D218" t="n">
+        <v>35346</v>
+      </c>
+      <c r="E218" s="1" t="n">
+        <v>46223.63135921297</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>4020495</v>
+      </c>
+      <c r="B219" t="n">
+        <v>2600015553</v>
+      </c>
+      <c r="C219" t="n">
+        <v>310</v>
+      </c>
+      <c r="D219" t="n">
+        <v>35346</v>
+      </c>
+      <c r="E219" s="1" t="n">
+        <v>46223.63135921297</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>4018940</v>
+      </c>
+      <c r="B220" t="n">
+        <v>2600004645</v>
+      </c>
+      <c r="C220" t="n">
+        <v>310</v>
+      </c>
+      <c r="D220" t="n">
+        <v>35346</v>
+      </c>
+      <c r="E220" s="1" t="n">
+        <v>46223.63135921297</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>4018380</v>
+      </c>
+      <c r="B221" t="n">
+        <v>2500029308</v>
+      </c>
+      <c r="C221" t="n">
+        <v>310</v>
+      </c>
+      <c r="D221" t="n">
+        <v>35346</v>
+      </c>
+      <c r="E221" s="1" t="n">
+        <v>46223.63135921297</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>4022190</v>
+      </c>
+      <c r="B222" t="n">
+        <v>2600011519</v>
+      </c>
+      <c r="C222" t="n">
+        <v>310</v>
+      </c>
+      <c r="D222" t="n">
+        <v>35346</v>
+      </c>
+      <c r="E222" s="1" t="n">
+        <v>46223.63135921297</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>4018784</v>
+      </c>
+      <c r="B223" t="n">
+        <v>2600017568</v>
+      </c>
+      <c r="C223" t="n">
+        <v>310</v>
+      </c>
+      <c r="D223" t="n">
+        <v>35346</v>
+      </c>
+      <c r="E223" s="1" t="n">
+        <v>46223.63135921297</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>4018940</v>
+      </c>
+      <c r="B224" t="n">
+        <v>2600019424</v>
+      </c>
+      <c r="C224" t="n">
+        <v>310</v>
+      </c>
+      <c r="D224" t="n">
+        <v>35346</v>
+      </c>
+      <c r="E224" s="1" t="n">
+        <v>46223.63135921297</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>4018388</v>
+      </c>
+      <c r="B225" t="n">
+        <v>2600008281</v>
+      </c>
+      <c r="C225" t="n">
+        <v>310</v>
+      </c>
+      <c r="D225" t="n">
+        <v>35346</v>
+      </c>
+      <c r="E225" s="1" t="n">
+        <v>46223.63135921297</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>4015026</v>
+      </c>
+      <c r="B226" t="n">
+        <v>2600018286</v>
+      </c>
+      <c r="C226" t="n">
+        <v>310</v>
+      </c>
+      <c r="D226" t="n">
+        <v>35346</v>
+      </c>
+      <c r="E226" s="1" t="n">
+        <v>46223.63135921297</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>4020141</v>
+      </c>
+      <c r="B227" t="n">
+        <v>2600015024</v>
+      </c>
+      <c r="C227" t="n">
+        <v>310</v>
+      </c>
+      <c r="D227" t="n">
+        <v>35346</v>
+      </c>
+      <c r="E227" s="1" t="n">
+        <v>46223.63135921297</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>4015026</v>
+      </c>
+      <c r="B228" t="n">
+        <v>2600018287</v>
+      </c>
+      <c r="C228" t="n">
+        <v>310</v>
+      </c>
+      <c r="D228" t="n">
+        <v>35346</v>
+      </c>
+      <c r="E228" s="1" t="n">
+        <v>46223.63135921297</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>4022441</v>
+      </c>
+      <c r="B229" t="n">
+        <v>2600010688</v>
+      </c>
+      <c r="C229" t="n">
+        <v>310</v>
+      </c>
+      <c r="D229" t="n">
+        <v>35346</v>
+      </c>
+      <c r="E229" s="1" t="n">
+        <v>46223.63135921297</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>4000689</v>
+      </c>
+      <c r="B230" t="n">
+        <v>2600020819</v>
+      </c>
+      <c r="C230" t="n">
+        <v>310</v>
+      </c>
+      <c r="D230" t="n">
+        <v>35346</v>
+      </c>
+      <c r="E230" s="1" t="n">
+        <v>46223.63135921297</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>4000689</v>
+      </c>
+      <c r="B231" t="n">
+        <v>2600018163</v>
+      </c>
+      <c r="C231" t="n">
+        <v>310</v>
+      </c>
+      <c r="D231" t="n">
+        <v>35346</v>
+      </c>
+      <c r="E231" s="1" t="n">
+        <v>46223.63135921297</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>4000689</v>
+      </c>
+      <c r="B232" t="n">
+        <v>2600020770</v>
+      </c>
+      <c r="C232" t="n">
+        <v>310</v>
+      </c>
+      <c r="D232" t="n">
+        <v>35346</v>
+      </c>
+      <c r="E232" s="1" t="n">
+        <v>46223.63135921297</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>4000194</v>
+      </c>
+      <c r="B233" t="n">
+        <v>2600010300</v>
+      </c>
+      <c r="C233" t="n">
+        <v>310</v>
+      </c>
+      <c r="D233" t="n">
+        <v>35346</v>
+      </c>
+      <c r="E233" s="1" t="n">
+        <v>46223.63135921297</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>4000231</v>
+      </c>
+      <c r="B234" t="n">
+        <v>2600020446</v>
+      </c>
+      <c r="C234" t="n">
+        <v>310</v>
+      </c>
+      <c r="D234" t="n">
+        <v>35346</v>
+      </c>
+      <c r="E234" s="1" t="n">
+        <v>46223.63135921297</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>4006022</v>
+      </c>
+      <c r="B235" t="n">
+        <v>2600020784</v>
+      </c>
+      <c r="C235" t="n">
+        <v>310</v>
+      </c>
+      <c r="D235" t="n">
+        <v>35346</v>
+      </c>
+      <c r="E235" s="1" t="n">
+        <v>46223.63135921297</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>4009062</v>
+      </c>
+      <c r="B236" t="n">
+        <v>2600009844</v>
+      </c>
+      <c r="C236" t="n">
+        <v>310</v>
+      </c>
+      <c r="D236" t="n">
+        <v>35346</v>
+      </c>
+      <c r="E236" s="1" t="n">
+        <v>46223.63135921297</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>4000688</v>
+      </c>
+      <c r="B237" t="n">
+        <v>2600020945</v>
+      </c>
+      <c r="C237" t="n">
+        <v>310</v>
+      </c>
+      <c r="D237" t="n">
+        <v>35346</v>
+      </c>
+      <c r="E237" s="1" t="n">
+        <v>46223.63135921297</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>4013457</v>
+      </c>
+      <c r="B238" t="n">
+        <v>2600013728</v>
+      </c>
+      <c r="C238" t="n">
+        <v>310</v>
+      </c>
+      <c r="D238" t="n">
+        <v>35346</v>
+      </c>
+      <c r="E238" s="1" t="n">
+        <v>46223.63135921297</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>4023137</v>
+      </c>
+      <c r="B239" t="n">
+        <v>2600010468</v>
+      </c>
+      <c r="C239" t="n">
+        <v>310</v>
+      </c>
+      <c r="D239" t="n">
+        <v>35346</v>
+      </c>
+      <c r="E239" s="1" t="n">
+        <v>46223.63135921297</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>4001552</v>
+      </c>
+      <c r="B240" t="n">
+        <v>2600020439</v>
+      </c>
+      <c r="C240" t="n">
+        <v>310</v>
+      </c>
+      <c r="D240" t="n">
+        <v>35346</v>
+      </c>
+      <c r="E240" s="1" t="n">
+        <v>46223.63135921297</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>4001395</v>
+      </c>
+      <c r="B241" t="n">
+        <v>2600016470</v>
+      </c>
+      <c r="C241" t="n">
+        <v>310</v>
+      </c>
+      <c r="D241" t="n">
+        <v>35346</v>
+      </c>
+      <c r="E241" s="1" t="n">
+        <v>46223.63135921297</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>4000312</v>
+      </c>
+      <c r="B242" t="n">
+        <v>2600017353</v>
+      </c>
+      <c r="C242" t="n">
+        <v>310</v>
+      </c>
+      <c r="D242" t="n">
+        <v>35346</v>
+      </c>
+      <c r="E242" s="1" t="n">
+        <v>46223.63135921297</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>4000688</v>
+      </c>
+      <c r="B243" t="n">
+        <v>2600020621</v>
+      </c>
+      <c r="C243" t="n">
+        <v>310</v>
+      </c>
+      <c r="D243" t="n">
+        <v>35346</v>
+      </c>
+      <c r="E243" s="1" t="n">
+        <v>46223.63135921297</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>4001395</v>
+      </c>
+      <c r="B244" t="n">
+        <v>2600012761</v>
+      </c>
+      <c r="C244" t="n">
+        <v>310</v>
+      </c>
+      <c r="D244" t="n">
+        <v>35346</v>
+      </c>
+      <c r="E244" s="1" t="n">
+        <v>46223.63135921297</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>4017193</v>
+      </c>
+      <c r="B245" t="n">
+        <v>2600019636</v>
+      </c>
+      <c r="C245" t="n">
+        <v>310</v>
+      </c>
+      <c r="D245" t="n">
+        <v>35346</v>
+      </c>
+      <c r="E245" s="1" t="n">
+        <v>46223.63135921297</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>4000310</v>
+      </c>
+      <c r="B246" t="n">
+        <v>2600012968</v>
+      </c>
+      <c r="C246" t="n">
+        <v>310</v>
+      </c>
+      <c r="D246" t="n">
+        <v>35346</v>
+      </c>
+      <c r="E246" s="1" t="n">
+        <v>46223.63135921297</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>4009062</v>
+      </c>
+      <c r="B247" t="n">
+        <v>2600020947</v>
+      </c>
+      <c r="C247" t="n">
+        <v>310</v>
+      </c>
+      <c r="D247" t="n">
+        <v>35346</v>
+      </c>
+      <c r="E247" s="1" t="n">
+        <v>46223.63135921297</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>4001552</v>
+      </c>
+      <c r="B248" t="n">
+        <v>2600020441</v>
+      </c>
+      <c r="C248" t="n">
+        <v>310</v>
+      </c>
+      <c r="D248" t="n">
+        <v>35346</v>
+      </c>
+      <c r="E248" s="1" t="n">
+        <v>46223.63135921297</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>4001395</v>
+      </c>
+      <c r="B249" t="n">
+        <v>2600005145</v>
+      </c>
+      <c r="C249" t="n">
+        <v>310</v>
+      </c>
+      <c r="D249" t="n">
+        <v>35346</v>
+      </c>
+      <c r="E249" s="1" t="n">
+        <v>46223.63135921297</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>4021439</v>
+      </c>
+      <c r="B250" t="n">
+        <v>2600020948</v>
+      </c>
+      <c r="C250" t="n">
+        <v>310</v>
+      </c>
+      <c r="D250" t="n">
+        <v>35346</v>
+      </c>
+      <c r="E250" s="1" t="n">
+        <v>46223.63135921297</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>4020514</v>
+      </c>
+      <c r="B251" t="n">
+        <v>2600019429</v>
+      </c>
+      <c r="C251" t="n">
+        <v>310</v>
+      </c>
+      <c r="D251" t="n">
+        <v>35346</v>
+      </c>
+      <c r="E251" s="1" t="n">
+        <v>46223.63135921297</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>4000194</v>
+      </c>
+      <c r="B252" t="n">
+        <v>2600008215</v>
+      </c>
+      <c r="C252" t="n">
+        <v>310</v>
+      </c>
+      <c r="D252" t="n">
+        <v>35346</v>
+      </c>
+      <c r="E252" s="1" t="n">
+        <v>46223.63135921297</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>4021440</v>
+      </c>
+      <c r="B253" t="n">
+        <v>2600020946</v>
+      </c>
+      <c r="C253" t="n">
+        <v>310</v>
+      </c>
+      <c r="D253" t="n">
+        <v>35346</v>
+      </c>
+      <c r="E253" s="1" t="n">
+        <v>46223.63135921297</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>4017193</v>
+      </c>
+      <c r="B254" t="n">
+        <v>2600008794</v>
+      </c>
+      <c r="C254" t="n">
+        <v>310</v>
+      </c>
+      <c r="D254" t="n">
+        <v>35346</v>
+      </c>
+      <c r="E254" s="1" t="n">
+        <v>46223.63135921297</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>4000312</v>
+      </c>
+      <c r="B255" t="n">
+        <v>2600013428</v>
+      </c>
+      <c r="C255" t="n">
+        <v>310</v>
+      </c>
+      <c r="D255" t="n">
+        <v>35346</v>
+      </c>
+      <c r="E255" s="1" t="n">
+        <v>46223.63135921297</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>4000312</v>
+      </c>
+      <c r="B256" t="n">
+        <v>2600013649</v>
+      </c>
+      <c r="C256" t="n">
+        <v>310</v>
+      </c>
+      <c r="D256" t="n">
+        <v>35346</v>
+      </c>
+      <c r="E256" s="1" t="n">
+        <v>46223.63135921297</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>4000310</v>
+      </c>
+      <c r="B257" t="n">
+        <v>2600017434</v>
+      </c>
+      <c r="C257" t="n">
+        <v>310</v>
+      </c>
+      <c r="D257" t="n">
+        <v>35346</v>
+      </c>
+      <c r="E257" s="1" t="n">
+        <v>46223.63135921297</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>4017193</v>
+      </c>
+      <c r="B258" t="n">
+        <v>2600018765</v>
+      </c>
+      <c r="C258" t="n">
+        <v>310</v>
+      </c>
+      <c r="D258" t="n">
+        <v>35346</v>
+      </c>
+      <c r="E258" s="1" t="n">
+        <v>46223.63135921297</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>4001494</v>
+      </c>
+      <c r="B259" t="n">
+        <v>2600018758</v>
+      </c>
+      <c r="C259" t="n">
+        <v>310</v>
+      </c>
+      <c r="D259" t="n">
+        <v>35346</v>
+      </c>
+      <c r="E259" s="1" t="n">
+        <v>46223.63135921297</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>3000366</v>
+      </c>
+      <c r="B260" t="n">
+        <v>2600018162</v>
+      </c>
+      <c r="C260" t="n">
+        <v>300</v>
+      </c>
+      <c r="D260" t="n">
+        <v>6342324</v>
+      </c>
+      <c r="E260" s="1" t="n">
+        <v>46224.58327586806</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>3000366</v>
+      </c>
+      <c r="B261" t="n">
+        <v>2600015715</v>
+      </c>
+      <c r="C261" t="n">
+        <v>300</v>
+      </c>
+      <c r="D261" t="n">
+        <v>6342324</v>
+      </c>
+      <c r="E261" s="1" t="n">
+        <v>46224.58327586806</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>3000550</v>
+      </c>
+      <c r="B262" t="n">
+        <v>2600012494</v>
+      </c>
+      <c r="C262" t="n">
+        <v>300</v>
+      </c>
+      <c r="D262" t="n">
+        <v>6342324</v>
+      </c>
+      <c r="E262" s="1" t="n">
+        <v>46224.58327586806</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
+        <v>3000550</v>
+      </c>
+      <c r="B263" t="n">
+        <v>2600004986</v>
+      </c>
+      <c r="C263" t="n">
+        <v>300</v>
+      </c>
+      <c r="D263" t="n">
+        <v>6342324</v>
+      </c>
+      <c r="E263" s="1" t="n">
+        <v>46224.58327586806</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="n">
+        <v>3000550</v>
+      </c>
+      <c r="B264" t="n">
+        <v>2600012581</v>
+      </c>
+      <c r="C264" t="n">
+        <v>300</v>
+      </c>
+      <c r="D264" t="n">
+        <v>6342324</v>
+      </c>
+      <c r="E264" s="1" t="n">
+        <v>46224.58327586806</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="n">
+        <v>3000550</v>
+      </c>
+      <c r="B265" t="n">
+        <v>2600004989</v>
+      </c>
+      <c r="C265" t="n">
+        <v>300</v>
+      </c>
+      <c r="D265" t="n">
+        <v>6342324</v>
+      </c>
+      <c r="E265" s="1" t="n">
+        <v>46224.58327586806</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="n">
+        <v>3000550</v>
+      </c>
+      <c r="B266" t="n">
+        <v>2600012492</v>
+      </c>
+      <c r="C266" t="n">
+        <v>300</v>
+      </c>
+      <c r="D266" t="n">
+        <v>6342324</v>
+      </c>
+      <c r="E266" s="1" t="n">
+        <v>46224.58327586806</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="n">
+        <v>3000550</v>
+      </c>
+      <c r="B267" t="n">
+        <v>2600004995</v>
+      </c>
+      <c r="C267" t="n">
+        <v>300</v>
+      </c>
+      <c r="D267" t="n">
+        <v>6342324</v>
+      </c>
+      <c r="E267" s="1" t="n">
+        <v>46224.58327586806</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="n">
+        <v>3000093</v>
+      </c>
+      <c r="B268" t="n">
+        <v>2600019667</v>
+      </c>
+      <c r="C268" t="n">
+        <v>300</v>
+      </c>
+      <c r="D268" t="n">
+        <v>6342324</v>
+      </c>
+      <c r="E268" s="1" t="n">
+        <v>46224.58327586806</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="n">
+        <v>3000486</v>
+      </c>
+      <c r="B269" t="n">
+        <v>2600020244</v>
+      </c>
+      <c r="C269" t="n">
+        <v>300</v>
+      </c>
+      <c r="D269" t="n">
+        <v>6342324</v>
+      </c>
+      <c r="E269" s="1" t="n">
+        <v>46224.58327586806</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="n">
+        <v>3000093</v>
+      </c>
+      <c r="B270" t="n">
+        <v>2600008079</v>
+      </c>
+      <c r="C270" t="n">
+        <v>300</v>
+      </c>
+      <c r="D270" t="n">
+        <v>6342324</v>
+      </c>
+      <c r="E270" s="1" t="n">
+        <v>46224.58327586806</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="n">
+        <v>3000537</v>
+      </c>
+      <c r="B271" t="n">
+        <v>2600014583</v>
+      </c>
+      <c r="C271" t="n">
+        <v>300</v>
+      </c>
+      <c r="D271" t="n">
+        <v>6342324</v>
+      </c>
+      <c r="E271" s="1" t="n">
+        <v>46224.58327586806</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="n">
+        <v>3000292</v>
+      </c>
+      <c r="B272" t="n">
+        <v>2600012774</v>
+      </c>
+      <c r="C272" t="n">
+        <v>300</v>
+      </c>
+      <c r="D272" t="n">
+        <v>6342324</v>
+      </c>
+      <c r="E272" s="1" t="n">
+        <v>46224.58327586806</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="n">
+        <v>3000537</v>
+      </c>
+      <c r="B273" t="n">
+        <v>2600012348</v>
+      </c>
+      <c r="C273" t="n">
+        <v>300</v>
+      </c>
+      <c r="D273" t="n">
+        <v>6342324</v>
+      </c>
+      <c r="E273" s="1" t="n">
+        <v>46224.58327586806</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="n">
+        <v>3000733</v>
+      </c>
+      <c r="B274" t="n">
+        <v>2600017894</v>
+      </c>
+      <c r="C274" t="n">
+        <v>300</v>
+      </c>
+      <c r="D274" t="n">
+        <v>6342324</v>
+      </c>
+      <c r="E274" s="1" t="n">
+        <v>46224.58327586806</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="n">
+        <v>4038837</v>
+      </c>
+      <c r="B275" t="n">
+        <v>2500043845</v>
+      </c>
+      <c r="C275" t="n">
+        <v>310</v>
+      </c>
+      <c r="D275" t="n">
+        <v>612345688</v>
+      </c>
+      <c r="E275" s="1" t="n">
+        <v>46224.66405245371</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="n">
+        <v>4000689</v>
+      </c>
+      <c r="B276" t="n">
+        <v>2600020819</v>
+      </c>
+      <c r="C276" t="n">
+        <v>310</v>
+      </c>
+      <c r="D276" t="n">
+        <v>612345688</v>
+      </c>
+      <c r="E276" s="1" t="n">
+        <v>46224.66405245371</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="n">
+        <v>4009121</v>
+      </c>
+      <c r="B277" t="n">
+        <v>2600009846</v>
+      </c>
+      <c r="C277" t="n">
+        <v>310</v>
+      </c>
+      <c r="D277" t="n">
+        <v>612345688</v>
+      </c>
+      <c r="E277" s="1" t="n">
+        <v>46224.66405245371</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="n">
+        <v>4000194</v>
+      </c>
+      <c r="B278" t="n">
+        <v>2600017631</v>
+      </c>
+      <c r="C278" t="n">
+        <v>310</v>
+      </c>
+      <c r="D278" t="n">
+        <v>612345688</v>
+      </c>
+      <c r="E278" s="1" t="n">
+        <v>46224.66405245371</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="n">
+        <v>4000689</v>
+      </c>
+      <c r="B279" t="n">
+        <v>2600018163</v>
+      </c>
+      <c r="C279" t="n">
+        <v>310</v>
+      </c>
+      <c r="D279" t="n">
+        <v>612345688</v>
+      </c>
+      <c r="E279" s="1" t="n">
+        <v>46224.66405245371</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="n">
+        <v>4009121</v>
+      </c>
+      <c r="B280" t="n">
+        <v>2600016130</v>
+      </c>
+      <c r="C280" t="n">
+        <v>310</v>
+      </c>
+      <c r="D280" t="n">
+        <v>612345688</v>
+      </c>
+      <c r="E280" s="1" t="n">
+        <v>46224.66405245371</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="n">
+        <v>4000194</v>
+      </c>
+      <c r="B281" t="n">
+        <v>2600016030</v>
+      </c>
+      <c r="C281" t="n">
+        <v>310</v>
+      </c>
+      <c r="D281" t="n">
+        <v>612345688</v>
+      </c>
+      <c r="E281" s="1" t="n">
+        <v>46224.66405245371</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="n">
+        <v>4000194</v>
+      </c>
+      <c r="B282" t="n">
+        <v>2600010300</v>
+      </c>
+      <c r="C282" t="n">
+        <v>310</v>
+      </c>
+      <c r="D282" t="n">
+        <v>612345688</v>
+      </c>
+      <c r="E282" s="1" t="n">
+        <v>46224.66405245371</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="n">
+        <v>4000688</v>
+      </c>
+      <c r="B283" t="n">
+        <v>2600020945</v>
+      </c>
+      <c r="C283" t="n">
+        <v>310</v>
+      </c>
+      <c r="D283" t="n">
+        <v>612345688</v>
+      </c>
+      <c r="E283" s="1" t="n">
+        <v>46224.66405245371</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="n">
+        <v>4009121</v>
+      </c>
+      <c r="B284" t="n">
+        <v>2600005939</v>
+      </c>
+      <c r="C284" t="n">
+        <v>310</v>
+      </c>
+      <c r="D284" t="n">
+        <v>612345688</v>
+      </c>
+      <c r="E284" s="1" t="n">
+        <v>46224.66405245371</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="n">
+        <v>4000688</v>
+      </c>
+      <c r="B285" t="n">
+        <v>2600018239</v>
+      </c>
+      <c r="C285" t="n">
+        <v>310</v>
+      </c>
+      <c r="D285" t="n">
+        <v>612345688</v>
+      </c>
+      <c r="E285" s="1" t="n">
+        <v>46224.66405245371</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="n">
+        <v>4009062</v>
+      </c>
+      <c r="B286" t="n">
+        <v>2600013776</v>
+      </c>
+      <c r="C286" t="n">
+        <v>310</v>
+      </c>
+      <c r="D286" t="n">
+        <v>612345688</v>
+      </c>
+      <c r="E286" s="1" t="n">
+        <v>46224.66405245371</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="n">
+        <v>4000688</v>
+      </c>
+      <c r="B287" t="n">
+        <v>2600020621</v>
+      </c>
+      <c r="C287" t="n">
+        <v>310</v>
+      </c>
+      <c r="D287" t="n">
+        <v>612345688</v>
+      </c>
+      <c r="E287" s="1" t="n">
+        <v>46224.66405245371</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="n">
+        <v>4000194</v>
+      </c>
+      <c r="B288" t="n">
+        <v>2600016029</v>
+      </c>
+      <c r="C288" t="n">
+        <v>310</v>
+      </c>
+      <c r="D288" t="n">
+        <v>612345688</v>
+      </c>
+      <c r="E288" s="1" t="n">
+        <v>46224.66405245371</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="n">
+        <v>4021439</v>
+      </c>
+      <c r="B289" t="n">
+        <v>2600017475</v>
+      </c>
+      <c r="C289" t="n">
+        <v>310</v>
+      </c>
+      <c r="D289" t="n">
+        <v>612345688</v>
+      </c>
+      <c r="E289" s="1" t="n">
+        <v>46224.66405245371</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="n">
+        <v>3000021</v>
+      </c>
+      <c r="B290" t="n">
+        <v>2600008300</v>
+      </c>
+      <c r="C290" t="n">
+        <v>300</v>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="E290" s="1" t="n">
+        <v>46224.68011892361</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="n">
+        <v>2004583</v>
+      </c>
+      <c r="B291" t="n">
+        <v>2624906</v>
+      </c>
+      <c r="C291" t="n">
+        <v>300</v>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="E291" s="1" t="n">
+        <v>46224.68011892361</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="n">
+        <v>2000182</v>
+      </c>
+      <c r="B292" t="n">
+        <v>2624910</v>
+      </c>
+      <c r="C292" t="n">
+        <v>300</v>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="E292" s="1" t="n">
+        <v>46224.68011892361</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="n">
+        <v>2003659</v>
+      </c>
+      <c r="B293" t="n">
+        <v>2625968</v>
+      </c>
+      <c r="C293" t="n">
+        <v>300</v>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="E293" s="1" t="n">
+        <v>46224.68011892361</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="n">
+        <v>2000081</v>
+      </c>
+      <c r="B294" t="n">
+        <v>2617402</v>
+      </c>
+      <c r="C294" t="n">
+        <v>300</v>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="E294" s="1" t="n">
+        <v>46224.68011892361</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="n">
+        <v>2000081</v>
+      </c>
+      <c r="B295" t="n">
+        <v>2617406</v>
+      </c>
+      <c r="C295" t="n">
+        <v>300</v>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="E295" s="1" t="n">
+        <v>46224.68011892361</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="n">
+        <v>2000162</v>
+      </c>
+      <c r="B296" t="n">
+        <v>2625505</v>
+      </c>
+      <c r="C296" t="n">
+        <v>300</v>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="E296" s="1" t="n">
+        <v>46224.68011892361</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="n">
+        <v>2004217</v>
+      </c>
+      <c r="B297" t="n">
+        <v>2622168</v>
+      </c>
+      <c r="C297" t="n">
+        <v>300</v>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="E297" s="1" t="n">
+        <v>46224.68011892361</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="n">
+        <v>2003758</v>
+      </c>
+      <c r="B298" t="n">
+        <v>2618560</v>
+      </c>
+      <c r="C298" t="n">
+        <v>300</v>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="E298" s="1" t="n">
+        <v>46224.68011892361</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="n">
+        <v>3000043</v>
+      </c>
+      <c r="B299" t="n">
+        <v>2600017675</v>
+      </c>
+      <c r="C299" t="n">
+        <v>300</v>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="E299" s="1" t="n">
+        <v>46224.68011892361</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="n">
+        <v>3000043</v>
+      </c>
+      <c r="B300" t="n">
+        <v>2600011703</v>
+      </c>
+      <c r="C300" t="n">
+        <v>300</v>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="E300" s="1" t="n">
+        <v>46224.68011892361</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="n">
+        <v>3000040</v>
+      </c>
+      <c r="B301" t="n">
+        <v>2600012503</v>
+      </c>
+      <c r="C301" t="n">
+        <v>300</v>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="E301" s="1" t="n">
+        <v>46224.68011892361</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="n">
+        <v>3000024</v>
+      </c>
+      <c r="B302" t="n">
+        <v>2600017561</v>
+      </c>
+      <c r="C302" t="n">
+        <v>300</v>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="E302" s="1" t="n">
+        <v>46224.68011892361</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="n">
+        <v>3000024</v>
+      </c>
+      <c r="B303" t="n">
+        <v>2600017563</v>
+      </c>
+      <c r="C303" t="n">
+        <v>300</v>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="E303" s="1" t="n">
+        <v>46224.68011892361</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="n">
+        <v>3000078</v>
+      </c>
+      <c r="B304" t="n">
+        <v>2600017539</v>
+      </c>
+      <c r="C304" t="n">
+        <v>300</v>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="E304" s="1" t="n">
+        <v>46224.68011892361</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="n">
+        <v>3000068</v>
+      </c>
+      <c r="B305" t="n">
+        <v>2600020662</v>
+      </c>
+      <c r="C305" t="n">
+        <v>300</v>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="E305" s="1" t="n">
+        <v>46224.68011892361</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="n">
+        <v>3000093</v>
+      </c>
+      <c r="B306" t="n">
+        <v>2600019667</v>
+      </c>
+      <c r="C306" t="n">
+        <v>300</v>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="E306" s="1" t="n">
+        <v>46224.68011892361</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="n">
+        <v>3000040</v>
+      </c>
+      <c r="B307" t="n">
+        <v>2600009308</v>
+      </c>
+      <c r="C307" t="n">
+        <v>300</v>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="E307" s="1" t="n">
+        <v>46224.68011892361</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="n">
+        <v>3000027</v>
+      </c>
+      <c r="B308" t="n">
+        <v>2600017523</v>
+      </c>
+      <c r="C308" t="n">
+        <v>300</v>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="E308" s="1" t="n">
+        <v>46224.68011892361</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="n">
+        <v>3000043</v>
+      </c>
+      <c r="B309" t="n">
+        <v>2600017674</v>
+      </c>
+      <c r="C309" t="n">
+        <v>300</v>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="E309" s="1" t="n">
+        <v>46224.68011892361</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="n">
+        <v>3000037</v>
+      </c>
+      <c r="B310" t="n">
+        <v>2600016291</v>
+      </c>
+      <c r="C310" t="n">
+        <v>300</v>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="E310" s="1" t="n">
+        <v>46224.68011892361</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="n">
+        <v>3000027</v>
+      </c>
+      <c r="B311" t="n">
+        <v>2600020426</v>
+      </c>
+      <c r="C311" t="n">
+        <v>300</v>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="E311" s="1" t="n">
+        <v>46224.68011892361</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="n">
+        <v>3000093</v>
+      </c>
+      <c r="B312" t="n">
+        <v>2600008079</v>
+      </c>
+      <c r="C312" t="n">
+        <v>300</v>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="E312" s="1" t="n">
+        <v>46224.68011892361</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="n">
+        <v>3000066</v>
+      </c>
+      <c r="B313" t="n">
+        <v>2600012787</v>
+      </c>
+      <c r="C313" t="n">
+        <v>300</v>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="E313" s="1" t="n">
+        <v>46224.68011892361</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="n">
+        <v>3000037</v>
+      </c>
+      <c r="B314" t="n">
+        <v>2600019509</v>
+      </c>
+      <c r="C314" t="n">
+        <v>300</v>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="E314" s="1" t="n">
+        <v>46224.68011892361</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="n">
+        <v>3000129</v>
+      </c>
+      <c r="B315" t="n">
+        <v>2600018626</v>
+      </c>
+      <c r="C315" t="n">
+        <v>300</v>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="E315" s="1" t="n">
+        <v>46224.68011892361</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="n">
+        <v>2003758</v>
+      </c>
+      <c r="B316" t="n">
+        <v>2624076</v>
+      </c>
+      <c r="C316" t="n">
+        <v>300</v>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="E316" s="1" t="n">
+        <v>46224.68011892361</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="n">
+        <v>2003717</v>
+      </c>
+      <c r="B317" t="n">
+        <v>2623720</v>
+      </c>
+      <c r="C317" t="n">
+        <v>300</v>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="E317" s="1" t="n">
+        <v>46224.68011892361</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="n">
+        <v>3000055</v>
+      </c>
+      <c r="B318" t="n">
+        <v>2600019511</v>
+      </c>
+      <c r="C318" t="n">
+        <v>300</v>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="E318" s="1" t="n">
+        <v>46224.68011892361</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="n">
+        <v>3000060</v>
+      </c>
+      <c r="B319" t="n">
+        <v>2600019119</v>
+      </c>
+      <c r="C319" t="n">
+        <v>300</v>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="E319" s="1" t="n">
+        <v>46224.68011892361</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="n">
+        <v>3000055</v>
+      </c>
+      <c r="B320" t="n">
+        <v>2600019456</v>
+      </c>
+      <c r="C320" t="n">
+        <v>300</v>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="E320" s="1" t="n">
+        <v>46224.68011892361</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="n">
+        <v>3000055</v>
+      </c>
+      <c r="B321" t="n">
+        <v>2600013124</v>
+      </c>
+      <c r="C321" t="n">
+        <v>300</v>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="E321" s="1" t="n">
+        <v>46224.68011892361</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="n">
+        <v>3000055</v>
+      </c>
+      <c r="B322" t="n">
+        <v>2600013125</v>
+      </c>
+      <c r="C322" t="n">
+        <v>300</v>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="E322" s="1" t="n">
+        <v>46224.68011892361</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="n">
+        <v>3000366</v>
+      </c>
+      <c r="B323" t="n">
+        <v>2600018162</v>
+      </c>
+      <c r="C323" t="n">
+        <v>300</v>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="E323" s="1" t="n">
+        <v>46224.68076042824</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="n">
+        <v>3000366</v>
+      </c>
+      <c r="B324" t="n">
+        <v>2600015715</v>
+      </c>
+      <c r="C324" t="n">
+        <v>300</v>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="E324" s="1" t="n">
+        <v>46224.68076042824</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="n">
+        <v>3000550</v>
+      </c>
+      <c r="B325" t="n">
+        <v>2600012494</v>
+      </c>
+      <c r="C325" t="n">
+        <v>300</v>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="E325" s="1" t="n">
+        <v>46224.68076042824</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="n">
+        <v>3000550</v>
+      </c>
+      <c r="B326" t="n">
+        <v>2600004986</v>
+      </c>
+      <c r="C326" t="n">
+        <v>300</v>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="E326" s="1" t="n">
+        <v>46224.68076042824</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="n">
+        <v>3000550</v>
+      </c>
+      <c r="B327" t="n">
+        <v>2600012581</v>
+      </c>
+      <c r="C327" t="n">
+        <v>300</v>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="E327" s="1" t="n">
+        <v>46224.68076042824</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="n">
+        <v>3000550</v>
+      </c>
+      <c r="B328" t="n">
+        <v>2600004989</v>
+      </c>
+      <c r="C328" t="n">
+        <v>300</v>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="E328" s="1" t="n">
+        <v>46224.68076042824</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="n">
+        <v>3000550</v>
+      </c>
+      <c r="B329" t="n">
+        <v>2600012492</v>
+      </c>
+      <c r="C329" t="n">
+        <v>300</v>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="E329" s="1" t="n">
+        <v>46224.68076042824</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="n">
+        <v>3000550</v>
+      </c>
+      <c r="B330" t="n">
+        <v>2600004995</v>
+      </c>
+      <c r="C330" t="n">
+        <v>300</v>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="E330" s="1" t="n">
+        <v>46224.68076042824</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="n">
+        <v>3000093</v>
+      </c>
+      <c r="B331" t="n">
+        <v>2600019667</v>
+      </c>
+      <c r="C331" t="n">
+        <v>300</v>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="E331" s="1" t="n">
+        <v>46224.68076042824</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="n">
+        <v>3000486</v>
+      </c>
+      <c r="B332" t="n">
+        <v>2600020244</v>
+      </c>
+      <c r="C332" t="n">
+        <v>300</v>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="E332" s="1" t="n">
+        <v>46224.68076042824</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="n">
+        <v>3000093</v>
+      </c>
+      <c r="B333" t="n">
+        <v>2600008079</v>
+      </c>
+      <c r="C333" t="n">
+        <v>300</v>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="E333" s="1" t="n">
+        <v>46224.68076042824</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="n">
+        <v>3000537</v>
+      </c>
+      <c r="B334" t="n">
+        <v>2600014583</v>
+      </c>
+      <c r="C334" t="n">
+        <v>300</v>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="E334" s="1" t="n">
+        <v>46224.68076042824</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="n">
+        <v>3000292</v>
+      </c>
+      <c r="B335" t="n">
+        <v>2600012774</v>
+      </c>
+      <c r="C335" t="n">
+        <v>300</v>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="E335" s="1" t="n">
+        <v>46224.68076042824</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="n">
+        <v>3000537</v>
+      </c>
+      <c r="B336" t="n">
+        <v>2600012348</v>
+      </c>
+      <c r="C336" t="n">
+        <v>300</v>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="E336" s="1" t="n">
+        <v>46224.68076042824</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="n">
+        <v>3000733</v>
+      </c>
+      <c r="B337" t="n">
+        <v>2600017894</v>
+      </c>
+      <c r="C337" t="n">
+        <v>300</v>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="E337" s="1" t="n">
+        <v>46224.68076042824</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="n">
+        <v>3000366</v>
+      </c>
+      <c r="B338" t="n">
+        <v>2600018162</v>
+      </c>
+      <c r="C338" t="n">
+        <v>300</v>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="E338" s="1" t="n">
+        <v>46224.68109415509</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="n">
+        <v>3000366</v>
+      </c>
+      <c r="B339" t="n">
+        <v>2600015715</v>
+      </c>
+      <c r="C339" t="n">
+        <v>300</v>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="E339" s="1" t="n">
+        <v>46224.68109415509</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="n">
+        <v>3000550</v>
+      </c>
+      <c r="B340" t="n">
+        <v>2600012494</v>
+      </c>
+      <c r="C340" t="n">
+        <v>300</v>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="E340" s="1" t="n">
+        <v>46224.68109415509</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="n">
+        <v>3000550</v>
+      </c>
+      <c r="B341" t="n">
+        <v>2600004986</v>
+      </c>
+      <c r="C341" t="n">
+        <v>300</v>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="E341" s="1" t="n">
+        <v>46224.68109415509</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="n">
+        <v>3000550</v>
+      </c>
+      <c r="B342" t="n">
+        <v>2600012581</v>
+      </c>
+      <c r="C342" t="n">
+        <v>300</v>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="E342" s="1" t="n">
+        <v>46224.68109415509</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="n">
+        <v>3000550</v>
+      </c>
+      <c r="B343" t="n">
+        <v>2600004989</v>
+      </c>
+      <c r="C343" t="n">
+        <v>300</v>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="E343" s="1" t="n">
+        <v>46224.68109415509</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="n">
+        <v>3000550</v>
+      </c>
+      <c r="B344" t="n">
+        <v>2600012492</v>
+      </c>
+      <c r="C344" t="n">
+        <v>300</v>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="E344" s="1" t="n">
+        <v>46224.68109415509</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="n">
+        <v>3000550</v>
+      </c>
+      <c r="B345" t="n">
+        <v>2600004995</v>
+      </c>
+      <c r="C345" t="n">
+        <v>300</v>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="E345" s="1" t="n">
+        <v>46224.68109415509</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="n">
+        <v>3000093</v>
+      </c>
+      <c r="B346" t="n">
+        <v>2600019667</v>
+      </c>
+      <c r="C346" t="n">
+        <v>300</v>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="E346" s="1" t="n">
+        <v>46224.68109415509</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="n">
+        <v>3000486</v>
+      </c>
+      <c r="B347" t="n">
+        <v>2600020244</v>
+      </c>
+      <c r="C347" t="n">
+        <v>300</v>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="E347" s="1" t="n">
+        <v>46224.68109415509</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="n">
+        <v>3000093</v>
+      </c>
+      <c r="B348" t="n">
+        <v>2600008079</v>
+      </c>
+      <c r="C348" t="n">
+        <v>300</v>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="E348" s="1" t="n">
+        <v>46224.68109415509</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="n">
+        <v>3000537</v>
+      </c>
+      <c r="B349" t="n">
+        <v>2600014583</v>
+      </c>
+      <c r="C349" t="n">
+        <v>300</v>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="E349" s="1" t="n">
+        <v>46224.68109415509</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="n">
+        <v>3000292</v>
+      </c>
+      <c r="B350" t="n">
+        <v>2600012774</v>
+      </c>
+      <c r="C350" t="n">
+        <v>300</v>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="E350" s="1" t="n">
+        <v>46224.68109415509</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="n">
+        <v>3000537</v>
+      </c>
+      <c r="B351" t="n">
+        <v>2600012348</v>
+      </c>
+      <c r="C351" t="n">
+        <v>300</v>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="E351" s="1" t="n">
+        <v>46224.68109415509</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="n">
+        <v>3000733</v>
+      </c>
+      <c r="B352" t="n">
+        <v>2600017894</v>
+      </c>
+      <c r="C352" t="n">
+        <v>300</v>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="E352" s="1" t="n">
+        <v>46224.68109415509</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="n">
+        <v>4018101</v>
+      </c>
+      <c r="B353" t="n">
+        <v>2600020068</v>
+      </c>
+      <c r="C353" t="n">
+        <v>310</v>
+      </c>
+      <c r="D353" t="inlineStr"/>
+      <c r="E353" s="1" t="n">
+        <v>46224.72446489584</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="n">
+        <v>4013827</v>
+      </c>
+      <c r="B354" t="n">
+        <v>2600018149</v>
+      </c>
+      <c r="C354" t="n">
+        <v>310</v>
+      </c>
+      <c r="D354" t="inlineStr"/>
+      <c r="E354" s="1" t="n">
+        <v>46224.72446489584</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="n">
+        <v>4012180</v>
+      </c>
+      <c r="B355" t="n">
+        <v>2600016304</v>
+      </c>
+      <c r="C355" t="n">
+        <v>310</v>
+      </c>
+      <c r="D355" t="inlineStr"/>
+      <c r="E355" s="1" t="n">
+        <v>46224.72446489584</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="n">
+        <v>4035564</v>
+      </c>
+      <c r="B356" t="n">
+        <v>2400041446</v>
+      </c>
+      <c r="C356" t="n">
+        <v>310</v>
+      </c>
+      <c r="D356" t="inlineStr"/>
+      <c r="E356" s="1" t="n">
+        <v>46224.72446489584</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="n">
+        <v>4021094</v>
+      </c>
+      <c r="B357" t="n">
+        <v>2600010101</v>
+      </c>
+      <c r="C357" t="n">
+        <v>310</v>
+      </c>
+      <c r="D357" t="inlineStr"/>
+      <c r="E357" s="1" t="n">
+        <v>46224.72446489584</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="n">
+        <v>4021094</v>
+      </c>
+      <c r="B358" t="n">
+        <v>2600020024</v>
+      </c>
+      <c r="C358" t="n">
+        <v>310</v>
+      </c>
+      <c r="D358" t="inlineStr"/>
+      <c r="E358" s="1" t="n">
+        <v>46224.72446489584</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="n">
+        <v>3000204</v>
+      </c>
+      <c r="B359" t="n">
+        <v>2600013272</v>
+      </c>
+      <c r="C359" t="n">
+        <v>300</v>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>1232454</t>
+        </is>
+      </c>
+      <c r="E359" s="1" t="n">
+        <v>46224.73883230324</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="n">
+        <v>3000204</v>
+      </c>
+      <c r="B360" t="n">
+        <v>2600017554</v>
+      </c>
+      <c r="C360" t="n">
+        <v>300</v>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>1232454</t>
+        </is>
+      </c>
+      <c r="E360" s="1" t="n">
+        <v>46224.73883230324</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="n">
+        <v>3000204</v>
+      </c>
+      <c r="B361" t="n">
+        <v>2600017507</v>
+      </c>
+      <c r="C361" t="n">
+        <v>300</v>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>1232454</t>
+        </is>
+      </c>
+      <c r="E361" s="1" t="n">
+        <v>46224.73883230324</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="n">
+        <v>3000204</v>
+      </c>
+      <c r="B362" t="n">
+        <v>2600017552</v>
+      </c>
+      <c r="C362" t="n">
+        <v>300</v>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>1232454</t>
+        </is>
+      </c>
+      <c r="E362" s="1" t="n">
+        <v>46224.73883230324</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="n">
+        <v>3000204</v>
+      </c>
+      <c r="B363" t="n">
+        <v>2600017553</v>
+      </c>
+      <c r="C363" t="n">
+        <v>300</v>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>1232454</t>
+        </is>
+      </c>
+      <c r="E363" s="1" t="n">
+        <v>46224.73883230324</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="n">
+        <v>3000203</v>
+      </c>
+      <c r="B364" t="n">
+        <v>2600016051</v>
+      </c>
+      <c r="C364" t="n">
+        <v>300</v>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>1232454</t>
+        </is>
+      </c>
+      <c r="E364" s="1" t="n">
+        <v>46224.73883230324</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="n">
+        <v>3000191</v>
+      </c>
+      <c r="B365" t="n">
+        <v>2600019386</v>
+      </c>
+      <c r="C365" t="n">
+        <v>300</v>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>1232454</t>
+        </is>
+      </c>
+      <c r="E365" s="1" t="n">
+        <v>46224.73883230324</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="n">
+        <v>3000204</v>
+      </c>
+      <c r="B366" t="n">
+        <v>2600018147</v>
+      </c>
+      <c r="C366" t="n">
+        <v>300</v>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>1232454</t>
+        </is>
+      </c>
+      <c r="E366" s="1" t="n">
+        <v>46224.73883230324</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="n">
+        <v>3000205</v>
+      </c>
+      <c r="B367" t="n">
+        <v>2600017875</v>
+      </c>
+      <c r="C367" t="n">
+        <v>300</v>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>1232454</t>
+        </is>
+      </c>
+      <c r="E367" s="1" t="n">
+        <v>46224.73883230324</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="n">
+        <v>3000191</v>
+      </c>
+      <c r="B368" t="n">
+        <v>2600019385</v>
+      </c>
+      <c r="C368" t="n">
+        <v>300</v>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>1232454</t>
+        </is>
+      </c>
+      <c r="E368" s="1" t="n">
+        <v>46224.73883230324</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="n">
+        <v>3000191</v>
+      </c>
+      <c r="B369" t="n">
+        <v>2600008743</v>
+      </c>
+      <c r="C369" t="n">
+        <v>300</v>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>1232454</t>
+        </is>
+      </c>
+      <c r="E369" s="1" t="n">
+        <v>46224.73883230324</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="n">
+        <v>3000204</v>
+      </c>
+      <c r="B370" t="n">
+        <v>2600013273</v>
+      </c>
+      <c r="C370" t="n">
+        <v>300</v>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>1232454</t>
+        </is>
+      </c>
+      <c r="E370" s="1" t="n">
+        <v>46224.73883230324</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="n">
+        <v>3000191</v>
+      </c>
+      <c r="B371" t="n">
+        <v>2600019384</v>
+      </c>
+      <c r="C371" t="n">
+        <v>300</v>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>1232454</t>
+        </is>
+      </c>
+      <c r="E371" s="1" t="n">
+        <v>46224.73883230324</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="n">
+        <v>3000204</v>
+      </c>
+      <c r="B372" t="n">
+        <v>2600013266</v>
+      </c>
+      <c r="C372" t="n">
+        <v>300</v>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>1232454</t>
+        </is>
+      </c>
+      <c r="E372" s="1" t="n">
+        <v>46224.73883230324</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="n">
+        <v>3000127</v>
+      </c>
+      <c r="B373" t="n">
+        <v>2600016288</v>
+      </c>
+      <c r="C373" t="n">
+        <v>300</v>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>1232454</t>
+        </is>
+      </c>
+      <c r="E373" s="1" t="n">
+        <v>46224.73883230324</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="n">
+        <v>3000161</v>
+      </c>
+      <c r="B374" t="n">
+        <v>2600010682</v>
+      </c>
+      <c r="C374" t="n">
+        <v>300</v>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>1232454</t>
+        </is>
+      </c>
+      <c r="E374" s="1" t="n">
+        <v>46224.73883230324</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="n">
+        <v>3000133</v>
+      </c>
+      <c r="B375" t="n">
+        <v>2600019672</v>
+      </c>
+      <c r="C375" t="n">
+        <v>300</v>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>1232454</t>
+        </is>
+      </c>
+      <c r="E375" s="1" t="n">
+        <v>46224.73883230324</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="n">
+        <v>3000249</v>
+      </c>
+      <c r="B376" t="n">
+        <v>2600018153</v>
+      </c>
+      <c r="C376" t="n">
+        <v>300</v>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>1232454</t>
+        </is>
+      </c>
+      <c r="E376" s="1" t="n">
+        <v>46224.73883230324</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="n">
+        <v>3000249</v>
+      </c>
+      <c r="B377" t="n">
+        <v>2600018151</v>
+      </c>
+      <c r="C377" t="n">
+        <v>300</v>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>1232454</t>
+        </is>
+      </c>
+      <c r="E377" s="1" t="n">
+        <v>46224.73883230324</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="n">
+        <v>3000133</v>
+      </c>
+      <c r="B378" t="n">
+        <v>2600019670</v>
+      </c>
+      <c r="C378" t="n">
+        <v>300</v>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>1232454</t>
+        </is>
+      </c>
+      <c r="E378" s="1" t="n">
+        <v>46224.73883230324</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="n">
+        <v>3000134</v>
+      </c>
+      <c r="B379" t="n">
+        <v>2600020924</v>
+      </c>
+      <c r="C379" t="n">
+        <v>300</v>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>1232454</t>
+        </is>
+      </c>
+      <c r="E379" s="1" t="n">
+        <v>46224.73883230324</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="n">
+        <v>3000086</v>
+      </c>
+      <c r="B380" t="n">
+        <v>2600020069</v>
+      </c>
+      <c r="C380" t="n">
+        <v>300</v>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>1232454</t>
+        </is>
+      </c>
+      <c r="E380" s="1" t="n">
+        <v>46224.73883230324</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="n">
+        <v>3000086</v>
+      </c>
+      <c r="B381" t="n">
+        <v>2600020070</v>
+      </c>
+      <c r="C381" t="n">
+        <v>300</v>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>1232454</t>
+        </is>
+      </c>
+      <c r="E381" s="1" t="n">
+        <v>46224.73883230324</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="n">
+        <v>4018101</v>
+      </c>
+      <c r="B382" t="n">
+        <v>2600017871</v>
+      </c>
+      <c r="C382" t="n">
+        <v>310</v>
+      </c>
+      <c r="D382" t="inlineStr"/>
+      <c r="E382" s="1" t="n">
+        <v>46224.75992053241</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="n">
+        <v>4034441</v>
+      </c>
+      <c r="B383" t="n">
+        <v>2400021304</v>
+      </c>
+      <c r="C383" t="n">
+        <v>310</v>
+      </c>
+      <c r="D383" t="inlineStr"/>
+      <c r="E383" s="1" t="n">
+        <v>46224.75992053241</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="n">
+        <v>4034457</v>
+      </c>
+      <c r="B384" t="n">
+        <v>2600016364</v>
+      </c>
+      <c r="C384" t="n">
+        <v>310</v>
+      </c>
+      <c r="D384" t="inlineStr"/>
+      <c r="E384" s="1" t="n">
+        <v>46224.75992053241</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="n">
+        <v>4038837</v>
+      </c>
+      <c r="B385" t="n">
+        <v>2600008160</v>
+      </c>
+      <c r="C385" t="n">
+        <v>310</v>
+      </c>
+      <c r="D385" t="inlineStr"/>
+      <c r="E385" s="1" t="n">
+        <v>46224.75992053241</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="n">
+        <v>4027483</v>
+      </c>
+      <c r="B386" t="n">
+        <v>2600015651</v>
+      </c>
+      <c r="C386" t="n">
+        <v>310</v>
+      </c>
+      <c r="D386" t="inlineStr"/>
+      <c r="E386" s="1" t="n">
+        <v>46224.75992053241</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="n">
+        <v>4001389</v>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>2600020445</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr"/>
+      <c r="E387" s="1" t="n">
+        <v>46224.7605434451</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="n">
+        <v>4000231</v>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>2600020447</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr"/>
+      <c r="E388" s="1" t="n">
+        <v>46224.7605434451</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="n">
+        <v>4000399</v>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>2600017356</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr"/>
+      <c r="E389" s="1" t="n">
+        <v>46224.7605434451</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="n">
+        <v>4000203</v>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>2600017367</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr"/>
+      <c r="E390" s="1" t="n">
+        <v>46224.7605434451</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="n">
+        <v>4000228</v>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>2600020443</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr"/>
+      <c r="E391" s="1" t="n">
+        <v>46224.7605434451</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="n">
+        <v>4000399</v>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>2600010472</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr"/>
+      <c r="E392" s="1" t="n">
+        <v>46224.7605434451</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="n">
+        <v>4001389</v>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>2600019548</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr"/>
+      <c r="E393" s="1" t="n">
+        <v>46224.7605434451</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="n">
+        <v>4000231</v>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>2600020435</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr"/>
+      <c r="E394" s="1" t="n">
+        <v>46224.7605434451</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="n">
+        <v>4000203</v>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>2600012969</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr"/>
+      <c r="E395" s="1" t="n">
+        <v>46224.7605434451</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="n">
+        <v>4001247</v>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>2400040579</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr"/>
+      <c r="E396" s="1" t="n">
+        <v>46224.7605434451</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="n">
+        <v>4001395</v>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>2600016471</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr"/>
+      <c r="E397" s="1" t="n">
+        <v>46224.7605434451</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="n">
+        <v>4000310</v>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>2600020442</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr"/>
+      <c r="E398" s="1" t="n">
+        <v>46224.7605434451</v>
       </c>
     </row>
   </sheetData>

--- a/data/historico/historico_documentos.xlsx
+++ b/data/historico/historico_documentos.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E398"/>
+  <dimension ref="A1:E744"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7146,228 +7146,5986 @@
       <c r="A387" t="n">
         <v>4001389</v>
       </c>
-      <c r="B387" t="inlineStr">
-        <is>
-          <t>2600020445</t>
-        </is>
-      </c>
-      <c r="C387" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
+      <c r="B387" t="n">
+        <v>2600020445</v>
+      </c>
+      <c r="C387" t="n">
+        <v>310</v>
       </c>
       <c r="D387" t="inlineStr"/>
       <c r="E387" s="1" t="n">
-        <v>46224.7605434451</v>
+        <v>46224.76054344908</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="n">
         <v>4000231</v>
       </c>
-      <c r="B388" t="inlineStr">
-        <is>
-          <t>2600020447</t>
-        </is>
-      </c>
-      <c r="C388" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
+      <c r="B388" t="n">
+        <v>2600020447</v>
+      </c>
+      <c r="C388" t="n">
+        <v>310</v>
       </c>
       <c r="D388" t="inlineStr"/>
       <c r="E388" s="1" t="n">
-        <v>46224.7605434451</v>
+        <v>46224.76054344908</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
         <v>4000399</v>
       </c>
-      <c r="B389" t="inlineStr">
-        <is>
-          <t>2600017356</t>
-        </is>
-      </c>
-      <c r="C389" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
+      <c r="B389" t="n">
+        <v>2600017356</v>
+      </c>
+      <c r="C389" t="n">
+        <v>310</v>
       </c>
       <c r="D389" t="inlineStr"/>
       <c r="E389" s="1" t="n">
-        <v>46224.7605434451</v>
+        <v>46224.76054344908</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="n">
         <v>4000203</v>
       </c>
-      <c r="B390" t="inlineStr">
-        <is>
-          <t>2600017367</t>
-        </is>
-      </c>
-      <c r="C390" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
+      <c r="B390" t="n">
+        <v>2600017367</v>
+      </c>
+      <c r="C390" t="n">
+        <v>310</v>
       </c>
       <c r="D390" t="inlineStr"/>
       <c r="E390" s="1" t="n">
-        <v>46224.7605434451</v>
+        <v>46224.76054344908</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="n">
         <v>4000228</v>
       </c>
-      <c r="B391" t="inlineStr">
-        <is>
-          <t>2600020443</t>
-        </is>
-      </c>
-      <c r="C391" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
+      <c r="B391" t="n">
+        <v>2600020443</v>
+      </c>
+      <c r="C391" t="n">
+        <v>310</v>
       </c>
       <c r="D391" t="inlineStr"/>
       <c r="E391" s="1" t="n">
-        <v>46224.7605434451</v>
+        <v>46224.76054344908</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
         <v>4000399</v>
       </c>
-      <c r="B392" t="inlineStr">
-        <is>
-          <t>2600010472</t>
-        </is>
-      </c>
-      <c r="C392" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
+      <c r="B392" t="n">
+        <v>2600010472</v>
+      </c>
+      <c r="C392" t="n">
+        <v>310</v>
       </c>
       <c r="D392" t="inlineStr"/>
       <c r="E392" s="1" t="n">
-        <v>46224.7605434451</v>
+        <v>46224.76054344908</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
         <v>4001389</v>
       </c>
-      <c r="B393" t="inlineStr">
-        <is>
-          <t>2600019548</t>
-        </is>
-      </c>
-      <c r="C393" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
+      <c r="B393" t="n">
+        <v>2600019548</v>
+      </c>
+      <c r="C393" t="n">
+        <v>310</v>
       </c>
       <c r="D393" t="inlineStr"/>
       <c r="E393" s="1" t="n">
-        <v>46224.7605434451</v>
+        <v>46224.76054344908</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="n">
         <v>4000231</v>
       </c>
-      <c r="B394" t="inlineStr">
-        <is>
-          <t>2600020435</t>
-        </is>
-      </c>
-      <c r="C394" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
+      <c r="B394" t="n">
+        <v>2600020435</v>
+      </c>
+      <c r="C394" t="n">
+        <v>310</v>
       </c>
       <c r="D394" t="inlineStr"/>
       <c r="E394" s="1" t="n">
-        <v>46224.7605434451</v>
+        <v>46224.76054344908</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="n">
         <v>4000203</v>
       </c>
-      <c r="B395" t="inlineStr">
-        <is>
-          <t>2600012969</t>
-        </is>
-      </c>
-      <c r="C395" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
+      <c r="B395" t="n">
+        <v>2600012969</v>
+      </c>
+      <c r="C395" t="n">
+        <v>310</v>
       </c>
       <c r="D395" t="inlineStr"/>
       <c r="E395" s="1" t="n">
-        <v>46224.7605434451</v>
+        <v>46224.76054344908</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="n">
         <v>4001247</v>
       </c>
-      <c r="B396" t="inlineStr">
-        <is>
-          <t>2400040579</t>
-        </is>
-      </c>
-      <c r="C396" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
+      <c r="B396" t="n">
+        <v>2400040579</v>
+      </c>
+      <c r="C396" t="n">
+        <v>310</v>
       </c>
       <c r="D396" t="inlineStr"/>
       <c r="E396" s="1" t="n">
-        <v>46224.7605434451</v>
+        <v>46224.76054344908</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
         <v>4001395</v>
       </c>
-      <c r="B397" t="inlineStr">
-        <is>
-          <t>2600016471</t>
-        </is>
-      </c>
-      <c r="C397" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
+      <c r="B397" t="n">
+        <v>2600016471</v>
+      </c>
+      <c r="C397" t="n">
+        <v>310</v>
       </c>
       <c r="D397" t="inlineStr"/>
       <c r="E397" s="1" t="n">
-        <v>46224.7605434451</v>
+        <v>46224.76054344908</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="n">
         <v>4000310</v>
       </c>
-      <c r="B398" t="inlineStr">
-        <is>
-          <t>2600020442</t>
-        </is>
-      </c>
-      <c r="C398" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
+      <c r="B398" t="n">
+        <v>2600020442</v>
+      </c>
+      <c r="C398" t="n">
+        <v>310</v>
       </c>
       <c r="D398" t="inlineStr"/>
       <c r="E398" s="1" t="n">
-        <v>46224.7605434451</v>
+        <v>46224.76054344908</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="n">
+        <v>3004710</v>
+      </c>
+      <c r="B399" t="n">
+        <v>2600009719</v>
+      </c>
+      <c r="C399" t="n">
+        <v>300</v>
+      </c>
+      <c r="D399" t="inlineStr"/>
+      <c r="E399" s="1" t="n">
+        <v>46224.77465783565</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="n">
+        <v>3003464</v>
+      </c>
+      <c r="B400" t="n">
+        <v>2600020613</v>
+      </c>
+      <c r="C400" t="n">
+        <v>300</v>
+      </c>
+      <c r="D400" t="inlineStr"/>
+      <c r="E400" s="1" t="n">
+        <v>46224.77465783565</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="n">
+        <v>3000542</v>
+      </c>
+      <c r="B401" t="n">
+        <v>2600019525</v>
+      </c>
+      <c r="C401" t="n">
+        <v>300</v>
+      </c>
+      <c r="D401" t="inlineStr"/>
+      <c r="E401" s="1" t="n">
+        <v>46224.77465783565</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="n">
+        <v>3004710</v>
+      </c>
+      <c r="B402" t="n">
+        <v>2600006472</v>
+      </c>
+      <c r="C402" t="n">
+        <v>300</v>
+      </c>
+      <c r="D402" t="inlineStr"/>
+      <c r="E402" s="1" t="n">
+        <v>46224.77465783565</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="n">
+        <v>3004710</v>
+      </c>
+      <c r="B403" t="n">
+        <v>2600015046</v>
+      </c>
+      <c r="C403" t="n">
+        <v>300</v>
+      </c>
+      <c r="D403" t="inlineStr"/>
+      <c r="E403" s="1" t="n">
+        <v>46224.77465783565</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="n">
+        <v>3000550</v>
+      </c>
+      <c r="B404" t="n">
+        <v>2600016047</v>
+      </c>
+      <c r="C404" t="n">
+        <v>300</v>
+      </c>
+      <c r="D404" t="inlineStr"/>
+      <c r="E404" s="1" t="n">
+        <v>46224.77465783565</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B405" t="n">
+        <v>2600011176</v>
+      </c>
+      <c r="C405" t="n">
+        <v>300</v>
+      </c>
+      <c r="D405" t="inlineStr"/>
+      <c r="E405" s="1" t="n">
+        <v>46224.77465783565</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="n">
+        <v>3000455</v>
+      </c>
+      <c r="B406" t="n">
+        <v>2600018630</v>
+      </c>
+      <c r="C406" t="n">
+        <v>300</v>
+      </c>
+      <c r="D406" t="inlineStr"/>
+      <c r="E406" s="1" t="n">
+        <v>46224.77465783565</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="n">
+        <v>3000455</v>
+      </c>
+      <c r="B407" t="n">
+        <v>2600018629</v>
+      </c>
+      <c r="C407" t="n">
+        <v>300</v>
+      </c>
+      <c r="D407" t="inlineStr"/>
+      <c r="E407" s="1" t="n">
+        <v>46224.77465783565</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="n">
+        <v>3000407</v>
+      </c>
+      <c r="B408" t="n">
+        <v>2600011685</v>
+      </c>
+      <c r="C408" t="n">
+        <v>300</v>
+      </c>
+      <c r="D408" t="inlineStr"/>
+      <c r="E408" s="1" t="n">
+        <v>46224.77465783565</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="n">
+        <v>3002645</v>
+      </c>
+      <c r="B409" t="n">
+        <v>2600016285</v>
+      </c>
+      <c r="C409" t="n">
+        <v>300</v>
+      </c>
+      <c r="D409" t="inlineStr"/>
+      <c r="E409" s="1" t="n">
+        <v>46224.77465783565</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="n">
+        <v>3002101</v>
+      </c>
+      <c r="B410" t="n">
+        <v>2600020144</v>
+      </c>
+      <c r="C410" t="n">
+        <v>300</v>
+      </c>
+      <c r="D410" t="inlineStr"/>
+      <c r="E410" s="1" t="n">
+        <v>46224.77465783565</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B411" t="n">
+        <v>2600020431</v>
+      </c>
+      <c r="C411" t="n">
+        <v>300</v>
+      </c>
+      <c r="D411" t="inlineStr"/>
+      <c r="E411" s="1" t="n">
+        <v>46224.77465783565</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="n">
+        <v>3004710</v>
+      </c>
+      <c r="B412" t="n">
+        <v>2600006471</v>
+      </c>
+      <c r="C412" t="n">
+        <v>300</v>
+      </c>
+      <c r="D412" t="inlineStr"/>
+      <c r="E412" s="1" t="n">
+        <v>46224.77601776621</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="n">
+        <v>3005283</v>
+      </c>
+      <c r="B413" t="n">
+        <v>2500031292</v>
+      </c>
+      <c r="C413" t="n">
+        <v>300</v>
+      </c>
+      <c r="D413" t="inlineStr"/>
+      <c r="E413" s="1" t="n">
+        <v>46224.77601776621</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="n">
+        <v>3000502</v>
+      </c>
+      <c r="B414" t="n">
+        <v>2600015623</v>
+      </c>
+      <c r="C414" t="n">
+        <v>300</v>
+      </c>
+      <c r="D414" t="inlineStr"/>
+      <c r="E414" s="1" t="n">
+        <v>46224.77601776621</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="n">
+        <v>3001786</v>
+      </c>
+      <c r="B415" t="n">
+        <v>2600018871</v>
+      </c>
+      <c r="C415" t="n">
+        <v>300</v>
+      </c>
+      <c r="D415" t="inlineStr"/>
+      <c r="E415" s="1" t="n">
+        <v>46224.77601776621</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B416" t="n">
+        <v>2600014698</v>
+      </c>
+      <c r="C416" t="n">
+        <v>300</v>
+      </c>
+      <c r="D416" t="inlineStr"/>
+      <c r="E416" s="1" t="n">
+        <v>46224.77601776621</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="n">
+        <v>3000030</v>
+      </c>
+      <c r="B417" t="n">
+        <v>2600014122</v>
+      </c>
+      <c r="C417" t="n">
+        <v>300</v>
+      </c>
+      <c r="D417" t="inlineStr"/>
+      <c r="E417" s="1" t="n">
+        <v>46224.77601776621</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="n">
+        <v>3004538</v>
+      </c>
+      <c r="B418" t="n">
+        <v>2600017518</v>
+      </c>
+      <c r="C418" t="n">
+        <v>300</v>
+      </c>
+      <c r="D418" t="inlineStr"/>
+      <c r="E418" s="1" t="n">
+        <v>46224.77601776621</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="n">
+        <v>3000500</v>
+      </c>
+      <c r="B419" t="n">
+        <v>2600016292</v>
+      </c>
+      <c r="C419" t="n">
+        <v>300</v>
+      </c>
+      <c r="D419" t="inlineStr"/>
+      <c r="E419" s="1" t="n">
+        <v>46224.77601776621</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="n">
+        <v>3002645</v>
+      </c>
+      <c r="B420" t="n">
+        <v>2600006122</v>
+      </c>
+      <c r="C420" t="n">
+        <v>300</v>
+      </c>
+      <c r="D420" t="inlineStr"/>
+      <c r="E420" s="1" t="n">
+        <v>46224.77601776621</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="n">
+        <v>3000549</v>
+      </c>
+      <c r="B421" t="n">
+        <v>2600017698</v>
+      </c>
+      <c r="C421" t="n">
+        <v>300</v>
+      </c>
+      <c r="D421" t="inlineStr"/>
+      <c r="E421" s="1" t="n">
+        <v>46224.77601776621</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="n">
+        <v>3000169</v>
+      </c>
+      <c r="B422" t="n">
+        <v>2600008233</v>
+      </c>
+      <c r="C422" t="n">
+        <v>300</v>
+      </c>
+      <c r="D422" t="inlineStr"/>
+      <c r="E422" s="1" t="n">
+        <v>46224.77604326389</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="n">
+        <v>3002762</v>
+      </c>
+      <c r="B423" t="n">
+        <v>2600019318</v>
+      </c>
+      <c r="C423" t="n">
+        <v>300</v>
+      </c>
+      <c r="D423" t="inlineStr"/>
+      <c r="E423" s="1" t="n">
+        <v>46224.77604326389</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="n">
+        <v>3000534</v>
+      </c>
+      <c r="B424" t="n">
+        <v>2600010870</v>
+      </c>
+      <c r="C424" t="n">
+        <v>300</v>
+      </c>
+      <c r="D424" t="inlineStr"/>
+      <c r="E424" s="1" t="n">
+        <v>46224.77604326389</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="n">
+        <v>3000542</v>
+      </c>
+      <c r="B425" t="n">
+        <v>2600019526</v>
+      </c>
+      <c r="C425" t="n">
+        <v>300</v>
+      </c>
+      <c r="D425" t="inlineStr"/>
+      <c r="E425" s="1" t="n">
+        <v>46224.77604326389</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="n">
+        <v>3004065</v>
+      </c>
+      <c r="B426" t="n">
+        <v>2600014322</v>
+      </c>
+      <c r="C426" t="n">
+        <v>300</v>
+      </c>
+      <c r="D426" t="inlineStr"/>
+      <c r="E426" s="1" t="n">
+        <v>46224.77604326389</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="n">
+        <v>3002762</v>
+      </c>
+      <c r="B427" t="n">
+        <v>2600012837</v>
+      </c>
+      <c r="C427" t="n">
+        <v>300</v>
+      </c>
+      <c r="D427" t="inlineStr"/>
+      <c r="E427" s="1" t="n">
+        <v>46224.77604326389</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="n">
+        <v>3000169</v>
+      </c>
+      <c r="B428" t="n">
+        <v>2600008293</v>
+      </c>
+      <c r="C428" t="n">
+        <v>300</v>
+      </c>
+      <c r="D428" t="inlineStr"/>
+      <c r="E428" s="1" t="n">
+        <v>46224.77604326389</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="n">
+        <v>3002762</v>
+      </c>
+      <c r="B429" t="n">
+        <v>2600016651</v>
+      </c>
+      <c r="C429" t="n">
+        <v>300</v>
+      </c>
+      <c r="D429" t="inlineStr"/>
+      <c r="E429" s="1" t="n">
+        <v>46224.77604326389</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="n">
+        <v>2004133</v>
+      </c>
+      <c r="B430" t="n">
+        <v>2501221</v>
+      </c>
+      <c r="C430" t="n">
+        <v>300</v>
+      </c>
+      <c r="D430" t="inlineStr"/>
+      <c r="E430" s="1" t="n">
+        <v>46224.77604326389</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="n">
+        <v>3000550</v>
+      </c>
+      <c r="B431" t="n">
+        <v>2600004996</v>
+      </c>
+      <c r="C431" t="n">
+        <v>300</v>
+      </c>
+      <c r="D431" t="inlineStr"/>
+      <c r="E431" s="1" t="n">
+        <v>46224.77604326389</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="n">
+        <v>3000550</v>
+      </c>
+      <c r="B432" t="n">
+        <v>2600016287</v>
+      </c>
+      <c r="C432" t="n">
+        <v>300</v>
+      </c>
+      <c r="D432" t="inlineStr"/>
+      <c r="E432" s="1" t="n">
+        <v>46224.77604326389</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="n">
+        <v>3000030</v>
+      </c>
+      <c r="B433" t="n">
+        <v>2600003953</v>
+      </c>
+      <c r="C433" t="n">
+        <v>300</v>
+      </c>
+      <c r="D433" t="inlineStr"/>
+      <c r="E433" s="1" t="n">
+        <v>46224.77604326389</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="n">
+        <v>3004466</v>
+      </c>
+      <c r="B434" t="n">
+        <v>2600017762</v>
+      </c>
+      <c r="C434" t="n">
+        <v>300</v>
+      </c>
+      <c r="D434" t="inlineStr"/>
+      <c r="E434" s="1" t="n">
+        <v>46224.77604326389</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="n">
+        <v>3004466</v>
+      </c>
+      <c r="B435" t="n">
+        <v>2600017761</v>
+      </c>
+      <c r="C435" t="n">
+        <v>300</v>
+      </c>
+      <c r="D435" t="inlineStr"/>
+      <c r="E435" s="1" t="n">
+        <v>46224.77604326389</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="n">
+        <v>3000363</v>
+      </c>
+      <c r="B436" t="n">
+        <v>2600018471</v>
+      </c>
+      <c r="C436" t="n">
+        <v>300</v>
+      </c>
+      <c r="D436" t="inlineStr"/>
+      <c r="E436" s="1" t="n">
+        <v>46224.77604326389</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="n">
+        <v>3000485</v>
+      </c>
+      <c r="B437" t="n">
+        <v>2600020245</v>
+      </c>
+      <c r="C437" t="n">
+        <v>300</v>
+      </c>
+      <c r="D437" t="inlineStr"/>
+      <c r="E437" s="1" t="n">
+        <v>46224.77604326389</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="n">
+        <v>3002529</v>
+      </c>
+      <c r="B438" t="n">
+        <v>2600016281</v>
+      </c>
+      <c r="C438" t="n">
+        <v>300</v>
+      </c>
+      <c r="D438" t="inlineStr"/>
+      <c r="E438" s="1" t="n">
+        <v>46224.77604326389</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="n">
+        <v>3001685</v>
+      </c>
+      <c r="B439" t="n">
+        <v>2600016702</v>
+      </c>
+      <c r="C439" t="n">
+        <v>300</v>
+      </c>
+      <c r="D439" t="inlineStr"/>
+      <c r="E439" s="1" t="n">
+        <v>46224.77604326389</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="n">
+        <v>3002529</v>
+      </c>
+      <c r="B440" t="n">
+        <v>2600012001</v>
+      </c>
+      <c r="C440" t="n">
+        <v>300</v>
+      </c>
+      <c r="D440" t="inlineStr"/>
+      <c r="E440" s="1" t="n">
+        <v>46224.77604326389</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="n">
+        <v>3004642</v>
+      </c>
+      <c r="B441" t="n">
+        <v>2600015414</v>
+      </c>
+      <c r="C441" t="n">
+        <v>300</v>
+      </c>
+      <c r="D441" t="inlineStr"/>
+      <c r="E441" s="1" t="n">
+        <v>46224.77604326389</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="n">
+        <v>3000447</v>
+      </c>
+      <c r="B442" t="n">
+        <v>2600020468</v>
+      </c>
+      <c r="C442" t="n">
+        <v>300</v>
+      </c>
+      <c r="D442" t="inlineStr"/>
+      <c r="E442" s="1" t="n">
+        <v>46224.77604326389</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="n">
+        <v>3000500</v>
+      </c>
+      <c r="B443" t="n">
+        <v>2600016293</v>
+      </c>
+      <c r="C443" t="n">
+        <v>300</v>
+      </c>
+      <c r="D443" t="inlineStr"/>
+      <c r="E443" s="1" t="n">
+        <v>46224.77604326389</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="n">
+        <v>3003802</v>
+      </c>
+      <c r="B444" t="n">
+        <v>2600013411</v>
+      </c>
+      <c r="C444" t="n">
+        <v>300</v>
+      </c>
+      <c r="D444" t="inlineStr"/>
+      <c r="E444" s="1" t="n">
+        <v>46224.77604326389</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="n">
+        <v>3003421</v>
+      </c>
+      <c r="B445" t="n">
+        <v>2600018684</v>
+      </c>
+      <c r="C445" t="n">
+        <v>300</v>
+      </c>
+      <c r="D445" t="inlineStr"/>
+      <c r="E445" s="1" t="n">
+        <v>46224.77604326389</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="n">
+        <v>3003905</v>
+      </c>
+      <c r="B446" t="n">
+        <v>2600012765</v>
+      </c>
+      <c r="C446" t="n">
+        <v>300</v>
+      </c>
+      <c r="D446" t="inlineStr"/>
+      <c r="E446" s="1" t="n">
+        <v>46224.77604326389</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="n">
+        <v>3000310</v>
+      </c>
+      <c r="B447" t="n">
+        <v>2400021998</v>
+      </c>
+      <c r="C447" t="n">
+        <v>300</v>
+      </c>
+      <c r="D447" t="inlineStr"/>
+      <c r="E447" s="1" t="n">
+        <v>46224.77604326389</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="n">
+        <v>3004491</v>
+      </c>
+      <c r="B448" t="n">
+        <v>2600016350</v>
+      </c>
+      <c r="C448" t="n">
+        <v>300</v>
+      </c>
+      <c r="D448" t="inlineStr"/>
+      <c r="E448" s="1" t="n">
+        <v>46224.77604326389</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="n">
+        <v>3002529</v>
+      </c>
+      <c r="B449" t="n">
+        <v>2600018731</v>
+      </c>
+      <c r="C449" t="n">
+        <v>300</v>
+      </c>
+      <c r="D449" t="inlineStr"/>
+      <c r="E449" s="1" t="n">
+        <v>46224.77604326389</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="n">
+        <v>3000253</v>
+      </c>
+      <c r="B450" t="n">
+        <v>2600017831</v>
+      </c>
+      <c r="C450" t="n">
+        <v>300</v>
+      </c>
+      <c r="D450" t="inlineStr"/>
+      <c r="E450" s="1" t="n">
+        <v>46224.77604326389</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="n">
+        <v>3003421</v>
+      </c>
+      <c r="B451" t="n">
+        <v>2600018683</v>
+      </c>
+      <c r="C451" t="n">
+        <v>300</v>
+      </c>
+      <c r="D451" t="inlineStr"/>
+      <c r="E451" s="1" t="n">
+        <v>46224.77604326389</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="n">
+        <v>3000496</v>
+      </c>
+      <c r="B452" t="n">
+        <v>2600019773</v>
+      </c>
+      <c r="C452" t="n">
+        <v>300</v>
+      </c>
+      <c r="D452" t="inlineStr"/>
+      <c r="E452" s="1" t="n">
+        <v>46224.77604326389</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="n">
+        <v>3004538</v>
+      </c>
+      <c r="B453" t="n">
+        <v>2600013128</v>
+      </c>
+      <c r="C453" t="n">
+        <v>300</v>
+      </c>
+      <c r="D453" t="inlineStr"/>
+      <c r="E453" s="1" t="n">
+        <v>46224.77604326389</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="n">
+        <v>3003803</v>
+      </c>
+      <c r="B454" t="n">
+        <v>2600019776</v>
+      </c>
+      <c r="C454" t="n">
+        <v>300</v>
+      </c>
+      <c r="D454" t="inlineStr"/>
+      <c r="E454" s="1" t="n">
+        <v>46224.77604326389</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="n">
+        <v>3000015</v>
+      </c>
+      <c r="B455" t="n">
+        <v>2600009164</v>
+      </c>
+      <c r="C455" t="n">
+        <v>300</v>
+      </c>
+      <c r="D455" t="inlineStr"/>
+      <c r="E455" s="1" t="n">
+        <v>46224.77610663194</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="n">
+        <v>3003509</v>
+      </c>
+      <c r="B456" t="n">
+        <v>2600000221</v>
+      </c>
+      <c r="C456" t="n">
+        <v>300</v>
+      </c>
+      <c r="D456" t="inlineStr"/>
+      <c r="E456" s="1" t="n">
+        <v>46224.77610663194</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="n">
+        <v>3001628</v>
+      </c>
+      <c r="B457" t="n">
+        <v>2600014414</v>
+      </c>
+      <c r="C457" t="n">
+        <v>300</v>
+      </c>
+      <c r="D457" t="inlineStr"/>
+      <c r="E457" s="1" t="n">
+        <v>46224.77610663194</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="n">
+        <v>3000550</v>
+      </c>
+      <c r="B458" t="n">
+        <v>2600016046</v>
+      </c>
+      <c r="C458" t="n">
+        <v>300</v>
+      </c>
+      <c r="D458" t="inlineStr"/>
+      <c r="E458" s="1" t="n">
+        <v>46224.77610663194</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="n">
+        <v>3000550</v>
+      </c>
+      <c r="B459" t="n">
+        <v>2600016045</v>
+      </c>
+      <c r="C459" t="n">
+        <v>300</v>
+      </c>
+      <c r="D459" t="inlineStr"/>
+      <c r="E459" s="1" t="n">
+        <v>46224.77610663194</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="n">
+        <v>3000226</v>
+      </c>
+      <c r="B460" t="n">
+        <v>2600012786</v>
+      </c>
+      <c r="C460" t="n">
+        <v>300</v>
+      </c>
+      <c r="D460" t="inlineStr"/>
+      <c r="E460" s="1" t="n">
+        <v>46224.77610663194</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="n">
+        <v>3000473</v>
+      </c>
+      <c r="B461" t="n">
+        <v>2600020921</v>
+      </c>
+      <c r="C461" t="n">
+        <v>300</v>
+      </c>
+      <c r="D461" t="inlineStr"/>
+      <c r="E461" s="1" t="n">
+        <v>46224.77610663194</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="n">
+        <v>3000473</v>
+      </c>
+      <c r="B462" t="n">
+        <v>2600020922</v>
+      </c>
+      <c r="C462" t="n">
+        <v>300</v>
+      </c>
+      <c r="D462" t="inlineStr"/>
+      <c r="E462" s="1" t="n">
+        <v>46224.77610663194</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="n">
+        <v>3000550</v>
+      </c>
+      <c r="B463" t="n">
+        <v>2600012493</v>
+      </c>
+      <c r="C463" t="n">
+        <v>300</v>
+      </c>
+      <c r="D463" t="inlineStr"/>
+      <c r="E463" s="1" t="n">
+        <v>46224.77610663194</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="n">
+        <v>3000457</v>
+      </c>
+      <c r="B464" t="n">
+        <v>2600019180</v>
+      </c>
+      <c r="C464" t="n">
+        <v>300</v>
+      </c>
+      <c r="D464" t="inlineStr"/>
+      <c r="E464" s="1" t="n">
+        <v>46224.77610663194</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="n">
+        <v>3000457</v>
+      </c>
+      <c r="B465" t="n">
+        <v>2600019183</v>
+      </c>
+      <c r="C465" t="n">
+        <v>300</v>
+      </c>
+      <c r="D465" t="inlineStr"/>
+      <c r="E465" s="1" t="n">
+        <v>46224.77610663194</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="n">
+        <v>3000539</v>
+      </c>
+      <c r="B466" t="n">
+        <v>2600014816</v>
+      </c>
+      <c r="C466" t="n">
+        <v>300</v>
+      </c>
+      <c r="D466" t="inlineStr"/>
+      <c r="E466" s="1" t="n">
+        <v>46224.77610663194</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="n">
+        <v>3002643</v>
+      </c>
+      <c r="B467" t="n">
+        <v>2600013794</v>
+      </c>
+      <c r="C467" t="n">
+        <v>300</v>
+      </c>
+      <c r="D467" t="inlineStr"/>
+      <c r="E467" s="1" t="n">
+        <v>46224.77610663194</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="n">
+        <v>3003618</v>
+      </c>
+      <c r="B468" t="n">
+        <v>2600000481</v>
+      </c>
+      <c r="C468" t="n">
+        <v>300</v>
+      </c>
+      <c r="D468" t="inlineStr"/>
+      <c r="E468" s="1" t="n">
+        <v>46224.77610663194</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="n">
+        <v>3000457</v>
+      </c>
+      <c r="B469" t="n">
+        <v>2600019182</v>
+      </c>
+      <c r="C469" t="n">
+        <v>300</v>
+      </c>
+      <c r="D469" t="inlineStr"/>
+      <c r="E469" s="1" t="n">
+        <v>46224.77610663194</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="n">
+        <v>3001987</v>
+      </c>
+      <c r="B470" t="n">
+        <v>2600015124</v>
+      </c>
+      <c r="C470" t="n">
+        <v>300</v>
+      </c>
+      <c r="D470" t="inlineStr"/>
+      <c r="E470" s="1" t="n">
+        <v>46224.77610663194</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="n">
+        <v>3003802</v>
+      </c>
+      <c r="B471" t="n">
+        <v>2600006355</v>
+      </c>
+      <c r="C471" t="n">
+        <v>300</v>
+      </c>
+      <c r="D471" t="inlineStr"/>
+      <c r="E471" s="1" t="n">
+        <v>46224.77610663194</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="n">
+        <v>3000457</v>
+      </c>
+      <c r="B472" t="n">
+        <v>2600019181</v>
+      </c>
+      <c r="C472" t="n">
+        <v>300</v>
+      </c>
+      <c r="D472" t="inlineStr"/>
+      <c r="E472" s="1" t="n">
+        <v>46224.77610663194</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="n">
+        <v>3000532</v>
+      </c>
+      <c r="B473" t="n">
+        <v>2600007092</v>
+      </c>
+      <c r="C473" t="n">
+        <v>300</v>
+      </c>
+      <c r="D473" t="inlineStr"/>
+      <c r="E473" s="1" t="n">
+        <v>46224.77610663194</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="n">
+        <v>3000301</v>
+      </c>
+      <c r="B474" t="n">
+        <v>2500014744</v>
+      </c>
+      <c r="C474" t="n">
+        <v>300</v>
+      </c>
+      <c r="D474" t="inlineStr"/>
+      <c r="E474" s="1" t="n">
+        <v>46224.77610663194</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="n">
+        <v>3000541</v>
+      </c>
+      <c r="B475" t="n">
+        <v>2600013104</v>
+      </c>
+      <c r="C475" t="n">
+        <v>300</v>
+      </c>
+      <c r="D475" t="inlineStr"/>
+      <c r="E475" s="1" t="n">
+        <v>46224.77610663194</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="n">
+        <v>3004538</v>
+      </c>
+      <c r="B476" t="n">
+        <v>2600013163</v>
+      </c>
+      <c r="C476" t="n">
+        <v>300</v>
+      </c>
+      <c r="D476" t="inlineStr"/>
+      <c r="E476" s="1" t="n">
+        <v>46224.77610663194</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="n">
+        <v>3001987</v>
+      </c>
+      <c r="B477" t="n">
+        <v>2600019202</v>
+      </c>
+      <c r="C477" t="n">
+        <v>300</v>
+      </c>
+      <c r="D477" t="inlineStr"/>
+      <c r="E477" s="1" t="n">
+        <v>46224.77610663194</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="n">
+        <v>3000447</v>
+      </c>
+      <c r="B478" t="n">
+        <v>2600020533</v>
+      </c>
+      <c r="C478" t="n">
+        <v>300</v>
+      </c>
+      <c r="D478" t="inlineStr"/>
+      <c r="E478" s="1" t="n">
+        <v>46224.77610663194</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="n">
+        <v>4032642</v>
+      </c>
+      <c r="B479" t="n">
+        <v>2600013973</v>
+      </c>
+      <c r="C479" t="n">
+        <v>310</v>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E479" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="n">
+        <v>4038405</v>
+      </c>
+      <c r="B480" t="n">
+        <v>2600019348</v>
+      </c>
+      <c r="C480" t="n">
+        <v>310</v>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E480" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="n">
+        <v>4034432</v>
+      </c>
+      <c r="B481" t="n">
+        <v>2600016025</v>
+      </c>
+      <c r="C481" t="n">
+        <v>310</v>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E481" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="n">
+        <v>4022441</v>
+      </c>
+      <c r="B482" t="n">
+        <v>2600017214</v>
+      </c>
+      <c r="C482" t="n">
+        <v>310</v>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E482" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="n">
+        <v>4028612</v>
+      </c>
+      <c r="B483" t="n">
+        <v>2600020436</v>
+      </c>
+      <c r="C483" t="n">
+        <v>310</v>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E483" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="n">
+        <v>4034768</v>
+      </c>
+      <c r="B484" t="n">
+        <v>2600018669</v>
+      </c>
+      <c r="C484" t="n">
+        <v>310</v>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E484" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="n">
+        <v>4029027</v>
+      </c>
+      <c r="B485" t="n">
+        <v>2600004495</v>
+      </c>
+      <c r="C485" t="n">
+        <v>310</v>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E485" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="n">
+        <v>4033648</v>
+      </c>
+      <c r="B486" t="n">
+        <v>2600019227</v>
+      </c>
+      <c r="C486" t="n">
+        <v>310</v>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E486" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="n">
+        <v>4033440</v>
+      </c>
+      <c r="B487" t="n">
+        <v>2600008430</v>
+      </c>
+      <c r="C487" t="n">
+        <v>310</v>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E487" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="n">
+        <v>4036542</v>
+      </c>
+      <c r="B488" t="n">
+        <v>2600012323</v>
+      </c>
+      <c r="C488" t="n">
+        <v>310</v>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E488" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="n">
+        <v>4031899</v>
+      </c>
+      <c r="B489" t="n">
+        <v>2600015692</v>
+      </c>
+      <c r="C489" t="n">
+        <v>310</v>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E489" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="n">
+        <v>4034766</v>
+      </c>
+      <c r="B490" t="n">
+        <v>2600004689</v>
+      </c>
+      <c r="C490" t="n">
+        <v>310</v>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E490" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="n">
+        <v>4033542</v>
+      </c>
+      <c r="B491" t="n">
+        <v>2600015563</v>
+      </c>
+      <c r="C491" t="n">
+        <v>310</v>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E491" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="n">
+        <v>4038112</v>
+      </c>
+      <c r="B492" t="n">
+        <v>2600019216</v>
+      </c>
+      <c r="C492" t="n">
+        <v>310</v>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E492" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="n">
+        <v>4028707</v>
+      </c>
+      <c r="B493" t="n">
+        <v>2600012908</v>
+      </c>
+      <c r="C493" t="n">
+        <v>310</v>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E493" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="n">
+        <v>4036693</v>
+      </c>
+      <c r="B494" t="n">
+        <v>2600007434</v>
+      </c>
+      <c r="C494" t="n">
+        <v>310</v>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E494" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="n">
+        <v>4024687</v>
+      </c>
+      <c r="B495" t="n">
+        <v>2600015532</v>
+      </c>
+      <c r="C495" t="n">
+        <v>310</v>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E495" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="n">
+        <v>4035960</v>
+      </c>
+      <c r="B496" t="n">
+        <v>2600013934</v>
+      </c>
+      <c r="C496" t="n">
+        <v>310</v>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E496" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="n">
+        <v>4036038</v>
+      </c>
+      <c r="B497" t="n">
+        <v>2600015695</v>
+      </c>
+      <c r="C497" t="n">
+        <v>310</v>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E497" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="n">
+        <v>4037795</v>
+      </c>
+      <c r="B498" t="n">
+        <v>2600012340</v>
+      </c>
+      <c r="C498" t="n">
+        <v>310</v>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E498" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="n">
+        <v>4034133</v>
+      </c>
+      <c r="B499" t="n">
+        <v>2600007936</v>
+      </c>
+      <c r="C499" t="n">
+        <v>310</v>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E499" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="n">
+        <v>4037786</v>
+      </c>
+      <c r="B500" t="n">
+        <v>2500044669</v>
+      </c>
+      <c r="C500" t="n">
+        <v>310</v>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E500" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="n">
+        <v>4024251</v>
+      </c>
+      <c r="B501" t="n">
+        <v>2600018270</v>
+      </c>
+      <c r="C501" t="n">
+        <v>310</v>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E501" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="n">
+        <v>4036038</v>
+      </c>
+      <c r="B502" t="n">
+        <v>2600004680</v>
+      </c>
+      <c r="C502" t="n">
+        <v>310</v>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E502" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="n">
+        <v>4032303</v>
+      </c>
+      <c r="B503" t="n">
+        <v>2600018038</v>
+      </c>
+      <c r="C503" t="n">
+        <v>310</v>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E503" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="n">
+        <v>4037248</v>
+      </c>
+      <c r="B504" t="n">
+        <v>2600004491</v>
+      </c>
+      <c r="C504" t="n">
+        <v>310</v>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E504" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="n">
+        <v>4033681</v>
+      </c>
+      <c r="B505" t="n">
+        <v>2600015870</v>
+      </c>
+      <c r="C505" t="n">
+        <v>310</v>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E505" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="n">
+        <v>4024293</v>
+      </c>
+      <c r="B506" t="n">
+        <v>2600011974</v>
+      </c>
+      <c r="C506" t="n">
+        <v>310</v>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E506" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="n">
+        <v>4031900</v>
+      </c>
+      <c r="B507" t="n">
+        <v>2600015377</v>
+      </c>
+      <c r="C507" t="n">
+        <v>310</v>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E507" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="n">
+        <v>4033619</v>
+      </c>
+      <c r="B508" t="n">
+        <v>2600017253</v>
+      </c>
+      <c r="C508" t="n">
+        <v>310</v>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E508" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="n">
+        <v>4035828</v>
+      </c>
+      <c r="B509" t="n">
+        <v>2600011799</v>
+      </c>
+      <c r="C509" t="n">
+        <v>310</v>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E509" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="n">
+        <v>4031295</v>
+      </c>
+      <c r="B510" t="n">
+        <v>2600018551</v>
+      </c>
+      <c r="C510" t="n">
+        <v>310</v>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E510" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="n">
+        <v>4037934</v>
+      </c>
+      <c r="B511" t="n">
+        <v>2600007785</v>
+      </c>
+      <c r="C511" t="n">
+        <v>310</v>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E511" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="n">
+        <v>4036193</v>
+      </c>
+      <c r="B512" t="n">
+        <v>2600015581</v>
+      </c>
+      <c r="C512" t="n">
+        <v>310</v>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E512" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="n">
+        <v>4029185</v>
+      </c>
+      <c r="B513" t="n">
+        <v>2600011846</v>
+      </c>
+      <c r="C513" t="n">
+        <v>310</v>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E513" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="n">
+        <v>4032672</v>
+      </c>
+      <c r="B514" t="n">
+        <v>2600011968</v>
+      </c>
+      <c r="C514" t="n">
+        <v>310</v>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E514" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="n">
+        <v>4036540</v>
+      </c>
+      <c r="B515" t="n">
+        <v>2600007544</v>
+      </c>
+      <c r="C515" t="n">
+        <v>310</v>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E515" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="n">
+        <v>4028673</v>
+      </c>
+      <c r="B516" t="n">
+        <v>2600012427</v>
+      </c>
+      <c r="C516" t="n">
+        <v>310</v>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E516" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="n">
+        <v>4034131</v>
+      </c>
+      <c r="B517" t="n">
+        <v>2600007131</v>
+      </c>
+      <c r="C517" t="n">
+        <v>310</v>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E517" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="n">
+        <v>4024254</v>
+      </c>
+      <c r="B518" t="n">
+        <v>2600018037</v>
+      </c>
+      <c r="C518" t="n">
+        <v>310</v>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E518" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="n">
+        <v>4031431</v>
+      </c>
+      <c r="B519" t="n">
+        <v>2600011435</v>
+      </c>
+      <c r="C519" t="n">
+        <v>310</v>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E519" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="n">
+        <v>4036926</v>
+      </c>
+      <c r="B520" t="n">
+        <v>2600012161</v>
+      </c>
+      <c r="C520" t="n">
+        <v>310</v>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E520" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="n">
+        <v>4036347</v>
+      </c>
+      <c r="B521" t="n">
+        <v>2600007628</v>
+      </c>
+      <c r="C521" t="n">
+        <v>310</v>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E521" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="n">
+        <v>4035719</v>
+      </c>
+      <c r="B522" t="n">
+        <v>2600012629</v>
+      </c>
+      <c r="C522" t="n">
+        <v>310</v>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E522" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="n">
+        <v>4031522</v>
+      </c>
+      <c r="B523" t="n">
+        <v>2600012255</v>
+      </c>
+      <c r="C523" t="n">
+        <v>310</v>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E523" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="n">
+        <v>4035959</v>
+      </c>
+      <c r="B524" t="n">
+        <v>2600012393</v>
+      </c>
+      <c r="C524" t="n">
+        <v>310</v>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E524" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="n">
+        <v>4031295</v>
+      </c>
+      <c r="B525" t="n">
+        <v>2600018552</v>
+      </c>
+      <c r="C525" t="n">
+        <v>310</v>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E525" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="n">
+        <v>4028656</v>
+      </c>
+      <c r="B526" t="n">
+        <v>2600017195</v>
+      </c>
+      <c r="C526" t="n">
+        <v>310</v>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E526" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="n">
+        <v>4036927</v>
+      </c>
+      <c r="B527" t="n">
+        <v>2600015006</v>
+      </c>
+      <c r="C527" t="n">
+        <v>310</v>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E527" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="n">
+        <v>4029103</v>
+      </c>
+      <c r="B528" t="n">
+        <v>2600001201</v>
+      </c>
+      <c r="C528" t="n">
+        <v>310</v>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E528" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="n">
+        <v>4034733</v>
+      </c>
+      <c r="B529" t="n">
+        <v>2600012641</v>
+      </c>
+      <c r="C529" t="n">
+        <v>310</v>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E529" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="n">
+        <v>4032379</v>
+      </c>
+      <c r="B530" t="n">
+        <v>2600007629</v>
+      </c>
+      <c r="C530" t="n">
+        <v>310</v>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E530" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="n">
+        <v>4033581</v>
+      </c>
+      <c r="B531" t="n">
+        <v>2600007277</v>
+      </c>
+      <c r="C531" t="n">
+        <v>310</v>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E531" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="n">
+        <v>4038303</v>
+      </c>
+      <c r="B532" t="n">
+        <v>2600011970</v>
+      </c>
+      <c r="C532" t="n">
+        <v>310</v>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E532" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="n">
+        <v>4035831</v>
+      </c>
+      <c r="B533" t="n">
+        <v>2600010820</v>
+      </c>
+      <c r="C533" t="n">
+        <v>310</v>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E533" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="n">
+        <v>4035721</v>
+      </c>
+      <c r="B534" t="n">
+        <v>2600008605</v>
+      </c>
+      <c r="C534" t="n">
+        <v>310</v>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E534" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="n">
+        <v>4029162</v>
+      </c>
+      <c r="B535" t="n">
+        <v>2600011829</v>
+      </c>
+      <c r="C535" t="n">
+        <v>310</v>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E535" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="n">
+        <v>4028476</v>
+      </c>
+      <c r="B536" t="n">
+        <v>2600012193</v>
+      </c>
+      <c r="C536" t="n">
+        <v>310</v>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E536" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="n">
+        <v>4031295</v>
+      </c>
+      <c r="B537" t="n">
+        <v>2600017536</v>
+      </c>
+      <c r="C537" t="n">
+        <v>310</v>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E537" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="n">
+        <v>4030063</v>
+      </c>
+      <c r="B538" t="n">
+        <v>2600007626</v>
+      </c>
+      <c r="C538" t="n">
+        <v>310</v>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E538" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="n">
+        <v>4028673</v>
+      </c>
+      <c r="B539" t="n">
+        <v>2600007591</v>
+      </c>
+      <c r="C539" t="n">
+        <v>310</v>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E539" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="n">
+        <v>4028735</v>
+      </c>
+      <c r="B540" t="n">
+        <v>2600014540</v>
+      </c>
+      <c r="C540" t="n">
+        <v>310</v>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E540" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="n">
+        <v>4034388</v>
+      </c>
+      <c r="B541" t="n">
+        <v>2600012374</v>
+      </c>
+      <c r="C541" t="n">
+        <v>310</v>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E541" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="n">
+        <v>4028735</v>
+      </c>
+      <c r="B542" t="n">
+        <v>2600014360</v>
+      </c>
+      <c r="C542" t="n">
+        <v>310</v>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E542" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="n">
+        <v>4028675</v>
+      </c>
+      <c r="B543" t="n">
+        <v>2600007592</v>
+      </c>
+      <c r="C543" t="n">
+        <v>310</v>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E543" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="n">
+        <v>4037918</v>
+      </c>
+      <c r="B544" t="n">
+        <v>2600014739</v>
+      </c>
+      <c r="C544" t="n">
+        <v>310</v>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E544" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="n">
+        <v>4032264</v>
+      </c>
+      <c r="B545" t="n">
+        <v>2600012383</v>
+      </c>
+      <c r="C545" t="n">
+        <v>310</v>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E545" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="n">
+        <v>4024515</v>
+      </c>
+      <c r="B546" t="n">
+        <v>2600018231</v>
+      </c>
+      <c r="C546" t="n">
+        <v>310</v>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E546" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="n">
+        <v>4037188</v>
+      </c>
+      <c r="B547" t="n">
+        <v>2600011971</v>
+      </c>
+      <c r="C547" t="n">
+        <v>310</v>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E547" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="n">
+        <v>4033543</v>
+      </c>
+      <c r="B548" t="n">
+        <v>2600015231</v>
+      </c>
+      <c r="C548" t="n">
+        <v>310</v>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E548" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="n">
+        <v>4032379</v>
+      </c>
+      <c r="B549" t="n">
+        <v>2600011972</v>
+      </c>
+      <c r="C549" t="n">
+        <v>310</v>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E549" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="n">
+        <v>4032644</v>
+      </c>
+      <c r="B550" t="n">
+        <v>2600007750</v>
+      </c>
+      <c r="C550" t="n">
+        <v>310</v>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E550" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="n">
+        <v>4024293</v>
+      </c>
+      <c r="B551" t="n">
+        <v>2600018218</v>
+      </c>
+      <c r="C551" t="n">
+        <v>310</v>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E551" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="n">
+        <v>4037919</v>
+      </c>
+      <c r="B552" t="n">
+        <v>2500046057</v>
+      </c>
+      <c r="C552" t="n">
+        <v>310</v>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E552" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="n">
+        <v>4029092</v>
+      </c>
+      <c r="B553" t="n">
+        <v>2600011828</v>
+      </c>
+      <c r="C553" t="n">
+        <v>310</v>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E553" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="n">
+        <v>4035959</v>
+      </c>
+      <c r="B554" t="n">
+        <v>2600015893</v>
+      </c>
+      <c r="C554" t="n">
+        <v>310</v>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E554" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="n">
+        <v>4031432</v>
+      </c>
+      <c r="B555" t="n">
+        <v>2600012441</v>
+      </c>
+      <c r="C555" t="n">
+        <v>310</v>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E555" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="n">
+        <v>4030834</v>
+      </c>
+      <c r="B556" t="n">
+        <v>2600012164</v>
+      </c>
+      <c r="C556" t="n">
+        <v>310</v>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E556" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="n">
+        <v>4032383</v>
+      </c>
+      <c r="B557" t="n">
+        <v>2600010433</v>
+      </c>
+      <c r="C557" t="n">
+        <v>310</v>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E557" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="n">
+        <v>4037286</v>
+      </c>
+      <c r="B558" t="n">
+        <v>2600014755</v>
+      </c>
+      <c r="C558" t="n">
+        <v>310</v>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E558" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="n">
+        <v>4034717</v>
+      </c>
+      <c r="B559" t="n">
+        <v>2600012628</v>
+      </c>
+      <c r="C559" t="n">
+        <v>310</v>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E559" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="n">
+        <v>4028742</v>
+      </c>
+      <c r="B560" t="n">
+        <v>2600012789</v>
+      </c>
+      <c r="C560" t="n">
+        <v>310</v>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E560" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="n">
+        <v>4029054</v>
+      </c>
+      <c r="B561" t="n">
+        <v>2600011808</v>
+      </c>
+      <c r="C561" t="n">
+        <v>310</v>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E561" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="n">
+        <v>4034463</v>
+      </c>
+      <c r="B562" t="n">
+        <v>2300048188</v>
+      </c>
+      <c r="C562" t="n">
+        <v>310</v>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E562" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="n">
+        <v>4036959</v>
+      </c>
+      <c r="B563" t="n">
+        <v>2600020654</v>
+      </c>
+      <c r="C563" t="n">
+        <v>310</v>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E563" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="n">
+        <v>4036735</v>
+      </c>
+      <c r="B564" t="n">
+        <v>2600004230</v>
+      </c>
+      <c r="C564" t="n">
+        <v>310</v>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E564" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="n">
+        <v>4028742</v>
+      </c>
+      <c r="B565" t="n">
+        <v>2600020162</v>
+      </c>
+      <c r="C565" t="n">
+        <v>310</v>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E565" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="n">
+        <v>4036959</v>
+      </c>
+      <c r="B566" t="n">
+        <v>2600020664</v>
+      </c>
+      <c r="C566" t="n">
+        <v>310</v>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E566" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="n">
+        <v>4031295</v>
+      </c>
+      <c r="B567" t="n">
+        <v>2600010135</v>
+      </c>
+      <c r="C567" t="n">
+        <v>310</v>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E567" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="n">
+        <v>4032383</v>
+      </c>
+      <c r="B568" t="n">
+        <v>2600011964</v>
+      </c>
+      <c r="C568" t="n">
+        <v>310</v>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E568" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="n">
+        <v>4034132</v>
+      </c>
+      <c r="B569" t="n">
+        <v>2600007625</v>
+      </c>
+      <c r="C569" t="n">
+        <v>310</v>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E569" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="n">
+        <v>4028735</v>
+      </c>
+      <c r="B570" t="n">
+        <v>2600010565</v>
+      </c>
+      <c r="C570" t="n">
+        <v>310</v>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E570" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="n">
+        <v>4036959</v>
+      </c>
+      <c r="B571" t="n">
+        <v>2600020663</v>
+      </c>
+      <c r="C571" t="n">
+        <v>310</v>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E571" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="n">
+        <v>4028735</v>
+      </c>
+      <c r="B572" t="n">
+        <v>2600019432</v>
+      </c>
+      <c r="C572" t="n">
+        <v>310</v>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E572" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="n">
+        <v>4032707</v>
+      </c>
+      <c r="B573" t="n">
+        <v>2600017183</v>
+      </c>
+      <c r="C573" t="n">
+        <v>310</v>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E573" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="n">
+        <v>4033310</v>
+      </c>
+      <c r="B574" t="n">
+        <v>2600014783</v>
+      </c>
+      <c r="C574" t="n">
+        <v>310</v>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E574" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="n">
+        <v>4028742</v>
+      </c>
+      <c r="B575" t="n">
+        <v>2600016711</v>
+      </c>
+      <c r="C575" t="n">
+        <v>310</v>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E575" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="n">
+        <v>4032577</v>
+      </c>
+      <c r="B576" t="n">
+        <v>2600015242</v>
+      </c>
+      <c r="C576" t="n">
+        <v>310</v>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E576" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="n">
+        <v>4035833</v>
+      </c>
+      <c r="B577" t="n">
+        <v>2600014984</v>
+      </c>
+      <c r="C577" t="n">
+        <v>310</v>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E577" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="n">
+        <v>4035865</v>
+      </c>
+      <c r="B578" t="n">
+        <v>2600008143</v>
+      </c>
+      <c r="C578" t="n">
+        <v>310</v>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E578" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="n">
+        <v>4028742</v>
+      </c>
+      <c r="B579" t="n">
+        <v>2600012790</v>
+      </c>
+      <c r="C579" t="n">
+        <v>310</v>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E579" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="n">
+        <v>4028742</v>
+      </c>
+      <c r="B580" t="n">
+        <v>2600013260</v>
+      </c>
+      <c r="C580" t="n">
+        <v>310</v>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E580" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="n">
+        <v>4034132</v>
+      </c>
+      <c r="B581" t="n">
+        <v>2600013919</v>
+      </c>
+      <c r="C581" t="n">
+        <v>310</v>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E581" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="n">
+        <v>4029185</v>
+      </c>
+      <c r="B582" t="n">
+        <v>2600015233</v>
+      </c>
+      <c r="C582" t="n">
+        <v>310</v>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E582" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="n">
+        <v>4037393</v>
+      </c>
+      <c r="B583" t="n">
+        <v>2600012438</v>
+      </c>
+      <c r="C583" t="n">
+        <v>310</v>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E583" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="n">
+        <v>4035828</v>
+      </c>
+      <c r="B584" t="n">
+        <v>2600015376</v>
+      </c>
+      <c r="C584" t="n">
+        <v>310</v>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E584" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="n">
+        <v>4038117</v>
+      </c>
+      <c r="B585" t="n">
+        <v>2600012158</v>
+      </c>
+      <c r="C585" t="n">
+        <v>310</v>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E585" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="n">
+        <v>4032673</v>
+      </c>
+      <c r="B586" t="n">
+        <v>2600011961</v>
+      </c>
+      <c r="C586" t="n">
+        <v>310</v>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E586" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="n">
+        <v>4032701</v>
+      </c>
+      <c r="B587" t="n">
+        <v>2600007551</v>
+      </c>
+      <c r="C587" t="n">
+        <v>310</v>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E587" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="n">
+        <v>4035726</v>
+      </c>
+      <c r="B588" t="n">
+        <v>2600007593</v>
+      </c>
+      <c r="C588" t="n">
+        <v>310</v>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E588" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="n">
+        <v>4029187</v>
+      </c>
+      <c r="B589" t="n">
+        <v>2600015271</v>
+      </c>
+      <c r="C589" t="n">
+        <v>310</v>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E589" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="n">
+        <v>4033046</v>
+      </c>
+      <c r="B590" t="n">
+        <v>2600018638</v>
+      </c>
+      <c r="C590" t="n">
+        <v>310</v>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E590" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="n">
+        <v>4029194</v>
+      </c>
+      <c r="B591" t="n">
+        <v>2600011836</v>
+      </c>
+      <c r="C591" t="n">
+        <v>310</v>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E591" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="n">
+        <v>4029186</v>
+      </c>
+      <c r="B592" t="n">
+        <v>2600011844</v>
+      </c>
+      <c r="C592" t="n">
+        <v>310</v>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E592" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="n">
+        <v>4035827</v>
+      </c>
+      <c r="B593" t="n">
+        <v>2600007756</v>
+      </c>
+      <c r="C593" t="n">
+        <v>310</v>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E593" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="n">
+        <v>4030415</v>
+      </c>
+      <c r="B594" t="n">
+        <v>2600012375</v>
+      </c>
+      <c r="C594" t="n">
+        <v>310</v>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E594" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="n">
+        <v>4036347</v>
+      </c>
+      <c r="B595" t="n">
+        <v>2600011969</v>
+      </c>
+      <c r="C595" t="n">
+        <v>310</v>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E595" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="n">
+        <v>4025810</v>
+      </c>
+      <c r="B596" t="n">
+        <v>2600011842</v>
+      </c>
+      <c r="C596" t="n">
+        <v>310</v>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E596" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="n">
+        <v>4032359</v>
+      </c>
+      <c r="B597" t="n">
+        <v>2600011429</v>
+      </c>
+      <c r="C597" t="n">
+        <v>310</v>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E597" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="n">
+        <v>4029186</v>
+      </c>
+      <c r="B598" t="n">
+        <v>2600015232</v>
+      </c>
+      <c r="C598" t="n">
+        <v>310</v>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E598" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="n">
+        <v>4036984</v>
+      </c>
+      <c r="B599" t="n">
+        <v>2600010976</v>
+      </c>
+      <c r="C599" t="n">
+        <v>310</v>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E599" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="n">
+        <v>4036234</v>
+      </c>
+      <c r="B600" t="n">
+        <v>2600014718</v>
+      </c>
+      <c r="C600" t="n">
+        <v>310</v>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E600" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="n">
+        <v>4033680</v>
+      </c>
+      <c r="B601" t="n">
+        <v>2600015372</v>
+      </c>
+      <c r="C601" t="n">
+        <v>310</v>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E601" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="n">
+        <v>4036691</v>
+      </c>
+      <c r="B602" t="n">
+        <v>2600007333</v>
+      </c>
+      <c r="C602" t="n">
+        <v>310</v>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E602" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="n">
+        <v>4032642</v>
+      </c>
+      <c r="B603" t="n">
+        <v>2600010585</v>
+      </c>
+      <c r="C603" t="n">
+        <v>310</v>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E603" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="n">
+        <v>4031970</v>
+      </c>
+      <c r="B604" t="n">
+        <v>2600015744</v>
+      </c>
+      <c r="C604" t="n">
+        <v>310</v>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E604" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="n">
+        <v>4027481</v>
+      </c>
+      <c r="B605" t="n">
+        <v>2600010697</v>
+      </c>
+      <c r="C605" t="n">
+        <v>310</v>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E605" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="n">
+        <v>4028610</v>
+      </c>
+      <c r="B606" t="n">
+        <v>2600009723</v>
+      </c>
+      <c r="C606" t="n">
+        <v>310</v>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E606" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="n">
+        <v>4032643</v>
+      </c>
+      <c r="B607" t="n">
+        <v>2600020643</v>
+      </c>
+      <c r="C607" t="n">
+        <v>310</v>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E607" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="n">
+        <v>4029266</v>
+      </c>
+      <c r="B608" t="n">
+        <v>2600017913</v>
+      </c>
+      <c r="C608" t="n">
+        <v>310</v>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E608" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="n">
+        <v>4031948</v>
+      </c>
+      <c r="B609" t="n">
+        <v>2600019801</v>
+      </c>
+      <c r="C609" t="n">
+        <v>310</v>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E609" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="n">
+        <v>4031948</v>
+      </c>
+      <c r="B610" t="n">
+        <v>2600018334</v>
+      </c>
+      <c r="C610" t="n">
+        <v>310</v>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E610" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="n">
+        <v>4023137</v>
+      </c>
+      <c r="B611" t="n">
+        <v>2600012970</v>
+      </c>
+      <c r="C611" t="n">
+        <v>310</v>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E611" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="n">
+        <v>4028082</v>
+      </c>
+      <c r="B612" t="n">
+        <v>2600010695</v>
+      </c>
+      <c r="C612" t="n">
+        <v>310</v>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E612" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="n">
+        <v>4033504</v>
+      </c>
+      <c r="B613" t="n">
+        <v>2600015659</v>
+      </c>
+      <c r="C613" t="n">
+        <v>310</v>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E613" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="n">
+        <v>4032642</v>
+      </c>
+      <c r="B614" t="n">
+        <v>2600017918</v>
+      </c>
+      <c r="C614" t="n">
+        <v>310</v>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E614" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="n">
+        <v>4034125</v>
+      </c>
+      <c r="B615" t="n">
+        <v>2600017366</v>
+      </c>
+      <c r="C615" t="n">
+        <v>310</v>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E615" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="n">
+        <v>4028610</v>
+      </c>
+      <c r="B616" t="n">
+        <v>2600017832</v>
+      </c>
+      <c r="C616" t="n">
+        <v>310</v>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E616" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="n">
+        <v>4027651</v>
+      </c>
+      <c r="B617" t="n">
+        <v>2600017915</v>
+      </c>
+      <c r="C617" t="n">
+        <v>310</v>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E617" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="n">
+        <v>4034682</v>
+      </c>
+      <c r="B618" t="n">
+        <v>2500043625</v>
+      </c>
+      <c r="C618" t="n">
+        <v>310</v>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E618" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="n">
+        <v>4034125</v>
+      </c>
+      <c r="B619" t="n">
+        <v>2600017365</v>
+      </c>
+      <c r="C619" t="n">
+        <v>310</v>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E619" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="n">
+        <v>4029266</v>
+      </c>
+      <c r="B620" t="n">
+        <v>2600011674</v>
+      </c>
+      <c r="C620" t="n">
+        <v>310</v>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E620" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="n">
+        <v>4027651</v>
+      </c>
+      <c r="B621" t="n">
+        <v>2600016056</v>
+      </c>
+      <c r="C621" t="n">
+        <v>310</v>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E621" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="n">
+        <v>4023137</v>
+      </c>
+      <c r="B622" t="n">
+        <v>2600018761</v>
+      </c>
+      <c r="C622" t="n">
+        <v>310</v>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E622" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="n">
+        <v>4031970</v>
+      </c>
+      <c r="B623" t="n">
+        <v>2600016482</v>
+      </c>
+      <c r="C623" t="n">
+        <v>310</v>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E623" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="n">
+        <v>4027481</v>
+      </c>
+      <c r="B624" t="n">
+        <v>2600017793</v>
+      </c>
+      <c r="C624" t="n">
+        <v>310</v>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E624" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="n">
+        <v>4030935</v>
+      </c>
+      <c r="B625" t="n">
+        <v>2600010733</v>
+      </c>
+      <c r="C625" t="n">
+        <v>310</v>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E625" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="n">
+        <v>4031619</v>
+      </c>
+      <c r="B626" t="n">
+        <v>2600018130</v>
+      </c>
+      <c r="C626" t="n">
+        <v>310</v>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E626" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="n">
+        <v>4028576</v>
+      </c>
+      <c r="B627" t="n">
+        <v>2600009950</v>
+      </c>
+      <c r="C627" t="n">
+        <v>310</v>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E627" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="n">
+        <v>4034426</v>
+      </c>
+      <c r="B628" t="n">
+        <v>2600016476</v>
+      </c>
+      <c r="C628" t="n">
+        <v>310</v>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E628" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="n">
+        <v>4038128</v>
+      </c>
+      <c r="B629" t="n">
+        <v>2600009142</v>
+      </c>
+      <c r="C629" t="n">
+        <v>310</v>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E629" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="n">
+        <v>4030368</v>
+      </c>
+      <c r="B630" t="n">
+        <v>2600021105</v>
+      </c>
+      <c r="C630" t="n">
+        <v>310</v>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E630" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="n">
+        <v>4031970</v>
+      </c>
+      <c r="B631" t="n">
+        <v>2600010713</v>
+      </c>
+      <c r="C631" t="n">
+        <v>310</v>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E631" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="n">
+        <v>4034432</v>
+      </c>
+      <c r="B632" t="n">
+        <v>2600014040</v>
+      </c>
+      <c r="C632" t="n">
+        <v>310</v>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>TESTE-FIX</t>
+        </is>
+      </c>
+      <c r="E632" s="1" t="n">
+        <v>46226.95586688657</v>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="n">
+        <v>4007866</v>
+      </c>
+      <c r="B633" t="n">
+        <v>2400036872</v>
+      </c>
+      <c r="C633" t="n">
+        <v>310</v>
+      </c>
+      <c r="D633" t="inlineStr"/>
+      <c r="E633" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="n">
+        <v>4035462</v>
+      </c>
+      <c r="B634" t="n">
+        <v>2600000029</v>
+      </c>
+      <c r="C634" t="n">
+        <v>310</v>
+      </c>
+      <c r="D634" t="inlineStr"/>
+      <c r="E634" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="n">
+        <v>4036038</v>
+      </c>
+      <c r="B635" t="n">
+        <v>2600007151</v>
+      </c>
+      <c r="C635" t="n">
+        <v>310</v>
+      </c>
+      <c r="D635" t="inlineStr"/>
+      <c r="E635" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="n">
+        <v>4040436</v>
+      </c>
+      <c r="B636" t="n">
+        <v>2600012252</v>
+      </c>
+      <c r="C636" t="n">
+        <v>310</v>
+      </c>
+      <c r="D636" t="inlineStr"/>
+      <c r="E636" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="n">
+        <v>4040563</v>
+      </c>
+      <c r="B637" t="n">
+        <v>2500039677</v>
+      </c>
+      <c r="C637" t="n">
+        <v>310</v>
+      </c>
+      <c r="D637" t="inlineStr"/>
+      <c r="E637" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="n">
+        <v>4040093</v>
+      </c>
+      <c r="B638" t="n">
+        <v>2600014767</v>
+      </c>
+      <c r="C638" t="n">
+        <v>310</v>
+      </c>
+      <c r="D638" t="inlineStr"/>
+      <c r="E638" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="n">
+        <v>4036544</v>
+      </c>
+      <c r="B639" t="n">
+        <v>2500032713</v>
+      </c>
+      <c r="C639" t="n">
+        <v>310</v>
+      </c>
+      <c r="D639" t="inlineStr"/>
+      <c r="E639" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="n">
+        <v>4040693</v>
+      </c>
+      <c r="B640" t="n">
+        <v>2600004923</v>
+      </c>
+      <c r="C640" t="n">
+        <v>310</v>
+      </c>
+      <c r="D640" t="inlineStr"/>
+      <c r="E640" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="n">
+        <v>4040440</v>
+      </c>
+      <c r="B641" t="n">
+        <v>2500034652</v>
+      </c>
+      <c r="C641" t="n">
+        <v>310</v>
+      </c>
+      <c r="D641" t="inlineStr"/>
+      <c r="E641" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="n">
+        <v>4036346</v>
+      </c>
+      <c r="B642" t="n">
+        <v>2600000741</v>
+      </c>
+      <c r="C642" t="n">
+        <v>310</v>
+      </c>
+      <c r="D642" t="inlineStr"/>
+      <c r="E642" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="n">
+        <v>4035556</v>
+      </c>
+      <c r="B643" t="n">
+        <v>2500030450</v>
+      </c>
+      <c r="C643" t="n">
+        <v>310</v>
+      </c>
+      <c r="D643" t="inlineStr"/>
+      <c r="E643" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="n">
+        <v>4040562</v>
+      </c>
+      <c r="B644" t="n">
+        <v>2600007145</v>
+      </c>
+      <c r="C644" t="n">
+        <v>310</v>
+      </c>
+      <c r="D644" t="inlineStr"/>
+      <c r="E644" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="n">
+        <v>4040371</v>
+      </c>
+      <c r="B645" t="n">
+        <v>2600016107</v>
+      </c>
+      <c r="C645" t="n">
+        <v>310</v>
+      </c>
+      <c r="D645" t="inlineStr"/>
+      <c r="E645" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="n">
+        <v>4040094</v>
+      </c>
+      <c r="B646" t="n">
+        <v>2600011626</v>
+      </c>
+      <c r="C646" t="n">
+        <v>310</v>
+      </c>
+      <c r="D646" t="inlineStr"/>
+      <c r="E646" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="n">
+        <v>4036540</v>
+      </c>
+      <c r="B647" t="n">
+        <v>2500040976</v>
+      </c>
+      <c r="C647" t="n">
+        <v>310</v>
+      </c>
+      <c r="D647" t="inlineStr"/>
+      <c r="E647" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="n">
+        <v>4036174</v>
+      </c>
+      <c r="B648" t="n">
+        <v>2600009028</v>
+      </c>
+      <c r="C648" t="n">
+        <v>310</v>
+      </c>
+      <c r="D648" t="inlineStr"/>
+      <c r="E648" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="n">
+        <v>4040878</v>
+      </c>
+      <c r="B649" t="n">
+        <v>2500033172</v>
+      </c>
+      <c r="C649" t="n">
+        <v>310</v>
+      </c>
+      <c r="D649" t="inlineStr"/>
+      <c r="E649" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="n">
+        <v>4036542</v>
+      </c>
+      <c r="B650" t="n">
+        <v>2500040428</v>
+      </c>
+      <c r="C650" t="n">
+        <v>310</v>
+      </c>
+      <c r="D650" t="inlineStr"/>
+      <c r="E650" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="n">
+        <v>4041625</v>
+      </c>
+      <c r="B651" t="n">
+        <v>2600007301</v>
+      </c>
+      <c r="C651" t="n">
+        <v>310</v>
+      </c>
+      <c r="D651" t="inlineStr"/>
+      <c r="E651" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="n">
+        <v>4040371</v>
+      </c>
+      <c r="B652" t="n">
+        <v>2600004727</v>
+      </c>
+      <c r="C652" t="n">
+        <v>310</v>
+      </c>
+      <c r="D652" t="inlineStr"/>
+      <c r="E652" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="n">
+        <v>4041624</v>
+      </c>
+      <c r="B653" t="n">
+        <v>2600012437</v>
+      </c>
+      <c r="C653" t="n">
+        <v>310</v>
+      </c>
+      <c r="D653" t="inlineStr"/>
+      <c r="E653" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="n">
+        <v>4039893</v>
+      </c>
+      <c r="B654" t="n">
+        <v>2500031528</v>
+      </c>
+      <c r="C654" t="n">
+        <v>310</v>
+      </c>
+      <c r="D654" t="inlineStr"/>
+      <c r="E654" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="n">
+        <v>4041624</v>
+      </c>
+      <c r="B655" t="n">
+        <v>2600017196</v>
+      </c>
+      <c r="C655" t="n">
+        <v>310</v>
+      </c>
+      <c r="D655" t="inlineStr"/>
+      <c r="E655" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="n">
+        <v>4039891</v>
+      </c>
+      <c r="B656" t="n">
+        <v>2600007103</v>
+      </c>
+      <c r="C656" t="n">
+        <v>310</v>
+      </c>
+      <c r="D656" t="inlineStr"/>
+      <c r="E656" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="n">
+        <v>4036318</v>
+      </c>
+      <c r="B657" t="n">
+        <v>2600005237</v>
+      </c>
+      <c r="C657" t="n">
+        <v>310</v>
+      </c>
+      <c r="D657" t="inlineStr"/>
+      <c r="E657" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="n">
+        <v>4036168</v>
+      </c>
+      <c r="B658" t="n">
+        <v>2600009033</v>
+      </c>
+      <c r="C658" t="n">
+        <v>310</v>
+      </c>
+      <c r="D658" t="inlineStr"/>
+      <c r="E658" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="n">
+        <v>4040239</v>
+      </c>
+      <c r="B659" t="n">
+        <v>2600014220</v>
+      </c>
+      <c r="C659" t="n">
+        <v>310</v>
+      </c>
+      <c r="D659" t="inlineStr"/>
+      <c r="E659" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="n">
+        <v>4041008</v>
+      </c>
+      <c r="B660" t="n">
+        <v>2600014215</v>
+      </c>
+      <c r="C660" t="n">
+        <v>310</v>
+      </c>
+      <c r="D660" t="inlineStr"/>
+      <c r="E660" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="n">
+        <v>4042043</v>
+      </c>
+      <c r="B661" t="n">
+        <v>2600017192</v>
+      </c>
+      <c r="C661" t="n">
+        <v>310</v>
+      </c>
+      <c r="D661" t="inlineStr"/>
+      <c r="E661" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="n">
+        <v>4035600</v>
+      </c>
+      <c r="B662" t="n">
+        <v>2600004469</v>
+      </c>
+      <c r="C662" t="n">
+        <v>310</v>
+      </c>
+      <c r="D662" t="inlineStr"/>
+      <c r="E662" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="n">
+        <v>4039894</v>
+      </c>
+      <c r="B663" t="n">
+        <v>2500034909</v>
+      </c>
+      <c r="C663" t="n">
+        <v>310</v>
+      </c>
+      <c r="D663" t="inlineStr"/>
+      <c r="E663" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="n">
+        <v>4042044</v>
+      </c>
+      <c r="B664" t="n">
+        <v>2600007954</v>
+      </c>
+      <c r="C664" t="n">
+        <v>310</v>
+      </c>
+      <c r="D664" t="inlineStr"/>
+      <c r="E664" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="n">
+        <v>4040084</v>
+      </c>
+      <c r="B665" t="n">
+        <v>2600019857</v>
+      </c>
+      <c r="C665" t="n">
+        <v>310</v>
+      </c>
+      <c r="D665" t="inlineStr"/>
+      <c r="E665" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="n">
+        <v>4042043</v>
+      </c>
+      <c r="B666" t="n">
+        <v>2600008553</v>
+      </c>
+      <c r="C666" t="n">
+        <v>310</v>
+      </c>
+      <c r="D666" t="inlineStr"/>
+      <c r="E666" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="n">
+        <v>4040421</v>
+      </c>
+      <c r="B667" t="n">
+        <v>2600007729</v>
+      </c>
+      <c r="C667" t="n">
+        <v>310</v>
+      </c>
+      <c r="D667" t="inlineStr"/>
+      <c r="E667" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="n">
+        <v>4040247</v>
+      </c>
+      <c r="B668" t="n">
+        <v>2600013622</v>
+      </c>
+      <c r="C668" t="n">
+        <v>310</v>
+      </c>
+      <c r="D668" t="inlineStr"/>
+      <c r="E668" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="n">
+        <v>4035629</v>
+      </c>
+      <c r="B669" t="n">
+        <v>2600004032</v>
+      </c>
+      <c r="C669" t="n">
+        <v>310</v>
+      </c>
+      <c r="D669" t="inlineStr"/>
+      <c r="E669" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="n">
+        <v>4041625</v>
+      </c>
+      <c r="B670" t="n">
+        <v>2600011876</v>
+      </c>
+      <c r="C670" t="n">
+        <v>310</v>
+      </c>
+      <c r="D670" t="inlineStr"/>
+      <c r="E670" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="n">
+        <v>4036541</v>
+      </c>
+      <c r="B671" t="n">
+        <v>2500040684</v>
+      </c>
+      <c r="C671" t="n">
+        <v>310</v>
+      </c>
+      <c r="D671" t="inlineStr"/>
+      <c r="E671" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="n">
+        <v>4040870</v>
+      </c>
+      <c r="B672" t="n">
+        <v>2500039100</v>
+      </c>
+      <c r="C672" t="n">
+        <v>310</v>
+      </c>
+      <c r="D672" t="inlineStr"/>
+      <c r="E672" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="n">
+        <v>4036541</v>
+      </c>
+      <c r="B673" t="n">
+        <v>2600011430</v>
+      </c>
+      <c r="C673" t="n">
+        <v>310</v>
+      </c>
+      <c r="D673" t="inlineStr"/>
+      <c r="E673" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="n">
+        <v>4042663</v>
+      </c>
+      <c r="B674" t="n">
+        <v>2600018621</v>
+      </c>
+      <c r="C674" t="n">
+        <v>310</v>
+      </c>
+      <c r="D674" t="inlineStr"/>
+      <c r="E674" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="n">
+        <v>4040563</v>
+      </c>
+      <c r="B675" t="n">
+        <v>2600001042</v>
+      </c>
+      <c r="C675" t="n">
+        <v>310</v>
+      </c>
+      <c r="D675" t="inlineStr"/>
+      <c r="E675" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="n">
+        <v>4039977</v>
+      </c>
+      <c r="B676" t="n">
+        <v>2600015395</v>
+      </c>
+      <c r="C676" t="n">
+        <v>310</v>
+      </c>
+      <c r="D676" t="inlineStr"/>
+      <c r="E676" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="n">
+        <v>4041517</v>
+      </c>
+      <c r="B677" t="n">
+        <v>2600011436</v>
+      </c>
+      <c r="C677" t="n">
+        <v>310</v>
+      </c>
+      <c r="D677" t="inlineStr"/>
+      <c r="E677" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="n">
+        <v>4001494</v>
+      </c>
+      <c r="B678" t="n">
+        <v>2600018760</v>
+      </c>
+      <c r="C678" t="n">
+        <v>310</v>
+      </c>
+      <c r="D678" t="inlineStr"/>
+      <c r="E678" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="n">
+        <v>4036612</v>
+      </c>
+      <c r="B679" t="n">
+        <v>2600003039</v>
+      </c>
+      <c r="C679" t="n">
+        <v>310</v>
+      </c>
+      <c r="D679" t="inlineStr"/>
+      <c r="E679" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="n">
+        <v>4000689</v>
+      </c>
+      <c r="B680" t="n">
+        <v>2600017666</v>
+      </c>
+      <c r="C680" t="n">
+        <v>310</v>
+      </c>
+      <c r="D680" t="inlineStr"/>
+      <c r="E680" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="n">
+        <v>4000228</v>
+      </c>
+      <c r="B681" t="n">
+        <v>2600012966</v>
+      </c>
+      <c r="C681" t="n">
+        <v>310</v>
+      </c>
+      <c r="D681" t="inlineStr"/>
+      <c r="E681" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="n">
+        <v>4000194</v>
+      </c>
+      <c r="B682" t="n">
+        <v>2600010299</v>
+      </c>
+      <c r="C682" t="n">
+        <v>310</v>
+      </c>
+      <c r="D682" t="inlineStr"/>
+      <c r="E682" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="n">
+        <v>4014578</v>
+      </c>
+      <c r="B683" t="n">
+        <v>2600006127</v>
+      </c>
+      <c r="C683" t="n">
+        <v>310</v>
+      </c>
+      <c r="D683" t="inlineStr"/>
+      <c r="E683" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="n">
+        <v>4000194</v>
+      </c>
+      <c r="B684" t="n">
+        <v>2600010293</v>
+      </c>
+      <c r="C684" t="n">
+        <v>310</v>
+      </c>
+      <c r="D684" t="inlineStr"/>
+      <c r="E684" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="n">
+        <v>4000194</v>
+      </c>
+      <c r="B685" t="n">
+        <v>2600002656</v>
+      </c>
+      <c r="C685" t="n">
+        <v>310</v>
+      </c>
+      <c r="D685" t="inlineStr"/>
+      <c r="E685" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="n">
+        <v>4000194</v>
+      </c>
+      <c r="B686" t="n">
+        <v>2600010298</v>
+      </c>
+      <c r="C686" t="n">
+        <v>310</v>
+      </c>
+      <c r="D686" t="inlineStr"/>
+      <c r="E686" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="n">
+        <v>4000194</v>
+      </c>
+      <c r="B687" t="n">
+        <v>2600016028</v>
+      </c>
+      <c r="C687" t="n">
+        <v>310</v>
+      </c>
+      <c r="D687" t="inlineStr"/>
+      <c r="E687" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="n">
+        <v>4006021</v>
+      </c>
+      <c r="B688" t="n">
+        <v>2600006094</v>
+      </c>
+      <c r="C688" t="n">
+        <v>310</v>
+      </c>
+      <c r="D688" t="inlineStr"/>
+      <c r="E688" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="n">
+        <v>4013743</v>
+      </c>
+      <c r="B689" t="n">
+        <v>2500036968</v>
+      </c>
+      <c r="C689" t="n">
+        <v>310</v>
+      </c>
+      <c r="D689" t="inlineStr"/>
+      <c r="E689" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="n">
+        <v>4006203</v>
+      </c>
+      <c r="B690" t="n">
+        <v>2600009300</v>
+      </c>
+      <c r="C690" t="n">
+        <v>310</v>
+      </c>
+      <c r="D690" t="inlineStr"/>
+      <c r="E690" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="n">
+        <v>4000203</v>
+      </c>
+      <c r="B691" t="n">
+        <v>2600001402</v>
+      </c>
+      <c r="C691" t="n">
+        <v>310</v>
+      </c>
+      <c r="D691" t="inlineStr"/>
+      <c r="E691" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="n">
+        <v>4014578</v>
+      </c>
+      <c r="B692" t="n">
+        <v>2500042296</v>
+      </c>
+      <c r="C692" t="n">
+        <v>310</v>
+      </c>
+      <c r="D692" t="inlineStr"/>
+      <c r="E692" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="n">
+        <v>4000194</v>
+      </c>
+      <c r="B693" t="n">
+        <v>2500044311</v>
+      </c>
+      <c r="C693" t="n">
+        <v>310</v>
+      </c>
+      <c r="D693" t="inlineStr"/>
+      <c r="E693" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="n">
+        <v>4006022</v>
+      </c>
+      <c r="B694" t="n">
+        <v>2500032744</v>
+      </c>
+      <c r="C694" t="n">
+        <v>310</v>
+      </c>
+      <c r="D694" t="inlineStr"/>
+      <c r="E694" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="n">
+        <v>4013458</v>
+      </c>
+      <c r="B695" t="n">
+        <v>2300046048</v>
+      </c>
+      <c r="C695" t="n">
+        <v>310</v>
+      </c>
+      <c r="D695" t="inlineStr"/>
+      <c r="E695" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="n">
+        <v>4000688</v>
+      </c>
+      <c r="B696" t="n">
+        <v>2600009098</v>
+      </c>
+      <c r="C696" t="n">
+        <v>310</v>
+      </c>
+      <c r="D696" t="inlineStr"/>
+      <c r="E696" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="n">
+        <v>4009121</v>
+      </c>
+      <c r="B697" t="n">
+        <v>2600001376</v>
+      </c>
+      <c r="C697" t="n">
+        <v>310</v>
+      </c>
+      <c r="D697" t="inlineStr"/>
+      <c r="E697" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="n">
+        <v>4001494</v>
+      </c>
+      <c r="B698" t="n">
+        <v>2600016473</v>
+      </c>
+      <c r="C698" t="n">
+        <v>310</v>
+      </c>
+      <c r="D698" t="inlineStr"/>
+      <c r="E698" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="n">
+        <v>4000688</v>
+      </c>
+      <c r="B699" t="n">
+        <v>2600016131</v>
+      </c>
+      <c r="C699" t="n">
+        <v>310</v>
+      </c>
+      <c r="D699" t="inlineStr"/>
+      <c r="E699" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="n">
+        <v>4013743</v>
+      </c>
+      <c r="B700" t="n">
+        <v>2600016877</v>
+      </c>
+      <c r="C700" t="n">
+        <v>310</v>
+      </c>
+      <c r="D700" t="inlineStr"/>
+      <c r="E700" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="n">
+        <v>4000231</v>
+      </c>
+      <c r="B701" t="n">
+        <v>2600014893</v>
+      </c>
+      <c r="C701" t="n">
+        <v>310</v>
+      </c>
+      <c r="D701" t="inlineStr"/>
+      <c r="E701" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="n">
+        <v>4001517</v>
+      </c>
+      <c r="B702" t="n">
+        <v>2600011462</v>
+      </c>
+      <c r="C702" t="n">
+        <v>310</v>
+      </c>
+      <c r="D702" t="inlineStr"/>
+      <c r="E702" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="n">
+        <v>4006022</v>
+      </c>
+      <c r="B703" t="n">
+        <v>2600008216</v>
+      </c>
+      <c r="C703" t="n">
+        <v>310</v>
+      </c>
+      <c r="D703" t="inlineStr"/>
+      <c r="E703" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="n">
+        <v>4013743</v>
+      </c>
+      <c r="B704" t="n">
+        <v>2600016876</v>
+      </c>
+      <c r="C704" t="n">
+        <v>310</v>
+      </c>
+      <c r="D704" t="inlineStr"/>
+      <c r="E704" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="n">
+        <v>4036612</v>
+      </c>
+      <c r="B705" t="n">
+        <v>2500044645</v>
+      </c>
+      <c r="C705" t="n">
+        <v>310</v>
+      </c>
+      <c r="D705" t="inlineStr"/>
+      <c r="E705" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="n">
+        <v>4013743</v>
+      </c>
+      <c r="B706" t="n">
+        <v>2600016875</v>
+      </c>
+      <c r="C706" t="n">
+        <v>310</v>
+      </c>
+      <c r="D706" t="inlineStr"/>
+      <c r="E706" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="n">
+        <v>4000310</v>
+      </c>
+      <c r="B707" t="n">
+        <v>2600017435</v>
+      </c>
+      <c r="C707" t="n">
+        <v>310</v>
+      </c>
+      <c r="D707" t="inlineStr"/>
+      <c r="E707" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="n">
+        <v>4000297</v>
+      </c>
+      <c r="B708" t="n">
+        <v>2500013773</v>
+      </c>
+      <c r="C708" t="n">
+        <v>310</v>
+      </c>
+      <c r="D708" t="inlineStr"/>
+      <c r="E708" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="n">
+        <v>4006022</v>
+      </c>
+      <c r="B709" t="n">
+        <v>2600005896</v>
+      </c>
+      <c r="C709" t="n">
+        <v>310</v>
+      </c>
+      <c r="D709" t="inlineStr"/>
+      <c r="E709" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="n">
+        <v>4000310</v>
+      </c>
+      <c r="B710" t="n">
+        <v>2600000399</v>
+      </c>
+      <c r="C710" t="n">
+        <v>310</v>
+      </c>
+      <c r="D710" t="inlineStr"/>
+      <c r="E710" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="n">
+        <v>4000194</v>
+      </c>
+      <c r="B711" t="n">
+        <v>2500013701</v>
+      </c>
+      <c r="C711" t="n">
+        <v>310</v>
+      </c>
+      <c r="D711" t="inlineStr"/>
+      <c r="E711" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="n">
+        <v>4006021</v>
+      </c>
+      <c r="B712" t="n">
+        <v>2600017364</v>
+      </c>
+      <c r="C712" t="n">
+        <v>310</v>
+      </c>
+      <c r="D712" t="inlineStr"/>
+      <c r="E712" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="n">
+        <v>4000312</v>
+      </c>
+      <c r="B713" t="n">
+        <v>2600017354</v>
+      </c>
+      <c r="C713" t="n">
+        <v>310</v>
+      </c>
+      <c r="D713" t="inlineStr"/>
+      <c r="E713" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="n">
+        <v>4001195</v>
+      </c>
+      <c r="B714" t="n">
+        <v>2600005931</v>
+      </c>
+      <c r="C714" t="n">
+        <v>310</v>
+      </c>
+      <c r="D714" t="inlineStr"/>
+      <c r="E714" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="n">
+        <v>4000399</v>
+      </c>
+      <c r="B715" t="n">
+        <v>2600003062</v>
+      </c>
+      <c r="C715" t="n">
+        <v>310</v>
+      </c>
+      <c r="D715" t="inlineStr"/>
+      <c r="E715" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="n">
+        <v>4001552</v>
+      </c>
+      <c r="B716" t="n">
+        <v>2600010469</v>
+      </c>
+      <c r="C716" t="n">
+        <v>310</v>
+      </c>
+      <c r="D716" t="inlineStr"/>
+      <c r="E716" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="n">
+        <v>4006203</v>
+      </c>
+      <c r="B717" t="n">
+        <v>2500009416</v>
+      </c>
+      <c r="C717" t="n">
+        <v>310</v>
+      </c>
+      <c r="D717" t="inlineStr"/>
+      <c r="E717" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="n">
+        <v>4013458</v>
+      </c>
+      <c r="B718" t="n">
+        <v>2400002913</v>
+      </c>
+      <c r="C718" t="n">
+        <v>310</v>
+      </c>
+      <c r="D718" t="inlineStr"/>
+      <c r="E718" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="n">
+        <v>4042087</v>
+      </c>
+      <c r="B719" t="n">
+        <v>2600008961</v>
+      </c>
+      <c r="C719" t="n">
+        <v>310</v>
+      </c>
+      <c r="D719" t="inlineStr"/>
+      <c r="E719" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="n">
+        <v>4006021</v>
+      </c>
+      <c r="B720" t="n">
+        <v>2600017442</v>
+      </c>
+      <c r="C720" t="n">
+        <v>310</v>
+      </c>
+      <c r="D720" t="inlineStr"/>
+      <c r="E720" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="n">
+        <v>4035648</v>
+      </c>
+      <c r="B721" t="n">
+        <v>2400034653</v>
+      </c>
+      <c r="C721" t="n">
+        <v>310</v>
+      </c>
+      <c r="D721" t="inlineStr"/>
+      <c r="E721" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="n">
+        <v>4039923</v>
+      </c>
+      <c r="B722" t="n">
+        <v>2600018727</v>
+      </c>
+      <c r="C722" t="n">
+        <v>310</v>
+      </c>
+      <c r="D722" t="inlineStr"/>
+      <c r="E722" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="n">
+        <v>4001247</v>
+      </c>
+      <c r="B723" t="n">
+        <v>2400027267</v>
+      </c>
+      <c r="C723" t="n">
+        <v>310</v>
+      </c>
+      <c r="D723" t="inlineStr"/>
+      <c r="E723" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="n">
+        <v>4001621</v>
+      </c>
+      <c r="B724" t="n">
+        <v>2600006360</v>
+      </c>
+      <c r="C724" t="n">
+        <v>310</v>
+      </c>
+      <c r="D724" t="inlineStr"/>
+      <c r="E724" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="n">
+        <v>4001247</v>
+      </c>
+      <c r="B725" t="n">
+        <v>2300046729</v>
+      </c>
+      <c r="C725" t="n">
+        <v>310</v>
+      </c>
+      <c r="D725" t="inlineStr"/>
+      <c r="E725" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="n">
+        <v>4001621</v>
+      </c>
+      <c r="B726" t="n">
+        <v>2600006359</v>
+      </c>
+      <c r="C726" t="n">
+        <v>310</v>
+      </c>
+      <c r="D726" t="inlineStr"/>
+      <c r="E726" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="n">
+        <v>4001247</v>
+      </c>
+      <c r="B727" t="n">
+        <v>2400040578</v>
+      </c>
+      <c r="C727" t="n">
+        <v>310</v>
+      </c>
+      <c r="D727" t="inlineStr"/>
+      <c r="E727" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="n">
+        <v>4001607</v>
+      </c>
+      <c r="B728" t="n">
+        <v>2600005202</v>
+      </c>
+      <c r="C728" t="n">
+        <v>310</v>
+      </c>
+      <c r="D728" t="inlineStr"/>
+      <c r="E728" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="n">
+        <v>4001602</v>
+      </c>
+      <c r="B729" t="n">
+        <v>2600020350</v>
+      </c>
+      <c r="C729" t="n">
+        <v>310</v>
+      </c>
+      <c r="D729" t="inlineStr"/>
+      <c r="E729" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="n">
+        <v>4001494</v>
+      </c>
+      <c r="B730" t="n">
+        <v>2600018759</v>
+      </c>
+      <c r="C730" t="n">
+        <v>310</v>
+      </c>
+      <c r="D730" t="inlineStr"/>
+      <c r="E730" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="n">
+        <v>4001552</v>
+      </c>
+      <c r="B731" t="n">
+        <v>2600020440</v>
+      </c>
+      <c r="C731" t="n">
+        <v>310</v>
+      </c>
+      <c r="D731" t="inlineStr"/>
+      <c r="E731" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="n">
+        <v>4013458</v>
+      </c>
+      <c r="B732" t="n">
+        <v>2600020448</v>
+      </c>
+      <c r="C732" t="n">
+        <v>310</v>
+      </c>
+      <c r="D732" t="inlineStr"/>
+      <c r="E732" s="1" t="n">
+        <v>46227.0375333912</v>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="n">
+        <v>3003509</v>
+      </c>
+      <c r="B733" t="n">
+        <v>2100040896</v>
+      </c>
+      <c r="C733" t="n">
+        <v>300</v>
+      </c>
+      <c r="D733" t="inlineStr"/>
+      <c r="E733" s="1" t="n">
+        <v>46227.08727435185</v>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="n">
+        <v>3000550</v>
+      </c>
+      <c r="B734" t="n">
+        <v>2500045195</v>
+      </c>
+      <c r="C734" t="n">
+        <v>300</v>
+      </c>
+      <c r="D734" t="inlineStr"/>
+      <c r="E734" s="1" t="n">
+        <v>46227.08727435185</v>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="n">
+        <v>3001750</v>
+      </c>
+      <c r="B735" t="n">
+        <v>2600017390</v>
+      </c>
+      <c r="C735" t="n">
+        <v>300</v>
+      </c>
+      <c r="D735" t="inlineStr"/>
+      <c r="E735" s="1" t="n">
+        <v>46227.08727435185</v>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="n">
+        <v>3001750</v>
+      </c>
+      <c r="B736" t="n">
+        <v>2600020429</v>
+      </c>
+      <c r="C736" t="n">
+        <v>300</v>
+      </c>
+      <c r="D736" t="inlineStr"/>
+      <c r="E736" s="1" t="n">
+        <v>46227.08727435185</v>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="n">
+        <v>3001659</v>
+      </c>
+      <c r="B737" t="n">
+        <v>2600015646</v>
+      </c>
+      <c r="C737" t="n">
+        <v>300</v>
+      </c>
+      <c r="D737" t="inlineStr"/>
+      <c r="E737" s="1" t="n">
+        <v>46227.08727435185</v>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="n">
+        <v>3000055</v>
+      </c>
+      <c r="B738" t="n">
+        <v>2500018214</v>
+      </c>
+      <c r="C738" t="n">
+        <v>300</v>
+      </c>
+      <c r="D738" t="inlineStr"/>
+      <c r="E738" s="1" t="n">
+        <v>46227.08727435185</v>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="n">
+        <v>3000537</v>
+      </c>
+      <c r="B739" t="n">
+        <v>2500036882</v>
+      </c>
+      <c r="C739" t="n">
+        <v>300</v>
+      </c>
+      <c r="D739" t="inlineStr"/>
+      <c r="E739" s="1" t="n">
+        <v>46227.08727435185</v>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="n">
+        <v>3003808</v>
+      </c>
+      <c r="B740" t="n">
+        <v>2600016580</v>
+      </c>
+      <c r="C740" t="n">
+        <v>300</v>
+      </c>
+      <c r="D740" t="inlineStr"/>
+      <c r="E740" s="1" t="n">
+        <v>46227.08727435185</v>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="n">
+        <v>4028613</v>
+      </c>
+      <c r="B741" t="n">
+        <v>2600017630</v>
+      </c>
+      <c r="C741" t="n">
+        <v>310</v>
+      </c>
+      <c r="D741" t="inlineStr"/>
+      <c r="E741" s="1" t="n">
+        <v>46227.09567518518</v>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="n">
+        <v>4009062</v>
+      </c>
+      <c r="B742" t="n">
+        <v>2600017721</v>
+      </c>
+      <c r="C742" t="n">
+        <v>310</v>
+      </c>
+      <c r="D742" t="inlineStr"/>
+      <c r="E742" s="1" t="n">
+        <v>46227.09567518518</v>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="n">
+        <v>4001624</v>
+      </c>
+      <c r="B743" t="n">
+        <v>2600017431</v>
+      </c>
+      <c r="C743" t="n">
+        <v>310</v>
+      </c>
+      <c r="D743" t="inlineStr"/>
+      <c r="E743" s="1" t="n">
+        <v>46227.09567518518</v>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="n">
+        <v>4018826</v>
+      </c>
+      <c r="B744" t="n">
+        <v>2600020365</v>
+      </c>
+      <c r="C744" t="n">
+        <v>310</v>
+      </c>
+      <c r="D744" t="inlineStr"/>
+      <c r="E744" s="1" t="n">
+        <v>46227.09567518518</v>
       </c>
     </row>
   </sheetData>

--- a/data/historico/historico_documentos.xlsx
+++ b/data/historico/historico_documentos.xlsx
@@ -16,10 +16,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -49,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,226 +476,6 @@
         <is>
           <t>total_valor_geracao</t>
         </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>3001628</v>
-      </c>
-      <c r="B2" t="n">
-        <v>2600014414</v>
-      </c>
-      <c r="C2" t="n">
-        <v>300</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>600005467</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="n">
-        <v>46229.76556306713</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>c9489548-026e-4449-9410-60c5cda92bac</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>valor</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I2" t="n">
-        <v>74560</v>
-      </c>
-      <c r="J2" t="n">
-        <v>5</v>
-      </c>
-      <c r="K2" t="n">
-        <v>100</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1653323.6127568</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>3000550</v>
-      </c>
-      <c r="B3" t="n">
-        <v>2600016047</v>
-      </c>
-      <c r="C3" t="n">
-        <v>300</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>600005467</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>46229.76556306713</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>c9489548-026e-4449-9410-60c5cda92bac</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>valor</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>18</v>
-      </c>
-      <c r="I3" t="n">
-        <v>292732.57</v>
-      </c>
-      <c r="J3" t="n">
-        <v>5</v>
-      </c>
-      <c r="K3" t="n">
-        <v>100</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1653323.6127568</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3000366</v>
-      </c>
-      <c r="B4" t="n">
-        <v>2600015715</v>
-      </c>
-      <c r="C4" t="n">
-        <v>300</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>600005467</t>
-        </is>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>46229.76556306713</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>c9489548-026e-4449-9410-60c5cda92bac</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>valor</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>25</v>
-      </c>
-      <c r="I4" t="n">
-        <v>308387.0391568</v>
-      </c>
-      <c r="J4" t="n">
-        <v>5</v>
-      </c>
-      <c r="K4" t="n">
-        <v>100</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1653323.6127568</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>3002233</v>
-      </c>
-      <c r="B5" t="n">
-        <v>2600014698</v>
-      </c>
-      <c r="C5" t="n">
-        <v>300</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>600005467</t>
-        </is>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46229.76556306713</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>c9489548-026e-4449-9410-60c5cda92bac</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>valor</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>12</v>
-      </c>
-      <c r="I5" t="n">
-        <v>257752</v>
-      </c>
-      <c r="J5" t="n">
-        <v>5</v>
-      </c>
-      <c r="K5" t="n">
-        <v>100</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1653323.6127568</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>3002233</v>
-      </c>
-      <c r="B6" t="n">
-        <v>2600011176</v>
-      </c>
-      <c r="C6" t="n">
-        <v>300</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>600005467</t>
-        </is>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46229.76556306713</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>c9489548-026e-4449-9410-60c5cda92bac</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>valor</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>42</v>
-      </c>
-      <c r="I6" t="n">
-        <v>719892.0035999999</v>
-      </c>
-      <c r="J6" t="n">
-        <v>5</v>
-      </c>
-      <c r="K6" t="n">
-        <v>100</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1653323.6127568</v>
       </c>
     </row>
   </sheetData>

--- a/data/historico/historico_documentos.xlsx
+++ b/data/historico/historico_documentos.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -46,8 +49,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,6 +480,226 @@
         <is>
           <t>total_valor_geracao</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3001628</v>
+      </c>
+      <c r="B2" t="n">
+        <v>2600014414</v>
+      </c>
+      <c r="C2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>345346</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="n">
+        <v>46229.92942528935</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2436b635-d34f-4e71-9116-1291819daa38</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>valor</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I2" t="n">
+        <v>74560</v>
+      </c>
+      <c r="J2" t="n">
+        <v>5</v>
+      </c>
+      <c r="K2" t="n">
+        <v>100</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1653323.6127568</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3000550</v>
+      </c>
+      <c r="B3" t="n">
+        <v>2600016047</v>
+      </c>
+      <c r="C3" t="n">
+        <v>300</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>345346</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>46229.92942528935</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2436b635-d34f-4e71-9116-1291819daa38</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>valor</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>18</v>
+      </c>
+      <c r="I3" t="n">
+        <v>292732.57</v>
+      </c>
+      <c r="J3" t="n">
+        <v>5</v>
+      </c>
+      <c r="K3" t="n">
+        <v>100</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1653323.6127568</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3000366</v>
+      </c>
+      <c r="B4" t="n">
+        <v>2600015715</v>
+      </c>
+      <c r="C4" t="n">
+        <v>300</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>345346</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>46229.92942528935</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2436b635-d34f-4e71-9116-1291819daa38</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>valor</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>25</v>
+      </c>
+      <c r="I4" t="n">
+        <v>308387.0391568</v>
+      </c>
+      <c r="J4" t="n">
+        <v>5</v>
+      </c>
+      <c r="K4" t="n">
+        <v>100</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1653323.6127568</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B5" t="n">
+        <v>2600014698</v>
+      </c>
+      <c r="C5" t="n">
+        <v>300</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>345346</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46229.92942528935</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2436b635-d34f-4e71-9116-1291819daa38</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>valor</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="n">
+        <v>257752</v>
+      </c>
+      <c r="J5" t="n">
+        <v>5</v>
+      </c>
+      <c r="K5" t="n">
+        <v>100</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1653323.6127568</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3002233</v>
+      </c>
+      <c r="B6" t="n">
+        <v>2600011176</v>
+      </c>
+      <c r="C6" t="n">
+        <v>300</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>345346</t>
+        </is>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46229.92942528935</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2436b635-d34f-4e71-9116-1291819daa38</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>valor</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>42</v>
+      </c>
+      <c r="I6" t="n">
+        <v>719892.0035999999</v>
+      </c>
+      <c r="J6" t="n">
+        <v>5</v>
+      </c>
+      <c r="K6" t="n">
+        <v>100</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1653323.6127568</v>
       </c>
     </row>
   </sheetData>

--- a/data/historico/historico_documentos.xlsx
+++ b/data/historico/historico_documentos.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -492,17 +492,13 @@
       <c r="C2" t="n">
         <v>300</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>345346</t>
-        </is>
-      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" s="1" t="n">
-        <v>46229.92942528935</v>
+        <v>46229.9451416088</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2436b635-d34f-4e71-9116-1291819daa38</t>
+          <t>7facf2f0-a5f3-4cf2-b7c5-b2f7d34d6da6</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -536,17 +532,13 @@
       <c r="C3" t="n">
         <v>300</v>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>345346</t>
-        </is>
-      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" s="1" t="n">
-        <v>46229.92942528935</v>
+        <v>46229.9451416088</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2436b635-d34f-4e71-9116-1291819daa38</t>
+          <t>7facf2f0-a5f3-4cf2-b7c5-b2f7d34d6da6</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -580,17 +572,13 @@
       <c r="C4" t="n">
         <v>300</v>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>345346</t>
-        </is>
-      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" s="1" t="n">
-        <v>46229.92942528935</v>
+        <v>46229.9451416088</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2436b635-d34f-4e71-9116-1291819daa38</t>
+          <t>7facf2f0-a5f3-4cf2-b7c5-b2f7d34d6da6</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -624,17 +612,13 @@
       <c r="C5" t="n">
         <v>300</v>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>345346</t>
-        </is>
-      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" s="1" t="n">
-        <v>46229.92942528935</v>
+        <v>46229.9451416088</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2436b635-d34f-4e71-9116-1291819daa38</t>
+          <t>7facf2f0-a5f3-4cf2-b7c5-b2f7d34d6da6</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -668,17 +652,13 @@
       <c r="C6" t="n">
         <v>300</v>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>345346</t>
-        </is>
-      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" s="1" t="n">
-        <v>46229.92942528935</v>
+        <v>46229.9451416088</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2436b635-d34f-4e71-9116-1291819daa38</t>
+          <t>7facf2f0-a5f3-4cf2-b7c5-b2f7d34d6da6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -700,6 +680,328 @@
       </c>
       <c r="L6" t="n">
         <v>1653323.6127568</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2000081.0</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2617402</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" s="1" t="n">
+        <v>46229.94527521631</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>b4e0b3e2-74d3-4597-abb9-48ce0cab50be</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>valor</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>26969.7645</v>
+      </c>
+      <c r="J7" t="n">
+        <v>7</v>
+      </c>
+      <c r="K7" t="n">
+        <v>100</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1255458.60284433</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>3000550.0</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2600004996</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" s="1" t="n">
+        <v>46229.94527521631</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>b4e0b3e2-74d3-4597-abb9-48ce0cab50be</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>valor</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>10</v>
+      </c>
+      <c r="I8" t="n">
+        <v>157622.70799632</v>
+      </c>
+      <c r="J8" t="n">
+        <v>7</v>
+      </c>
+      <c r="K8" t="n">
+        <v>100</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1255458.60284433</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>3000550.0</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2600012494</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" s="1" t="n">
+        <v>46229.94527521631</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>b4e0b3e2-74d3-4597-abb9-48ce0cab50be</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>valor</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>16</v>
+      </c>
+      <c r="I9" t="n">
+        <v>270211.82022797</v>
+      </c>
+      <c r="J9" t="n">
+        <v>7</v>
+      </c>
+      <c r="K9" t="n">
+        <v>100</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1255458.60284433</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>3000550.0</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2600016287</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" s="1" t="n">
+        <v>46229.94527521631</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>b4e0b3e2-74d3-4597-abb9-48ce0cab50be</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>valor</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I10" t="n">
+        <v>202661.01</v>
+      </c>
+      <c r="J10" t="n">
+        <v>7</v>
+      </c>
+      <c r="K10" t="n">
+        <v>100</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1255458.60284433</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>3000502.0</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2600015623</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" s="1" t="n">
+        <v>46229.94527521631</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>b4e0b3e2-74d3-4597-abb9-48ce0cab50be</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>valor</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>39</v>
+      </c>
+      <c r="I11" t="n">
+        <v>237709.89737418</v>
+      </c>
+      <c r="J11" t="n">
+        <v>7</v>
+      </c>
+      <c r="K11" t="n">
+        <v>100</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1255458.60284433</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>3000550.0</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2600012581</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" s="1" t="n">
+        <v>46229.94527521631</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>b4e0b3e2-74d3-4597-abb9-48ce0cab50be</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>valor</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>16</v>
+      </c>
+      <c r="I12" t="n">
+        <v>270211.84274586</v>
+      </c>
+      <c r="J12" t="n">
+        <v>7</v>
+      </c>
+      <c r="K12" t="n">
+        <v>100</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1255458.60284433</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>3000550.0</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2600012493</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" s="1" t="n">
+        <v>46229.94527521631</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>b4e0b3e2-74d3-4597-abb9-48ce0cab50be</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>valor</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>6</v>
+      </c>
+      <c r="I13" t="n">
+        <v>90071.56</v>
+      </c>
+      <c r="J13" t="n">
+        <v>7</v>
+      </c>
+      <c r="K13" t="n">
+        <v>100</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1255458.60284433</v>
       </c>
     </row>
   </sheetData>
